--- a/public/docs_ban_mong/HOBANMONG_THONG_KE_VAT_TU_NEO.xlsx
+++ b/public/docs_ban_mong/HOBANMONG_THONG_KE_VAT_TU_NEO.xlsx
@@ -10,7 +10,8 @@
     <sheet name="DeDay_TungDe" sheetId="5" state="visible" r:id="rId5"/>
     <sheet name="KiemTra_Nhanh" sheetId="6" state="visible" r:id="rId6"/>
     <sheet name="ChieuDaiCat" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="GhiChu" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="KiemTra_DauCoc_De" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="GhiChu" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames/>
 </workbook>
@@ -570,7 +571,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>24</row>
+      <row>25</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="1490133" cy="1117600"/>
@@ -595,7 +596,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>25</row>
+      <row>26</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="1490133" cy="1117600"/>
@@ -620,7 +621,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>26</row>
+      <row>27</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="1490133" cy="1117600"/>
@@ -645,7 +646,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>27</row>
+      <row>28</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="1490133" cy="1117600"/>
@@ -670,7 +671,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>28</row>
+      <row>29</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="1490133" cy="1117600"/>
@@ -695,7 +696,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>29</row>
+      <row>31</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="1490133" cy="1117600"/>
@@ -720,7 +721,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>31</row>
+      <row>32</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="1490133" cy="1117600"/>
@@ -745,7 +746,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>32</row>
+      <row>34</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="1490133" cy="1117600"/>
@@ -770,7 +771,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>34</row>
+      <row>35</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="1490133" cy="1117600"/>
@@ -795,7 +796,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>35</row>
+      <row>36</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="1490133" cy="1117600"/>
@@ -820,7 +821,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>36</row>
+      <row>37</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="1490133" cy="1117600"/>
@@ -845,7 +846,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>37</row>
+      <row>38</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="1490133" cy="1117600"/>
@@ -870,7 +871,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>38</row>
+      <row>39</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="1490133" cy="1117600"/>
@@ -895,7 +896,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>39</row>
+      <row>40</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="1490133" cy="1117600"/>
@@ -920,7 +921,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>40</row>
+      <row>41</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="1490133" cy="1117600"/>
@@ -945,7 +946,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>41</row>
+      <row>42</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="1490133" cy="1117600"/>
@@ -970,7 +971,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>42</row>
+      <row>43</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="1490133" cy="1117600"/>
@@ -995,7 +996,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>43</row>
+      <row>44</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="1490133" cy="1117600"/>
@@ -1020,7 +1021,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>44</row>
+      <row>45</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="1490133" cy="1117600"/>
@@ -1045,7 +1046,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>45</row>
+      <row>46</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="1490133" cy="1117600"/>
@@ -1070,7 +1071,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>46</row>
+      <row>50</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="1490133" cy="1117600"/>
@@ -1095,7 +1096,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>50</row>
+      <row>51</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="1490133" cy="1117600"/>
@@ -1120,7 +1121,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>51</row>
+      <row>52</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="1490133" cy="1117600"/>
@@ -1145,7 +1146,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>52</row>
+      <row>53</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="1490133" cy="1117600"/>
@@ -1170,7 +1171,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>53</row>
+      <row>55</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="1490133" cy="1117600"/>
@@ -1195,7 +1196,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>54</row>
+      <row>56</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="1490133" cy="1117600"/>
@@ -1206,31 +1207,6 @@
       </nvPicPr>
       <blipFill>
         <a:blip cstate="print" r:embed="rId41"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>2</col>
-      <colOff>0</colOff>
-      <row>56</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="1490133" cy="1117600"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="42" name="Image 42" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId42"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -1570,7 +1546,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I58"/>
+  <dimension ref="A1:I59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6.8" customWidth="1" min="1" max="1"/>
@@ -2141,7 +2117,7 @@
       </c>
       <c r="B20" s="7" t="inlineStr">
         <is>
-          <t>Bản nắp thép đầu cọc mạ kẽm</t>
+          <t>Bản mã đầu cọc mạ kẽm (cọc đơn và đài cọc đôi)</t>
         </is>
       </c>
       <c r="C20" s="6" t="n"/>
@@ -2156,19 +2132,19 @@
         </is>
       </c>
       <c r="F20" s="9" t="n">
-        <v>220</v>
+        <v>133</v>
       </c>
       <c r="G20" s="6" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>2%</t>
         </is>
       </c>
       <c r="H20" s="9" t="n">
-        <v>220</v>
+        <v>136</v>
       </c>
       <c r="I20" s="7" t="inlineStr">
         <is>
-          <t>Lấy theo chi tiết của Huổi Vanh (bảng order 15/10) — chưa có bản vẽ chi tiết đầu cọc</t>
+          <t>46 đầu cọc đơn + 87 đài cọc đôi; thiết kế sơ bộ src/lib/calc/shorePileHead.ts (γ = 1.2, T của bè), mức sử dụng lớn nhất 0,91</t>
         </is>
       </c>
     </row>
@@ -2178,13 +2154,13 @@
       </c>
       <c r="B21" s="7" t="inlineStr">
         <is>
-          <t>Tai neo đầu cọc (padeye đơn)</t>
+          <t>Tai neo đầu cọc / đài (padeye)</t>
         </is>
       </c>
       <c r="C21" s="6" t="n"/>
       <c r="D21" s="7" t="inlineStr">
         <is>
-          <t>SS400 t = 25, lỗ chốt Ø40; tim chốt cách mặt đất 0,1 m</t>
+          <t>SS400 t = 25, rộng 200, lỗ chốt Ø32 / Ø39 (= chốt ma-nê + 4 mm); tim chốt cách mặt đất 100 mm; hàn góc 10 mm hai phía</t>
         </is>
       </c>
       <c r="E21" s="6" t="inlineStr">
@@ -2197,15 +2173,15 @@
       </c>
       <c r="G21" s="6" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>2%</t>
         </is>
       </c>
       <c r="H21" s="9" t="n">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="I21" s="7" t="inlineStr">
         <is>
-          <t>Như trên; 1 cái mỗi điểm neo, phải chịu T_max của bè (tới 107,0 kN)</t>
+          <t>1 cái mỗi điểm neo, chịu cả T của dây (tới 107,0 kN); ma-nê 8.5 / 12 t</t>
         </is>
       </c>
     </row>
@@ -2215,13 +2191,13 @@
       </c>
       <c r="B22" s="7" t="inlineStr">
         <is>
-          <t>Râu thép ngàm bản nắp</t>
+          <t>Thép neo bản mã vào bê tông</t>
         </is>
       </c>
       <c r="C22" s="6" t="n"/>
       <c r="D22" s="7" t="inlineStr">
         <is>
-          <t>4Φ25 L = 600 mỗi cọc</t>
+          <t>4Φ22 CB400-V L = 600 mỗi bản mã</t>
         </is>
       </c>
       <c r="E22" s="6" t="inlineStr">
@@ -2230,7 +2206,7 @@
         </is>
       </c>
       <c r="F22" s="9" t="n">
-        <v>880</v>
+        <v>532</v>
       </c>
       <c r="G22" s="6" t="inlineStr">
         <is>
@@ -2238,11 +2214,11 @@
         </is>
       </c>
       <c r="H22" s="9" t="n">
-        <v>898</v>
+        <v>543</v>
       </c>
       <c r="I22" s="7" t="inlineStr">
         <is>
-          <t>Như trên</t>
+          <t>Theo thiết kế đầu cọc (H-6, H-7)</t>
         </is>
       </c>
     </row>
@@ -2252,7 +2228,7 @@
       </c>
       <c r="B23" s="7" t="inlineStr">
         <is>
-          <t>Đài / dầm nối đầu cọc đôi</t>
+          <t>Đài cọc đôi BTCT đổ tại chỗ</t>
         </is>
       </c>
       <c r="C23" s="6" t="inlineStr">
@@ -2262,86 +2238,90 @@
       </c>
       <c r="D23" s="7" t="inlineStr">
         <is>
-          <t>BTCT nối 2 cọc D350 cách nhau ≥ 3D, đỡ tai neo chung</t>
+          <t>C25/30; 1700×650×700 (dài × rộng × cao), 2 cọc D350 cách 1050 mm; 3Φ16 mỗi mặt chịu kéo, 4Φ12 cấu tạo, đai Φ10 a150; thép chủ cọc móc 90° vào đài</t>
         </is>
       </c>
       <c r="E23" s="6" t="inlineStr">
         <is>
-          <t>bộ</t>
-        </is>
-      </c>
-      <c r="F23" s="9" t="n">
-        <v>87</v>
+          <t>m³</t>
+        </is>
+      </c>
+      <c r="F23" s="8" t="n">
+        <v>67.3</v>
       </c>
       <c r="G23" s="6" t="inlineStr">
         <is>
-          <t>CHƯA thiết kế</t>
-        </is>
-      </c>
-      <c r="H23" s="9" t="n">
-        <v>87</v>
+          <t>5%</t>
+        </is>
+      </c>
+      <c r="H23" s="8" t="n">
+        <v>70.7</v>
       </c>
       <c r="I23" s="7" t="inlineStr">
         <is>
-          <t>87 điểm cọc đôi; hệ số nhóm 0,9 là GIẢ ĐỊNH — chưa có bản vẽ, KHÔNG đặt hàng theo dòng này</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="31" customHeight="1">
-      <c r="A24" s="4" t="inlineStr">
+          <t>87 điểm cọc đôi; thiết kế sơ bộ src/lib/calc/twinPileCap.ts (TC-1…TC-4), mức sử dụng lớn nhất 0,94; đỉnh đài ngang mặt đất</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="46" customHeight="1">
+      <c r="A24" s="6" t="n">
+        <v>17</v>
+      </c>
+      <c r="B24" s="7" t="inlineStr">
+        <is>
+          <t>Thép đài cọc đôi</t>
+        </is>
+      </c>
+      <c r="C24" s="6" t="inlineStr">
+        <is>
+          <t>(chưa có hình)</t>
+        </is>
+      </c>
+      <c r="D24" s="7" t="inlineStr">
+        <is>
+          <t>CB400-V Φ16, Φ12 + đai CB240-T Φ10</t>
+        </is>
+      </c>
+      <c r="E24" s="6" t="inlineStr">
+        <is>
+          <t>kg</t>
+        </is>
+      </c>
+      <c r="F24" s="9" t="n">
+        <v>3288</v>
+      </c>
+      <c r="G24" s="6" t="inlineStr">
+        <is>
+          <t>5%</t>
+        </is>
+      </c>
+      <c r="H24" s="9" t="n">
+        <v>3453</v>
+      </c>
+      <c r="I24" s="7" t="inlineStr">
+        <is>
+          <t>twinPileCap.ts</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="31" customHeight="1">
+      <c r="A25" s="4" t="inlineStr">
         <is>
           <t>III</t>
         </is>
       </c>
-      <c r="B24" s="5" t="inlineStr">
+      <c r="B25" s="5" t="inlineStr">
         <is>
           <t>ĐẾ NEO ĐÁY BTCT + VÍT XOẮN</t>
         </is>
       </c>
-      <c r="C24" s="4" t="n"/>
-      <c r="D24" s="5" t="n"/>
-      <c r="E24" s="4" t="n"/>
-      <c r="F24" s="5" t="n"/>
-      <c r="G24" s="4" t="n"/>
-      <c r="H24" s="5" t="n"/>
-      <c r="I24" s="5" t="n"/>
-    </row>
-    <row r="25" ht="92" customHeight="1">
-      <c r="A25" s="6" t="n">
-        <v>17</v>
-      </c>
-      <c r="B25" s="7" t="inlineStr">
-        <is>
-          <t>Bê tông đế đúc sẵn</t>
-        </is>
-      </c>
-      <c r="C25" s="6" t="n"/>
-      <c r="D25" s="7" t="inlineStr">
-        <is>
-          <t>C25/30 chống thấm; 54 đế 2,50 m, 8 đế 2,75 m, 1 đế 3,00 m, 9 đế 3,25 m, 12 đế 3,50 m, 7 đế 3,75 m, 3 đế 4,00 m, 2 đế 4,25 m, 1 đế 4,50 m, 3 đế 4,75 m, 1 đế 5,00 m; dày 0,4 / 0,5 / 0,6 / 0,8 m</t>
-        </is>
-      </c>
-      <c r="E25" s="6" t="inlineStr">
-        <is>
-          <t>m³</t>
-        </is>
-      </c>
-      <c r="F25" s="8" t="n">
-        <v>405</v>
-      </c>
-      <c r="G25" s="6" t="inlineStr">
-        <is>
-          <t>3%</t>
-        </is>
-      </c>
-      <c r="H25" s="8" t="n">
-        <v>417.2</v>
-      </c>
-      <c r="I25" s="7" t="inlineStr">
-        <is>
-          <t>101 đế, đế nặng nhất 28,7 t khi cẩu</t>
-        </is>
-      </c>
+      <c r="C25" s="4" t="n"/>
+      <c r="D25" s="5" t="n"/>
+      <c r="E25" s="4" t="n"/>
+      <c r="F25" s="5" t="n"/>
+      <c r="G25" s="4" t="n"/>
+      <c r="H25" s="5" t="n"/>
+      <c r="I25" s="5" t="n"/>
     </row>
     <row r="26" ht="92" customHeight="1">
       <c r="A26" s="6" t="n">
@@ -2349,34 +2329,34 @@
       </c>
       <c r="B26" s="7" t="inlineStr">
         <is>
-          <t>Thép bản đế</t>
+          <t>Bê tông đế đúc sẵn</t>
         </is>
       </c>
       <c r="C26" s="6" t="n"/>
       <c r="D26" s="7" t="inlineStr">
         <is>
-          <t>Φ12 a200</t>
+          <t>C25/30 chống thấm; 54 đế 2,50 m, 8 đế 2,75 m, 1 đế 3,00 m, 9 đế 3,25 m, 12 đế 3,50 m, 7 đế 3,75 m, 3 đế 4,00 m, 2 đế 4,25 m, 1 đế 4,50 m, 3 đế 4,75 m, 1 đế 5,00 m; dày 0,4 / 0,5 / 0,6 / 0,8 m</t>
         </is>
       </c>
       <c r="E26" s="6" t="inlineStr">
         <is>
-          <t>kg</t>
-        </is>
-      </c>
-      <c r="F26" s="9" t="n">
-        <v>17935</v>
+          <t>m³</t>
+        </is>
+      </c>
+      <c r="F26" s="8" t="n">
+        <v>405</v>
       </c>
       <c r="G26" s="6" t="inlineStr">
         <is>
           <t>3%</t>
         </is>
       </c>
-      <c r="H26" s="9" t="n">
-        <v>18474</v>
+      <c r="H26" s="8" t="n">
+        <v>417.2</v>
       </c>
       <c r="I26" s="7" t="inlineStr">
         <is>
-          <t>Engine (kiểm tra SV-6)</t>
+          <t>101 đế, đế nặng nhất 28,7 t khi cẩu</t>
         </is>
       </c>
     </row>
@@ -2386,34 +2366,34 @@
       </c>
       <c r="B27" s="7" t="inlineStr">
         <is>
-          <t>Vít xoắn ống thép mạ kẽm</t>
+          <t>Thép bản đế</t>
         </is>
       </c>
       <c r="C27" s="6" t="n"/>
       <c r="D27" s="7" t="inlineStr">
         <is>
-          <t>Ống Ø89×5, ren Ø105, ngàm 3 m; 4 vít/đế</t>
+          <t>Φ12 a200</t>
         </is>
       </c>
       <c r="E27" s="6" t="inlineStr">
         <is>
-          <t>md</t>
-        </is>
-      </c>
-      <c r="F27" s="8" t="n">
-        <v>1506</v>
+          <t>kg</t>
+        </is>
+      </c>
+      <c r="F27" s="9" t="n">
+        <v>17935</v>
       </c>
       <c r="G27" s="6" t="inlineStr">
         <is>
-          <t>5%</t>
-        </is>
-      </c>
-      <c r="H27" s="8" t="n">
-        <v>1581.3</v>
+          <t>3%</t>
+        </is>
+      </c>
+      <c r="H27" s="9" t="n">
+        <v>18474</v>
       </c>
       <c r="I27" s="7" t="inlineStr">
         <is>
-          <t>404 vít</t>
+          <t>Engine (kiểm tra SV-6)</t>
         </is>
       </c>
     </row>
@@ -2423,34 +2403,34 @@
       </c>
       <c r="B28" s="7" t="inlineStr">
         <is>
-          <t>Nắp chụp khóa đầu vít vào đế</t>
+          <t>Vít xoắn ống thép mạ kẽm</t>
         </is>
       </c>
       <c r="C28" s="6" t="n"/>
       <c r="D28" s="7" t="inlineStr">
         <is>
-          <t>Ống lồng Ø114×6 + bản bích chặn</t>
+          <t>Ống Ø89×5, ren Ø105, ngàm 3 m; 4 vít/đế</t>
         </is>
       </c>
       <c r="E28" s="6" t="inlineStr">
         <is>
-          <t>bộ</t>
-        </is>
-      </c>
-      <c r="F28" s="9" t="n">
-        <v>404</v>
+          <t>md</t>
+        </is>
+      </c>
+      <c r="F28" s="8" t="n">
+        <v>1506</v>
       </c>
       <c r="G28" s="6" t="inlineStr">
         <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="H28" s="9" t="n">
-        <v>404</v>
+          <t>5%</t>
+        </is>
+      </c>
+      <c r="H28" s="8" t="n">
+        <v>1581.3</v>
       </c>
       <c r="I28" s="7" t="inlineStr">
         <is>
-          <t>Chưa thiết kế chi tiết</t>
+          <t>404 vít</t>
         </is>
       </c>
     </row>
@@ -2460,13 +2440,13 @@
       </c>
       <c r="B29" s="7" t="inlineStr">
         <is>
-          <t>Tai neo đôi mặt đế</t>
+          <t>Nắp chụp khóa đầu vít vào đế</t>
         </is>
       </c>
       <c r="C29" s="6" t="n"/>
       <c r="D29" s="7" t="inlineStr">
         <is>
-          <t>SS400 t = 25, 2 lỗ chốt Ø40</t>
+          <t>Ống lồng Ø114×6 + bản bích chặn</t>
         </is>
       </c>
       <c r="E29" s="6" t="inlineStr">
@@ -2475,7 +2455,7 @@
         </is>
       </c>
       <c r="F29" s="9" t="n">
-        <v>37</v>
+        <v>404</v>
       </c>
       <c r="G29" s="6" t="inlineStr">
         <is>
@@ -2483,11 +2463,11 @@
         </is>
       </c>
       <c r="H29" s="9" t="n">
-        <v>37</v>
+        <v>404</v>
       </c>
       <c r="I29" s="7" t="inlineStr">
         <is>
-          <t>Mỗi đế 2 dây của 2 bè; CHƯA thiết kế</t>
+          <t>Chưa thiết kế chi tiết</t>
         </is>
       </c>
     </row>
@@ -2497,13 +2477,13 @@
       </c>
       <c r="B30" s="7" t="inlineStr">
         <is>
-          <t>Tai neo đơn mặt đế</t>
+          <t>Tai neo mặt đế (bản mã + tai + thép neo, 1 bộ mỗi dây)</t>
         </is>
       </c>
       <c r="C30" s="6" t="n"/>
       <c r="D30" s="7" t="inlineStr">
         <is>
-          <t>SS400 t = 25, 1 lỗ chốt Ø40</t>
+          <t>Bản mã SS400 400×400×20, tai t = 25 lỗ Ø32 / Ø36 / Ø39, 4Φ22 L = 350–600 móc vào lưới đáy đế; đặt sẵn khi đúc đế</t>
         </is>
       </c>
       <c r="E30" s="6" t="inlineStr">
@@ -2512,19 +2492,19 @@
         </is>
       </c>
       <c r="F30" s="9" t="n">
-        <v>64</v>
+        <v>138</v>
       </c>
       <c r="G30" s="6" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>2%</t>
         </is>
       </c>
       <c r="H30" s="9" t="n">
-        <v>64</v>
+        <v>141</v>
       </c>
       <c r="I30" s="7" t="inlineStr">
         <is>
-          <t>Đế một dây; CHƯA thiết kế</t>
+          <t>37 đế dùng chung có 2 bộ, 64 đế đơn có 1 bộ; tính cho lực lớn nhất của chính dây, cáp dốc tới 73° (có thành phần nhổ); mức sử dụng lớn nhất 0,99</t>
         </is>
       </c>
     </row>
@@ -3280,13 +3260,13 @@
       </c>
       <c r="B53" s="7" t="inlineStr">
         <is>
-          <t>Thép râu ngàm bản nắp Φ25</t>
+          <t>Thép đai xoắn Φ8</t>
         </is>
       </c>
       <c r="C53" s="6" t="n"/>
       <c r="D53" s="7" t="inlineStr">
         <is>
-          <t>CB400-V, 4 thanh L600 mỗi cọc</t>
+          <t>CB240-T, thép cuộn</t>
         </is>
       </c>
       <c r="E53" s="6" t="inlineStr">
@@ -3295,19 +3275,19 @@
         </is>
       </c>
       <c r="F53" s="9" t="n">
-        <v>2035</v>
+        <v>3563</v>
       </c>
       <c r="G53" s="6" t="inlineStr">
         <is>
-          <t>2%</t>
+          <t>5%</t>
         </is>
       </c>
       <c r="H53" s="9" t="n">
-        <v>2076</v>
+        <v>3742</v>
       </c>
       <c r="I53" s="7" t="inlineStr">
         <is>
-          <t>Lấy theo chi tiết của Huổi Vanh (bảng order 15/10)</t>
+          <t>Cọc khoan nhồi (engine)</t>
         </is>
       </c>
     </row>
@@ -3317,13 +3297,13 @@
       </c>
       <c r="B54" s="7" t="inlineStr">
         <is>
-          <t>Thép đai xoắn Φ8</t>
+          <t>Thép bản đế Φ12</t>
         </is>
       </c>
       <c r="C54" s="6" t="n"/>
       <c r="D54" s="7" t="inlineStr">
         <is>
-          <t>CB240-T, thép cuộn</t>
+          <t>CB400-V (lưới đế)</t>
         </is>
       </c>
       <c r="E54" s="6" t="inlineStr">
@@ -3332,35 +3312,39 @@
         </is>
       </c>
       <c r="F54" s="9" t="n">
-        <v>3563</v>
+        <v>17935</v>
       </c>
       <c r="G54" s="6" t="inlineStr">
         <is>
-          <t>5%</t>
+          <t>3%</t>
         </is>
       </c>
       <c r="H54" s="9" t="n">
-        <v>3742</v>
+        <v>18474</v>
       </c>
       <c r="I54" s="7" t="inlineStr">
         <is>
-          <t>Cọc khoan nhồi (engine)</t>
-        </is>
-      </c>
-    </row>
-    <row r="55" ht="92" customHeight="1">
+          <t>Đế BTCT (engine)</t>
+        </is>
+      </c>
+    </row>
+    <row r="55" ht="46" customHeight="1">
       <c r="A55" s="6" t="n">
         <v>43</v>
       </c>
       <c r="B55" s="7" t="inlineStr">
         <is>
-          <t>Thép bản đế Φ12</t>
-        </is>
-      </c>
-      <c r="C55" s="6" t="n"/>
+          <t>Thép ống vít Ø89×5</t>
+        </is>
+      </c>
+      <c r="C55" s="6" t="inlineStr">
+        <is>
+          <t>(chưa có hình)</t>
+        </is>
+      </c>
       <c r="D55" s="7" t="inlineStr">
         <is>
-          <t>CB400-V (lưới đế)</t>
+          <t>Ống thép mạ kẽm nhúng nóng</t>
         </is>
       </c>
       <c r="E55" s="6" t="inlineStr">
@@ -3369,39 +3353,35 @@
         </is>
       </c>
       <c r="F55" s="9" t="n">
-        <v>17935</v>
+        <v>15599</v>
       </c>
       <c r="G55" s="6" t="inlineStr">
         <is>
-          <t>3%</t>
+          <t>5%</t>
         </is>
       </c>
       <c r="H55" s="9" t="n">
-        <v>18474</v>
+        <v>16379</v>
       </c>
       <c r="I55" s="7" t="inlineStr">
         <is>
-          <t>Đế BTCT (engine)</t>
-        </is>
-      </c>
-    </row>
-    <row r="56" ht="46" customHeight="1">
+          <t>10,36 kg/m</t>
+        </is>
+      </c>
+    </row>
+    <row r="56" ht="92" customHeight="1">
       <c r="A56" s="6" t="n">
         <v>44</v>
       </c>
       <c r="B56" s="7" t="inlineStr">
         <is>
-          <t>Thép ống vít Ø89×5</t>
-        </is>
-      </c>
-      <c r="C56" s="6" t="inlineStr">
-        <is>
-          <t>(chưa có hình)</t>
-        </is>
-      </c>
+          <t>Thép tấm bản mã + tai neo (đầu cọc, đài, đế)</t>
+        </is>
+      </c>
+      <c r="C56" s="6" t="n"/>
       <c r="D56" s="7" t="inlineStr">
         <is>
-          <t>Ống thép mạ kẽm nhúng nóng</t>
+          <t>SS400 mạ kẽm nhúng nóng</t>
         </is>
       </c>
       <c r="E56" s="6" t="inlineStr">
@@ -3410,7 +3390,7 @@
         </is>
       </c>
       <c r="F56" s="9" t="n">
-        <v>15599</v>
+        <v>8248</v>
       </c>
       <c r="G56" s="6" t="inlineStr">
         <is>
@@ -3418,11 +3398,11 @@
         </is>
       </c>
       <c r="H56" s="9" t="n">
-        <v>16379</v>
+        <v>8661</v>
       </c>
       <c r="I56" s="7" t="inlineStr">
         <is>
-          <t>10,36 kg/m</t>
+          <t>271 bộ</t>
         </is>
       </c>
     </row>
@@ -3432,13 +3412,13 @@
       </c>
       <c r="B57" s="7" t="inlineStr">
         <is>
-          <t>Thép tấm bản nắp 400×400×20</t>
+          <t>Thép neo bản mã Φ22</t>
         </is>
       </c>
       <c r="C57" s="6" t="n"/>
       <c r="D57" s="7" t="inlineStr">
         <is>
-          <t>SS400 mạ kẽm</t>
+          <t>CB400-V</t>
         </is>
       </c>
       <c r="E57" s="6" t="inlineStr">
@@ -3447,19 +3427,19 @@
         </is>
       </c>
       <c r="F57" s="9" t="n">
-        <v>5526</v>
+        <v>1582</v>
       </c>
       <c r="G57" s="6" t="inlineStr">
         <is>
-          <t>2%</t>
+          <t>3%</t>
         </is>
       </c>
       <c r="H57" s="9" t="n">
-        <v>5637</v>
+        <v>1629</v>
       </c>
       <c r="I57" s="7" t="inlineStr">
         <is>
-          <t>25,1 kg/tấm</t>
+          <t>271 bộ × 4 thanh</t>
         </is>
       </c>
     </row>
@@ -3469,38 +3449,79 @@
       </c>
       <c r="B58" s="7" t="inlineStr">
         <is>
+          <t>Thép đài cọc đôi</t>
+        </is>
+      </c>
+      <c r="C58" s="6" t="inlineStr">
+        <is>
+          <t>(chưa có hình)</t>
+        </is>
+      </c>
+      <c r="D58" s="7" t="inlineStr">
+        <is>
+          <t>CB400-V Φ16, Φ12; CB240-T Φ10</t>
+        </is>
+      </c>
+      <c r="E58" s="6" t="inlineStr">
+        <is>
+          <t>kg</t>
+        </is>
+      </c>
+      <c r="F58" s="9" t="n">
+        <v>3288</v>
+      </c>
+      <c r="G58" s="6" t="inlineStr">
+        <is>
+          <t>5%</t>
+        </is>
+      </c>
+      <c r="H58" s="9" t="n">
+        <v>3453</v>
+      </c>
+      <c r="I58" s="7" t="inlineStr">
+        <is>
+          <t>twinPileCap.ts</t>
+        </is>
+      </c>
+    </row>
+    <row r="59" ht="46" customHeight="1">
+      <c r="A59" s="6" t="n">
+        <v>47</v>
+      </c>
+      <c r="B59" s="7" t="inlineStr">
+        <is>
           <t>TỔNG THÉP HỆ NEO</t>
         </is>
       </c>
-      <c r="C58" s="6" t="inlineStr">
+      <c r="C59" s="6" t="inlineStr">
         <is>
           <t>(chưa có hình)</t>
         </is>
       </c>
-      <c r="D58" s="7" t="inlineStr">
+      <c r="D59" s="7" t="inlineStr">
         <is>
           <t>Thép thanh + thép ống vít + thép tấm bản nắp</t>
         </is>
       </c>
-      <c r="E58" s="6" t="inlineStr">
+      <c r="E59" s="6" t="inlineStr">
         <is>
           <t>kg</t>
         </is>
       </c>
-      <c r="F58" s="9" t="n">
-        <v>79898</v>
-      </c>
-      <c r="G58" s="6" t="inlineStr">
+      <c r="F59" s="9" t="n">
+        <v>85455</v>
+      </c>
+      <c r="G59" s="6" t="inlineStr">
         <is>
           <t>theo từng loại</t>
         </is>
       </c>
-      <c r="H58" s="9" t="n">
-        <v>82606</v>
-      </c>
-      <c r="I58" s="7" t="inlineStr">
-        <is>
-          <t>Chưa gồm tai neo, nắp khóa vít, tấm chia (chưa có kích thước chi tiết)</t>
+      <c r="H59" s="9" t="n">
+        <v>88636</v>
+      </c>
+      <c r="I59" s="7" t="inlineStr">
+        <is>
+          <t>Chưa gồm nắp khóa vít, tấm chia (chưa có kích thước chi tiết)</t>
         </is>
       </c>
     </row>
@@ -3521,7 +3542,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F11"/>
+  <dimension ref="A1:F12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30.83203125" customWidth="1" min="1" max="1"/>
@@ -3542,7 +3563,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Chưa gồm: tai neo đầu cọc, tai neo của đế, nắp khóa vít, tấm chia tam giác, đài cọc đôi (chưa có kích thước chi tiết).</t>
+          <t>Chưa gồm: nắp khóa vít, tấm chia tam giác (chưa có kích thước chi tiết).</t>
         </is>
       </c>
     </row>
@@ -3637,100 +3658,100 @@
     <row r="6">
       <c r="A6" s="11" t="inlineStr">
         <is>
-          <t>Thép râu ngàm bản nắp Φ25</t>
+          <t>Thép đai xoắn Φ8</t>
         </is>
       </c>
       <c r="B6" s="11" t="inlineStr">
         <is>
-          <t>CB400-V, 4 thanh L600 mỗi cọc</t>
+          <t>CB240-T, thép cuộn</t>
         </is>
       </c>
       <c r="C6" s="11" t="n">
-        <v>2035</v>
+        <v>3563</v>
       </c>
       <c r="D6" s="11" t="inlineStr">
         <is>
-          <t>2%</t>
+          <t>5%</t>
         </is>
       </c>
       <c r="E6" s="11" t="n">
-        <v>2076</v>
+        <v>3742</v>
       </c>
       <c r="F6" s="11" t="inlineStr">
         <is>
-          <t>Lấy theo chi tiết của Huổi Vanh (bảng order 15/10)</t>
+          <t>Cọc khoan nhồi (engine)</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="11" t="inlineStr">
         <is>
-          <t>Thép đai xoắn Φ8</t>
+          <t>Thép bản đế Φ12</t>
         </is>
       </c>
       <c r="B7" s="11" t="inlineStr">
         <is>
-          <t>CB240-T, thép cuộn</t>
+          <t>CB400-V (lưới đế)</t>
         </is>
       </c>
       <c r="C7" s="11" t="n">
-        <v>3563</v>
+        <v>17935</v>
       </c>
       <c r="D7" s="11" t="inlineStr">
         <is>
-          <t>5%</t>
+          <t>3%</t>
         </is>
       </c>
       <c r="E7" s="11" t="n">
-        <v>3742</v>
+        <v>18474</v>
       </c>
       <c r="F7" s="11" t="inlineStr">
         <is>
-          <t>Cọc khoan nhồi (engine)</t>
+          <t>Đế BTCT (engine)</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="11" t="inlineStr">
         <is>
-          <t>Thép bản đế Φ12</t>
+          <t>Thép ống vít Ø89×5</t>
         </is>
       </c>
       <c r="B8" s="11" t="inlineStr">
         <is>
-          <t>CB400-V (lưới đế)</t>
+          <t>Ống thép mạ kẽm nhúng nóng</t>
         </is>
       </c>
       <c r="C8" s="11" t="n">
-        <v>17935</v>
+        <v>15599</v>
       </c>
       <c r="D8" s="11" t="inlineStr">
         <is>
-          <t>3%</t>
+          <t>5%</t>
         </is>
       </c>
       <c r="E8" s="11" t="n">
-        <v>18474</v>
+        <v>16379</v>
       </c>
       <c r="F8" s="11" t="inlineStr">
         <is>
-          <t>Đế BTCT (engine)</t>
+          <t>10,36 kg/m</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="11" t="inlineStr">
         <is>
-          <t>Thép ống vít Ø89×5</t>
+          <t>Thép tấm bản mã + tai neo (đầu cọc, đài, đế)</t>
         </is>
       </c>
       <c r="B9" s="11" t="inlineStr">
         <is>
-          <t>Ống thép mạ kẽm nhúng nóng</t>
+          <t>SS400 mạ kẽm nhúng nóng</t>
         </is>
       </c>
       <c r="C9" s="11" t="n">
-        <v>15599</v>
+        <v>8248</v>
       </c>
       <c r="D9" s="11" t="inlineStr">
         <is>
@@ -3738,57 +3759,85 @@
         </is>
       </c>
       <c r="E9" s="11" t="n">
-        <v>16379</v>
+        <v>8661</v>
       </c>
       <c r="F9" s="11" t="inlineStr">
         <is>
-          <t>10,36 kg/m</t>
+          <t>271 bộ</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="11" t="inlineStr">
         <is>
-          <t>Thép tấm bản nắp 400×400×20</t>
+          <t>Thép neo bản mã Φ22</t>
         </is>
       </c>
       <c r="B10" s="11" t="inlineStr">
         <is>
-          <t>SS400 mạ kẽm</t>
+          <t>CB400-V</t>
         </is>
       </c>
       <c r="C10" s="11" t="n">
-        <v>5526</v>
+        <v>1582</v>
       </c>
       <c r="D10" s="11" t="inlineStr">
         <is>
-          <t>2%</t>
+          <t>3%</t>
         </is>
       </c>
       <c r="E10" s="11" t="n">
-        <v>5637</v>
+        <v>1629</v>
       </c>
       <c r="F10" s="11" t="inlineStr">
         <is>
-          <t>25,1 kg/tấm</t>
+          <t>271 bộ × 4 thanh</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="11" t="inlineStr">
         <is>
+          <t>Thép đài cọc đôi</t>
+        </is>
+      </c>
+      <c r="B11" s="11" t="inlineStr">
+        <is>
+          <t>CB400-V Φ16, Φ12; CB240-T Φ10</t>
+        </is>
+      </c>
+      <c r="C11" s="11" t="n">
+        <v>3288</v>
+      </c>
+      <c r="D11" s="11" t="inlineStr">
+        <is>
+          <t>5%</t>
+        </is>
+      </c>
+      <c r="E11" s="11" t="n">
+        <v>3453</v>
+      </c>
+      <c r="F11" s="11" t="inlineStr">
+        <is>
+          <t>twinPileCap.ts</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="11" t="inlineStr">
+        <is>
           <t>TỔNG</t>
         </is>
       </c>
-      <c r="B11" s="11" t="str"/>
-      <c r="C11" s="11" t="n">
-        <v>79898</v>
-      </c>
-      <c r="D11" s="11" t="str"/>
-      <c r="E11" s="11" t="n">
-        <v>82606</v>
-      </c>
-      <c r="F11" s="11" t="str"/>
+      <c r="B12" s="11" t="str"/>
+      <c r="C12" s="11" t="n">
+        <v>85455</v>
+      </c>
+      <c r="D12" s="11" t="str"/>
+      <c r="E12" s="11" t="n">
+        <v>88636</v>
+      </c>
+      <c r="F12" s="11" t="str"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -31671,6 +31720,1018 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:R19"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="16.83203125" customWidth="1" min="1" max="1"/>
+    <col width="8.83203125" customWidth="1" min="2" max="2"/>
+    <col width="7.83203125" customWidth="1" min="3" max="3"/>
+    <col width="8.83203125" customWidth="1" min="4" max="4"/>
+    <col width="9.83203125" customWidth="1" min="5" max="5"/>
+    <col width="10.83203125" customWidth="1" min="6" max="6"/>
+    <col width="9.83203125" customWidth="1" min="7" max="7"/>
+    <col width="10.83203125" customWidth="1" min="8" max="8"/>
+    <col width="7.83203125" customWidth="1" min="9" max="9"/>
+    <col width="7.83203125" customWidth="1" min="10" max="10"/>
+    <col width="7.83203125" customWidth="1" min="11" max="11"/>
+    <col width="7.83203125" customWidth="1" min="12" max="12"/>
+    <col width="7.83203125" customWidth="1" min="13" max="13"/>
+    <col width="7.83203125" customWidth="1" min="14" max="14"/>
+    <col width="7.83203125" customWidth="1" min="15" max="15"/>
+    <col width="7.83203125" customWidth="1" min="16" max="16"/>
+    <col width="7.83203125" customWidth="1" min="17" max="17"/>
+    <col width="7.83203125" customWidth="1" min="18" max="18"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="10" t="inlineStr">
+        <is>
+          <t>KIỂM TRA ĐẦU CỌC, ĐÀI CỌC ĐÔI, TAI NEO MẶT ĐẾ (thiết kế sơ bộ, γ = 1.2)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Mức sử dụng = tải / khả năng; ≤ 1 là đạt. H-1…H-7: shorePileHead.ts (ma-nê, ép mặt, xé mép, hàn, thép neo, chiều dài neo); TC-1…TC-4: twinPileCap.ts. Mỗi dòng là một nhóm giống nhau (cùng bè, cùng loại).</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="48" customHeight="1">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>Loại</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>Bè</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>Số bộ</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>T (kN)</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
+          <t>Góc cáp (°)</t>
+        </is>
+      </c>
+      <c r="F3" s="3" t="inlineStr">
+        <is>
+          <t>Ma-nê WLL (t)</t>
+        </is>
+      </c>
+      <c r="G3" s="3" t="inlineStr">
+        <is>
+          <t>Lỗ chốt (mm)</t>
+        </is>
+      </c>
+      <c r="H3" s="3" t="inlineStr">
+        <is>
+          <t>Thép neo L (mm)</t>
+        </is>
+      </c>
+      <c r="I3" s="3" t="inlineStr">
+        <is>
+          <t>H-1</t>
+        </is>
+      </c>
+      <c r="J3" s="3" t="inlineStr">
+        <is>
+          <t>H-3</t>
+        </is>
+      </c>
+      <c r="K3" s="3" t="inlineStr">
+        <is>
+          <t>H-4</t>
+        </is>
+      </c>
+      <c r="L3" s="3" t="inlineStr">
+        <is>
+          <t>H-5</t>
+        </is>
+      </c>
+      <c r="M3" s="3" t="inlineStr">
+        <is>
+          <t>H-6</t>
+        </is>
+      </c>
+      <c r="N3" s="3" t="inlineStr">
+        <is>
+          <t>H-7</t>
+        </is>
+      </c>
+      <c r="O3" s="3" t="inlineStr">
+        <is>
+          <t>TC-1</t>
+        </is>
+      </c>
+      <c r="P3" s="3" t="inlineStr">
+        <is>
+          <t>TC-2</t>
+        </is>
+      </c>
+      <c r="Q3" s="3" t="inlineStr">
+        <is>
+          <t>TC-3</t>
+        </is>
+      </c>
+      <c r="R3" s="3" t="inlineStr">
+        <is>
+          <t>TC-4</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="11" t="inlineStr">
+        <is>
+          <t>Đài cọc đôi</t>
+        </is>
+      </c>
+      <c r="B4" s="11" t="inlineStr">
+        <is>
+          <t>BÈ 1</t>
+        </is>
+      </c>
+      <c r="C4" s="11" t="n">
+        <v>19</v>
+      </c>
+      <c r="D4" s="11" t="n">
+        <v>104.9</v>
+      </c>
+      <c r="E4" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="F4" s="11" t="n">
+        <v>12</v>
+      </c>
+      <c r="G4" s="11" t="n">
+        <v>39</v>
+      </c>
+      <c r="H4" s="11" t="n">
+        <v>600</v>
+      </c>
+      <c r="I4" s="11" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="J4" s="11" t="n">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="K4" s="11" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="L4" s="11" t="n">
+        <v>0.51</v>
+      </c>
+      <c r="M4" s="11" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="N4" s="11" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="O4" s="11" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="P4" s="11" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="Q4" s="11" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="R4" s="11" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="11" t="inlineStr">
+        <is>
+          <t>Tai neo mặt đế</t>
+        </is>
+      </c>
+      <c r="B5" s="11" t="inlineStr">
+        <is>
+          <t>BÈ 1</t>
+        </is>
+      </c>
+      <c r="C5" s="11" t="n">
+        <v>16</v>
+      </c>
+      <c r="D5" s="11" t="n">
+        <v>82.59999999999999</v>
+      </c>
+      <c r="E5" s="11" t="n">
+        <v>45</v>
+      </c>
+      <c r="F5" s="11" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="G5" s="11" t="n">
+        <v>32</v>
+      </c>
+      <c r="H5" s="11" t="n">
+        <v>350</v>
+      </c>
+      <c r="I5" s="11" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="J5" s="11" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="K5" s="11" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="L5" s="11" t="n">
+        <v>0.61</v>
+      </c>
+      <c r="M5" s="11" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="N5" s="11" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="O5" s="11" t="str"/>
+      <c r="P5" s="11" t="str"/>
+      <c r="Q5" s="11" t="str"/>
+      <c r="R5" s="11" t="str"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="11" t="inlineStr">
+        <is>
+          <t>Đầu cọc đơn</t>
+        </is>
+      </c>
+      <c r="B6" s="11" t="inlineStr">
+        <is>
+          <t>BÈ 2</t>
+        </is>
+      </c>
+      <c r="C6" s="11" t="n">
+        <v>25</v>
+      </c>
+      <c r="D6" s="11" t="n">
+        <v>73.7</v>
+      </c>
+      <c r="E6" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="F6" s="11" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="G6" s="11" t="n">
+        <v>32</v>
+      </c>
+      <c r="H6" s="11" t="n">
+        <v>600</v>
+      </c>
+      <c r="I6" s="11" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="J6" s="11" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="K6" s="11" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="L6" s="11" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="M6" s="11" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="N6" s="11" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="O6" s="11" t="str"/>
+      <c r="P6" s="11" t="str"/>
+      <c r="Q6" s="11" t="str"/>
+      <c r="R6" s="11" t="str"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="11" t="inlineStr">
+        <is>
+          <t>Tai neo mặt đế</t>
+        </is>
+      </c>
+      <c r="B7" s="11" t="inlineStr">
+        <is>
+          <t>BÈ 2</t>
+        </is>
+      </c>
+      <c r="C7" s="11" t="n">
+        <v>10</v>
+      </c>
+      <c r="D7" s="11" t="n">
+        <v>58.9</v>
+      </c>
+      <c r="E7" s="11" t="n">
+        <v>54</v>
+      </c>
+      <c r="F7" s="11" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="G7" s="11" t="n">
+        <v>32</v>
+      </c>
+      <c r="H7" s="11" t="n">
+        <v>350</v>
+      </c>
+      <c r="I7" s="11" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="J7" s="11" t="n">
+        <v>0.48</v>
+      </c>
+      <c r="K7" s="11" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="L7" s="11" t="n">
+        <v>0.39</v>
+      </c>
+      <c r="M7" s="11" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="N7" s="11" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="O7" s="11" t="str"/>
+      <c r="P7" s="11" t="str"/>
+      <c r="Q7" s="11" t="str"/>
+      <c r="R7" s="11" t="str"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="11" t="inlineStr">
+        <is>
+          <t>Đài cọc đôi</t>
+        </is>
+      </c>
+      <c r="B8" s="11" t="inlineStr">
+        <is>
+          <t>BÈ 3</t>
+        </is>
+      </c>
+      <c r="C8" s="11" t="n">
+        <v>17</v>
+      </c>
+      <c r="D8" s="11" t="n">
+        <v>106.9</v>
+      </c>
+      <c r="E8" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="F8" s="11" t="n">
+        <v>12</v>
+      </c>
+      <c r="G8" s="11" t="n">
+        <v>39</v>
+      </c>
+      <c r="H8" s="11" t="n">
+        <v>600</v>
+      </c>
+      <c r="I8" s="11" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="J8" s="11" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="K8" s="11" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="L8" s="11" t="n">
+        <v>0.52</v>
+      </c>
+      <c r="M8" s="11" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="N8" s="11" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="O8" s="11" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="P8" s="11" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="Q8" s="11" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="R8" s="11" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="11" t="inlineStr">
+        <is>
+          <t>Tai neo mặt đế</t>
+        </is>
+      </c>
+      <c r="B9" s="11" t="inlineStr">
+        <is>
+          <t>BÈ 3</t>
+        </is>
+      </c>
+      <c r="C9" s="11" t="n">
+        <v>26</v>
+      </c>
+      <c r="D9" s="11" t="n">
+        <v>82.5</v>
+      </c>
+      <c r="E9" s="11" t="n">
+        <v>49</v>
+      </c>
+      <c r="F9" s="11" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="G9" s="11" t="n">
+        <v>32</v>
+      </c>
+      <c r="H9" s="11" t="n">
+        <v>350</v>
+      </c>
+      <c r="I9" s="11" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="J9" s="11" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="K9" s="11" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="L9" s="11" t="n">
+        <v>0.59</v>
+      </c>
+      <c r="M9" s="11" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="N9" s="11" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="O9" s="11" t="str"/>
+      <c r="P9" s="11" t="str"/>
+      <c r="Q9" s="11" t="str"/>
+      <c r="R9" s="11" t="str"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="11" t="inlineStr">
+        <is>
+          <t>Đài cọc đôi</t>
+        </is>
+      </c>
+      <c r="B10" s="11" t="inlineStr">
+        <is>
+          <t>BÈ 4</t>
+        </is>
+      </c>
+      <c r="C10" s="11" t="n">
+        <v>16</v>
+      </c>
+      <c r="D10" s="11" t="n">
+        <v>94.59999999999999</v>
+      </c>
+      <c r="E10" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="F10" s="11" t="n">
+        <v>12</v>
+      </c>
+      <c r="G10" s="11" t="n">
+        <v>39</v>
+      </c>
+      <c r="H10" s="11" t="n">
+        <v>600</v>
+      </c>
+      <c r="I10" s="11" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="J10" s="11" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="K10" s="11" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="L10" s="11" t="n">
+        <v>0.46</v>
+      </c>
+      <c r="M10" s="11" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="N10" s="11" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="O10" s="11" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="P10" s="11" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="Q10" s="11" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="R10" s="11" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="11" t="inlineStr">
+        <is>
+          <t>Tai neo mặt đế</t>
+        </is>
+      </c>
+      <c r="B11" s="11" t="inlineStr">
+        <is>
+          <t>BÈ 4</t>
+        </is>
+      </c>
+      <c r="C11" s="11" t="n">
+        <v>21</v>
+      </c>
+      <c r="D11" s="11" t="n">
+        <v>70.09999999999999</v>
+      </c>
+      <c r="E11" s="11" t="n">
+        <v>55</v>
+      </c>
+      <c r="F11" s="11" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="G11" s="11" t="n">
+        <v>32</v>
+      </c>
+      <c r="H11" s="11" t="n">
+        <v>350</v>
+      </c>
+      <c r="I11" s="11" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="J11" s="11" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="K11" s="11" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="L11" s="11" t="n">
+        <v>0.46</v>
+      </c>
+      <c r="M11" s="11" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="N11" s="11" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="O11" s="11" t="str"/>
+      <c r="P11" s="11" t="str"/>
+      <c r="Q11" s="11" t="str"/>
+      <c r="R11" s="11" t="str"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="11" t="inlineStr">
+        <is>
+          <t>Đầu cọc đơn</t>
+        </is>
+      </c>
+      <c r="B12" s="11" t="inlineStr">
+        <is>
+          <t>BÈ 5</t>
+        </is>
+      </c>
+      <c r="C12" s="11" t="n">
+        <v>18</v>
+      </c>
+      <c r="D12" s="11" t="n">
+        <v>75</v>
+      </c>
+      <c r="E12" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="F12" s="11" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="G12" s="11" t="n">
+        <v>32</v>
+      </c>
+      <c r="H12" s="11" t="n">
+        <v>600</v>
+      </c>
+      <c r="I12" s="11" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="J12" s="11" t="n">
+        <v>0.61</v>
+      </c>
+      <c r="K12" s="11" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="L12" s="11" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="M12" s="11" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="N12" s="11" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="O12" s="11" t="str"/>
+      <c r="P12" s="11" t="str"/>
+      <c r="Q12" s="11" t="str"/>
+      <c r="R12" s="11" t="str"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="11" t="inlineStr">
+        <is>
+          <t>Tai neo mặt đế</t>
+        </is>
+      </c>
+      <c r="B13" s="11" t="inlineStr">
+        <is>
+          <t>BÈ 5</t>
+        </is>
+      </c>
+      <c r="C13" s="11" t="n">
+        <v>3</v>
+      </c>
+      <c r="D13" s="11" t="n">
+        <v>75</v>
+      </c>
+      <c r="E13" s="11" t="n">
+        <v>40</v>
+      </c>
+      <c r="F13" s="11" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="G13" s="11" t="n">
+        <v>32</v>
+      </c>
+      <c r="H13" s="11" t="n">
+        <v>350</v>
+      </c>
+      <c r="I13" s="11" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="J13" s="11" t="n">
+        <v>0.61</v>
+      </c>
+      <c r="K13" s="11" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="L13" s="11" t="n">
+        <v>0.58</v>
+      </c>
+      <c r="M13" s="11" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="N13" s="11" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="O13" s="11" t="str"/>
+      <c r="P13" s="11" t="str"/>
+      <c r="Q13" s="11" t="str"/>
+      <c r="R13" s="11" t="str"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="11" t="inlineStr">
+        <is>
+          <t>Đầu cọc đơn</t>
+        </is>
+      </c>
+      <c r="B14" s="11" t="inlineStr">
+        <is>
+          <t>BÈ 6</t>
+        </is>
+      </c>
+      <c r="C14" s="11" t="n">
+        <v>3</v>
+      </c>
+      <c r="D14" s="11" t="n">
+        <v>54.9</v>
+      </c>
+      <c r="E14" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="F14" s="11" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="G14" s="11" t="n">
+        <v>32</v>
+      </c>
+      <c r="H14" s="11" t="n">
+        <v>600</v>
+      </c>
+      <c r="I14" s="11" t="n">
+        <v>0.66</v>
+      </c>
+      <c r="J14" s="11" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="K14" s="11" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="L14" s="11" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="M14" s="11" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="N14" s="11" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="O14" s="11" t="str"/>
+      <c r="P14" s="11" t="str"/>
+      <c r="Q14" s="11" t="str"/>
+      <c r="R14" s="11" t="str"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="11" t="inlineStr">
+        <is>
+          <t>Tai neo mặt đế</t>
+        </is>
+      </c>
+      <c r="B15" s="11" t="inlineStr">
+        <is>
+          <t>BÈ 6</t>
+        </is>
+      </c>
+      <c r="C15" s="11" t="n">
+        <v>24</v>
+      </c>
+      <c r="D15" s="11" t="n">
+        <v>37.3</v>
+      </c>
+      <c r="E15" s="11" t="n">
+        <v>36</v>
+      </c>
+      <c r="F15" s="11" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="G15" s="11" t="n">
+        <v>32</v>
+      </c>
+      <c r="H15" s="11" t="n">
+        <v>350</v>
+      </c>
+      <c r="I15" s="11" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="J15" s="11" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="K15" s="11" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="L15" s="11" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="M15" s="11" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="N15" s="11" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="O15" s="11" t="str"/>
+      <c r="P15" s="11" t="str"/>
+      <c r="Q15" s="11" t="str"/>
+      <c r="R15" s="11" t="str"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="11" t="inlineStr">
+        <is>
+          <t>Đài cọc đôi</t>
+        </is>
+      </c>
+      <c r="B16" s="11" t="inlineStr">
+        <is>
+          <t>BÈ 7</t>
+        </is>
+      </c>
+      <c r="C16" s="11" t="n">
+        <v>20</v>
+      </c>
+      <c r="D16" s="11" t="n">
+        <v>107</v>
+      </c>
+      <c r="E16" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="F16" s="11" t="n">
+        <v>12</v>
+      </c>
+      <c r="G16" s="11" t="n">
+        <v>39</v>
+      </c>
+      <c r="H16" s="11" t="n">
+        <v>600</v>
+      </c>
+      <c r="I16" s="11" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="J16" s="11" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="K16" s="11" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="L16" s="11" t="n">
+        <v>0.52</v>
+      </c>
+      <c r="M16" s="11" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="N16" s="11" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="O16" s="11" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="P16" s="11" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="Q16" s="11" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="R16" s="11" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="11" t="inlineStr">
+        <is>
+          <t>Tai neo mặt đế</t>
+        </is>
+      </c>
+      <c r="B17" s="11" t="inlineStr">
+        <is>
+          <t>BÈ 7</t>
+        </is>
+      </c>
+      <c r="C17" s="11" t="n">
+        <v>20</v>
+      </c>
+      <c r="D17" s="11" t="n">
+        <v>82.7</v>
+      </c>
+      <c r="E17" s="11" t="n">
+        <v>45</v>
+      </c>
+      <c r="F17" s="11" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="G17" s="11" t="n">
+        <v>32</v>
+      </c>
+      <c r="H17" s="11" t="n">
+        <v>350</v>
+      </c>
+      <c r="I17" s="11" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="J17" s="11" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="K17" s="11" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="L17" s="11" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="M17" s="11" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="N17" s="11" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="O17" s="11" t="str"/>
+      <c r="P17" s="11" t="str"/>
+      <c r="Q17" s="11" t="str"/>
+      <c r="R17" s="11" t="str"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="11" t="inlineStr">
+        <is>
+          <t>Đài cọc đôi</t>
+        </is>
+      </c>
+      <c r="B18" s="11" t="inlineStr">
+        <is>
+          <t>BÈ 8</t>
+        </is>
+      </c>
+      <c r="C18" s="11" t="n">
+        <v>15</v>
+      </c>
+      <c r="D18" s="11" t="n">
+        <v>94</v>
+      </c>
+      <c r="E18" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="F18" s="11" t="n">
+        <v>12</v>
+      </c>
+      <c r="G18" s="11" t="n">
+        <v>39</v>
+      </c>
+      <c r="H18" s="11" t="n">
+        <v>600</v>
+      </c>
+      <c r="I18" s="11" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="J18" s="11" t="n">
+        <v>0.61</v>
+      </c>
+      <c r="K18" s="11" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="L18" s="11" t="n">
+        <v>0.46</v>
+      </c>
+      <c r="M18" s="11" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="N18" s="11" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="O18" s="11" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="P18" s="11" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="Q18" s="11" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="R18" s="11" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="11" t="inlineStr">
+        <is>
+          <t>Tai neo mặt đế</t>
+        </is>
+      </c>
+      <c r="B19" s="11" t="inlineStr">
+        <is>
+          <t>BÈ 8</t>
+        </is>
+      </c>
+      <c r="C19" s="11" t="n">
+        <v>18</v>
+      </c>
+      <c r="D19" s="11" t="n">
+        <v>92.3</v>
+      </c>
+      <c r="E19" s="11" t="n">
+        <v>46</v>
+      </c>
+      <c r="F19" s="11" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="G19" s="11" t="n">
+        <v>36</v>
+      </c>
+      <c r="H19" s="11" t="n">
+        <v>350</v>
+      </c>
+      <c r="I19" s="11" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="J19" s="11" t="n">
+        <v>0.66</v>
+      </c>
+      <c r="K19" s="11" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="L19" s="11" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="M19" s="11" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="N19" s="11" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="O19" s="11" t="str"/>
+      <c r="P19" s="11" t="str"/>
+      <c r="Q19" s="11" t="str"/>
+      <c r="R19" s="11" t="str"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:B11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -31742,7 +32803,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Bản nắp, tai neo, râu thép đầu cọc và nắp khóa vít, tai neo của đế lấy theo bảng order ngày 15/10 của Huổi Vanh — CHƯA có bản vẽ / tính toán chi tiết.</t>
+          <t>Đầu cọc, đài cọc đôi và tai neo mặt đế là THIẾT KẾ SƠ BỘ của web (shorePileHead.ts, twinPileCap.ts: ma-nê, ép mặt, xé mép lỗ, đường hàn, thép neo kéo + cắt, chiều dài neo, uốn / cắt / xoắn của đài) cho γ·T, T là lực lớn nhất của bè (đầu cọc) hoặc của chính dây (đế); bản vẽ chế tạo phải được kỹ sư kết cấu lập và kiểm tra. Nắp khóa vít vẫn CHƯA thiết kế.</t>
         </is>
       </c>
     </row>
@@ -31766,7 +32827,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>87 điểm neo bờ dùng cọc đôi (220 cọc / 133 điểm); đài nối đầu cọc đôi CHƯA thiết kế. 64/101 đế là đế một dây ở vùng nước trống; đế nặng nhất 28,7 t — cần sà lan / cẩu phù hợp.</t>
+          <t>87 điểm neo bờ dùng cọc đôi (220 cọc / 133 điểm); đài nối đầu cọc đôi: thiết kế sơ bộ ở mục II. 64/101 đế là đế một dây ở vùng nước trống; đế nặng nhất 28,7 t — cần sà lan / cẩu phù hợp.</t>
         </is>
       </c>
     </row>
@@ -31778,7 +32839,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Mặt bằng bè theo bản vẽ "221026 BỐ TRÍ BÈ PIN HỒ BẢN MÒNG" (đường bao tờ MB-B01-01; so với PA2 19/10 chỉ BÈ 4 và BÈ 6 đổi hình), số tấm pin từng bè theo bảng các tờ CT-BP (18.240 tấm). Vị trí dây, cọc, đế là thiết kế của web (scripts/planMooringLayoutV2.mjs), CHƯA khảo sát.</t>
+          <t>Mặt bằng bè theo bản vẽ "221026 BỐ TRÍ BÈ PIN HỒ BẢN MÒNG" (đường bao tờ MB-B01-01; so với PA2 19/10 chỉ BÈ 4 và BÈ 6 đổi hình), số tấm pin từng bè theo bảng các tờ CT-BP — ĐÃ CHỐT 18.240 tấm (Chủ đầu tư 22/10/2026). Vị trí dây, cọc, đế là thiết kế của web (scripts/planMooringLayoutV2.mjs), CHƯA khảo sát.</t>
         </is>
       </c>
     </row>

--- a/public/docs_ban_mong/HOBANMONG_THONG_KE_VAT_TU_NEO.xlsx
+++ b/public/docs_ban_mong/HOBANMONG_THONG_KE_VAT_TU_NEO.xlsx
@@ -1071,7 +1071,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>50</row>
+      <row>51</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="1490133" cy="1117600"/>
@@ -1096,7 +1096,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>51</row>
+      <row>52</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="1490133" cy="1117600"/>
@@ -1121,7 +1121,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>52</row>
+      <row>53</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="1490133" cy="1117600"/>
@@ -1146,7 +1146,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>53</row>
+      <row>54</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="1490133" cy="1117600"/>
@@ -1171,7 +1171,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>55</row>
+      <row>56</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="1490133" cy="1117600"/>
@@ -1196,7 +1196,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>56</row>
+      <row>57</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="1490133" cy="1117600"/>
@@ -1546,7 +1546,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I59"/>
+  <dimension ref="A1:I60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6.8" customWidth="1" min="1" max="1"/>
@@ -3109,7 +3109,7 @@
       </c>
       <c r="B48" s="5" t="inlineStr">
         <is>
-          <t>THIẾT BỊ BÙ DAO ĐỘNG MỰC NƯỚC (BẮT BUỘC, CHƯA THIẾT KẾ — KHÔNG ĐẶT HÀNG THEO MỤC NÀY)</t>
+          <t>THIẾT BỊ BÙ DAO ĐỘNG MỰC NƯỚC (BẮT BUỘC — CHỈ MỚI CÓ YÊU CẦU KỸ THUẬT, CHƯA CHỌN LOẠI: KHÔNG ĐẶT HÀNG THEO MỤC NÀY)</t>
         </is>
       </c>
       <c r="C48" s="4" t="n"/>
@@ -3126,7 +3126,7 @@
       </c>
       <c r="B49" s="7" t="inlineStr">
         <is>
-          <t>Thiết bị bù dao động mực nước mỗi dây</t>
+          <t>Bộ tự căng / thu xả cáp mỗi dây (đối trọng hoặc tời)</t>
         </is>
       </c>
       <c r="C49" s="6" t="inlineStr">
@@ -3136,7 +3136,7 @@
       </c>
       <c r="D49" s="7" t="inlineStr">
         <is>
-          <t>Đối trọng treo / bộ tự căng giữ dây vừa căng ở mọi mực nước (649,50–669,05 m); hành trình thu–xả: dây đáy tới 15,9 m, dây bờ tới 4,6 m; phải KHÓA được khi bão</t>
+          <t>Giữ lực căng đặt 5 kN ở mọi mực nước 649,50–669,05 m; hành trình thu–xả: dây đáy 15,9 m, dây bờ 4,6 m, cộng 3 m dư mỗi chiều</t>
         </is>
       </c>
       <c r="E49" s="6" t="inlineStr">
@@ -3149,7 +3149,7 @@
       </c>
       <c r="G49" s="6" t="inlineStr">
         <is>
-          <t>CHƯA thiết kế</t>
+          <t>CHƯA chọn loại</t>
         </is>
       </c>
       <c r="H49" s="9" t="n">
@@ -3157,65 +3157,69 @@
       </c>
       <c r="I49" s="7" t="inlineStr">
         <is>
-          <t>Lực dây 54,9–107,0 kN của engine CHỈ đúng khi có thiết bị này (cáp cắt cố định thì không cáp PES nào đủ — bảng so sánh ở Mục 4 trên web). Pre-FS gợi ý phao chỉ hướng ~2,5 t</t>
-        </is>
-      </c>
-    </row>
-    <row r="50" ht="31" customHeight="1">
-      <c r="A50" s="4" t="inlineStr">
+          <t>Yêu cầu của mô hình cân bằng (mooringEquilibrium.ts): dây luôn vừa căng ở mọi mực nước. Đối trọng treo một mình KHÔNG giữ được bè: nếu không khóa, bè trôi 5,1–6,3 m hết hành trình dư rồi lực dây vọt tới 108–296 kN</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" ht="46" customHeight="1">
+      <c r="A50" s="6" t="n">
+        <v>39</v>
+      </c>
+      <c r="B50" s="7" t="inlineStr">
+        <is>
+          <t>Bộ khóa / phanh cáp chống bão mỗi dây (fail-safe)</t>
+        </is>
+      </c>
+      <c r="C50" s="6" t="inlineStr">
+        <is>
+          <t>(chưa có hình)</t>
+        </is>
+      </c>
+      <c r="D50" s="7" t="inlineStr">
+        <is>
+          <t>Khóa cáp khi gió vượt ngưỡng, giữ tới lực đứt của cáp chính (PES-28: 235 kN; PES-32: 305 kN; PES-36: 385 kN) để khóa không yếu hơn cáp; mất điện / mất tín hiệu thì tự khóa (lò xo ép phanh)</t>
+        </is>
+      </c>
+      <c r="E50" s="6" t="inlineStr">
+        <is>
+          <t>bộ</t>
+        </is>
+      </c>
+      <c r="F50" s="9" t="n">
+        <v>271</v>
+      </c>
+      <c r="G50" s="6" t="inlineStr">
+        <is>
+          <t>CHƯA chọn loại</t>
+        </is>
+      </c>
+      <c r="H50" s="9" t="n">
+        <v>271</v>
+      </c>
+      <c r="I50" s="7" t="inlineStr">
+        <is>
+          <t>Lực dây, đế, cọc của bảng này chỉ đúng khi khóa làm việc. Cần: tín hiệu gió + dự phòng, kiểm tra định kỳ, thử tải; khóa hỏng thì hệ số an toàn cáp chỉ còn 1,3–2,8 (xem cảnh báo ở Header). Pre-FS gợi ý phao chỉ hướng ~2,5 t — chưa đánh giá</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" ht="31" customHeight="1">
+      <c r="A51" s="4" t="inlineStr">
         <is>
           <t>VII</t>
         </is>
       </c>
-      <c r="B50" s="5" t="inlineStr">
+      <c r="B51" s="5" t="inlineStr">
         <is>
           <t>TỔNG THÉP HỆ NEO (chi tiết theo đường kính: sheet TongHop_Thep)</t>
         </is>
       </c>
-      <c r="C50" s="4" t="n"/>
-      <c r="D50" s="5" t="n"/>
-      <c r="E50" s="4" t="n"/>
-      <c r="F50" s="5" t="n"/>
-      <c r="G50" s="4" t="n"/>
-      <c r="H50" s="5" t="n"/>
-      <c r="I50" s="5" t="n"/>
-    </row>
-    <row r="51" ht="92" customHeight="1">
-      <c r="A51" s="6" t="n">
-        <v>39</v>
-      </c>
-      <c r="B51" s="7" t="inlineStr">
-        <is>
-          <t>Thép chủ cọc Φ25</t>
-        </is>
-      </c>
-      <c r="C51" s="6" t="n"/>
-      <c r="D51" s="7" t="inlineStr">
-        <is>
-          <t>CB400-V, thanh vằn</t>
-        </is>
-      </c>
-      <c r="E51" s="6" t="inlineStr">
-        <is>
-          <t>kg</t>
-        </is>
-      </c>
-      <c r="F51" s="9" t="n">
-        <v>27009</v>
-      </c>
-      <c r="G51" s="6" t="inlineStr">
-        <is>
-          <t>3%</t>
-        </is>
-      </c>
-      <c r="H51" s="9" t="n">
-        <v>27820</v>
-      </c>
-      <c r="I51" s="7" t="inlineStr">
-        <is>
-          <t>Lồng thép cọc khoan nhồi (engine)</t>
-        </is>
-      </c>
+      <c r="C51" s="4" t="n"/>
+      <c r="D51" s="5" t="n"/>
+      <c r="E51" s="4" t="n"/>
+      <c r="F51" s="5" t="n"/>
+      <c r="G51" s="4" t="n"/>
+      <c r="H51" s="5" t="n"/>
+      <c r="I51" s="5" t="n"/>
     </row>
     <row r="52" ht="92" customHeight="1">
       <c r="A52" s="6" t="n">
@@ -3223,7 +3227,7 @@
       </c>
       <c r="B52" s="7" t="inlineStr">
         <is>
-          <t>Thép chủ cọc Φ28</t>
+          <t>Thép chủ cọc Φ25</t>
         </is>
       </c>
       <c r="C52" s="6" t="n"/>
@@ -3238,7 +3242,7 @@
         </is>
       </c>
       <c r="F52" s="9" t="n">
-        <v>8231</v>
+        <v>27009</v>
       </c>
       <c r="G52" s="6" t="inlineStr">
         <is>
@@ -3246,7 +3250,7 @@
         </is>
       </c>
       <c r="H52" s="9" t="n">
-        <v>8478</v>
+        <v>27820</v>
       </c>
       <c r="I52" s="7" t="inlineStr">
         <is>
@@ -3260,13 +3264,13 @@
       </c>
       <c r="B53" s="7" t="inlineStr">
         <is>
-          <t>Thép đai xoắn Φ8</t>
+          <t>Thép chủ cọc Φ28</t>
         </is>
       </c>
       <c r="C53" s="6" t="n"/>
       <c r="D53" s="7" t="inlineStr">
         <is>
-          <t>CB240-T, thép cuộn</t>
+          <t>CB400-V, thanh vằn</t>
         </is>
       </c>
       <c r="E53" s="6" t="inlineStr">
@@ -3275,19 +3279,19 @@
         </is>
       </c>
       <c r="F53" s="9" t="n">
-        <v>3563</v>
+        <v>8231</v>
       </c>
       <c r="G53" s="6" t="inlineStr">
         <is>
-          <t>5%</t>
+          <t>3%</t>
         </is>
       </c>
       <c r="H53" s="9" t="n">
-        <v>3742</v>
+        <v>8478</v>
       </c>
       <c r="I53" s="7" t="inlineStr">
         <is>
-          <t>Cọc khoan nhồi (engine)</t>
+          <t>Lồng thép cọc khoan nhồi (engine)</t>
         </is>
       </c>
     </row>
@@ -3297,13 +3301,13 @@
       </c>
       <c r="B54" s="7" t="inlineStr">
         <is>
-          <t>Thép bản đế Φ12</t>
+          <t>Thép đai xoắn Φ8</t>
         </is>
       </c>
       <c r="C54" s="6" t="n"/>
       <c r="D54" s="7" t="inlineStr">
         <is>
-          <t>CB400-V (lưới đế)</t>
+          <t>CB240-T, thép cuộn</t>
         </is>
       </c>
       <c r="E54" s="6" t="inlineStr">
@@ -3312,39 +3316,35 @@
         </is>
       </c>
       <c r="F54" s="9" t="n">
-        <v>17935</v>
+        <v>3563</v>
       </c>
       <c r="G54" s="6" t="inlineStr">
         <is>
-          <t>3%</t>
+          <t>5%</t>
         </is>
       </c>
       <c r="H54" s="9" t="n">
-        <v>18474</v>
+        <v>3742</v>
       </c>
       <c r="I54" s="7" t="inlineStr">
         <is>
-          <t>Đế BTCT (engine)</t>
-        </is>
-      </c>
-    </row>
-    <row r="55" ht="46" customHeight="1">
+          <t>Cọc khoan nhồi (engine)</t>
+        </is>
+      </c>
+    </row>
+    <row r="55" ht="92" customHeight="1">
       <c r="A55" s="6" t="n">
         <v>43</v>
       </c>
       <c r="B55" s="7" t="inlineStr">
         <is>
-          <t>Thép ống vít Ø89×5</t>
-        </is>
-      </c>
-      <c r="C55" s="6" t="inlineStr">
-        <is>
-          <t>(chưa có hình)</t>
-        </is>
-      </c>
+          <t>Thép bản đế Φ12</t>
+        </is>
+      </c>
+      <c r="C55" s="6" t="n"/>
       <c r="D55" s="7" t="inlineStr">
         <is>
-          <t>Ống thép mạ kẽm nhúng nóng</t>
+          <t>CB400-V (lưới đế)</t>
         </is>
       </c>
       <c r="E55" s="6" t="inlineStr">
@@ -3353,35 +3353,39 @@
         </is>
       </c>
       <c r="F55" s="9" t="n">
-        <v>15599</v>
+        <v>17935</v>
       </c>
       <c r="G55" s="6" t="inlineStr">
         <is>
-          <t>5%</t>
+          <t>3%</t>
         </is>
       </c>
       <c r="H55" s="9" t="n">
-        <v>16379</v>
+        <v>18474</v>
       </c>
       <c r="I55" s="7" t="inlineStr">
         <is>
-          <t>10,36 kg/m</t>
-        </is>
-      </c>
-    </row>
-    <row r="56" ht="92" customHeight="1">
+          <t>Đế BTCT (engine)</t>
+        </is>
+      </c>
+    </row>
+    <row r="56" ht="46" customHeight="1">
       <c r="A56" s="6" t="n">
         <v>44</v>
       </c>
       <c r="B56" s="7" t="inlineStr">
         <is>
-          <t>Thép tấm bản mã + tai neo (đầu cọc, đài, đế)</t>
-        </is>
-      </c>
-      <c r="C56" s="6" t="n"/>
+          <t>Thép ống vít Ø89×5</t>
+        </is>
+      </c>
+      <c r="C56" s="6" t="inlineStr">
+        <is>
+          <t>(chưa có hình)</t>
+        </is>
+      </c>
       <c r="D56" s="7" t="inlineStr">
         <is>
-          <t>SS400 mạ kẽm nhúng nóng</t>
+          <t>Ống thép mạ kẽm nhúng nóng</t>
         </is>
       </c>
       <c r="E56" s="6" t="inlineStr">
@@ -3390,7 +3394,7 @@
         </is>
       </c>
       <c r="F56" s="9" t="n">
-        <v>8248</v>
+        <v>15599</v>
       </c>
       <c r="G56" s="6" t="inlineStr">
         <is>
@@ -3398,11 +3402,11 @@
         </is>
       </c>
       <c r="H56" s="9" t="n">
-        <v>8661</v>
+        <v>16379</v>
       </c>
       <c r="I56" s="7" t="inlineStr">
         <is>
-          <t>271 bộ</t>
+          <t>10,36 kg/m</t>
         </is>
       </c>
     </row>
@@ -3412,13 +3416,13 @@
       </c>
       <c r="B57" s="7" t="inlineStr">
         <is>
-          <t>Thép neo bản mã Φ22</t>
+          <t>Thép tấm bản mã + tai neo (đầu cọc, đài, đế)</t>
         </is>
       </c>
       <c r="C57" s="6" t="n"/>
       <c r="D57" s="7" t="inlineStr">
         <is>
-          <t>CB400-V</t>
+          <t>SS400 mạ kẽm nhúng nóng</t>
         </is>
       </c>
       <c r="E57" s="6" t="inlineStr">
@@ -3427,39 +3431,35 @@
         </is>
       </c>
       <c r="F57" s="9" t="n">
-        <v>1582</v>
+        <v>8248</v>
       </c>
       <c r="G57" s="6" t="inlineStr">
         <is>
-          <t>3%</t>
+          <t>5%</t>
         </is>
       </c>
       <c r="H57" s="9" t="n">
-        <v>1629</v>
+        <v>8661</v>
       </c>
       <c r="I57" s="7" t="inlineStr">
         <is>
-          <t>271 bộ × 4 thanh</t>
-        </is>
-      </c>
-    </row>
-    <row r="58" ht="46" customHeight="1">
+          <t>271 bộ</t>
+        </is>
+      </c>
+    </row>
+    <row r="58" ht="92" customHeight="1">
       <c r="A58" s="6" t="n">
         <v>46</v>
       </c>
       <c r="B58" s="7" t="inlineStr">
         <is>
-          <t>Thép đài cọc đôi</t>
-        </is>
-      </c>
-      <c r="C58" s="6" t="inlineStr">
-        <is>
-          <t>(chưa có hình)</t>
-        </is>
-      </c>
+          <t>Thép neo bản mã Φ22</t>
+        </is>
+      </c>
+      <c r="C58" s="6" t="n"/>
       <c r="D58" s="7" t="inlineStr">
         <is>
-          <t>CB400-V Φ16, Φ12; CB240-T Φ10</t>
+          <t>CB400-V</t>
         </is>
       </c>
       <c r="E58" s="6" t="inlineStr">
@@ -3468,19 +3468,19 @@
         </is>
       </c>
       <c r="F58" s="9" t="n">
-        <v>3288</v>
+        <v>1582</v>
       </c>
       <c r="G58" s="6" t="inlineStr">
         <is>
-          <t>5%</t>
+          <t>3%</t>
         </is>
       </c>
       <c r="H58" s="9" t="n">
-        <v>3453</v>
+        <v>1629</v>
       </c>
       <c r="I58" s="7" t="inlineStr">
         <is>
-          <t>twinPileCap.ts</t>
+          <t>271 bộ × 4 thanh</t>
         </is>
       </c>
     </row>
@@ -3490,36 +3490,77 @@
       </c>
       <c r="B59" s="7" t="inlineStr">
         <is>
+          <t>Thép đài cọc đôi</t>
+        </is>
+      </c>
+      <c r="C59" s="6" t="inlineStr">
+        <is>
+          <t>(chưa có hình)</t>
+        </is>
+      </c>
+      <c r="D59" s="7" t="inlineStr">
+        <is>
+          <t>CB400-V Φ16, Φ12; CB240-T Φ10</t>
+        </is>
+      </c>
+      <c r="E59" s="6" t="inlineStr">
+        <is>
+          <t>kg</t>
+        </is>
+      </c>
+      <c r="F59" s="9" t="n">
+        <v>3288</v>
+      </c>
+      <c r="G59" s="6" t="inlineStr">
+        <is>
+          <t>5%</t>
+        </is>
+      </c>
+      <c r="H59" s="9" t="n">
+        <v>3453</v>
+      </c>
+      <c r="I59" s="7" t="inlineStr">
+        <is>
+          <t>twinPileCap.ts</t>
+        </is>
+      </c>
+    </row>
+    <row r="60" ht="46" customHeight="1">
+      <c r="A60" s="6" t="n">
+        <v>48</v>
+      </c>
+      <c r="B60" s="7" t="inlineStr">
+        <is>
           <t>TỔNG THÉP HỆ NEO</t>
         </is>
       </c>
-      <c r="C59" s="6" t="inlineStr">
+      <c r="C60" s="6" t="inlineStr">
         <is>
           <t>(chưa có hình)</t>
         </is>
       </c>
-      <c r="D59" s="7" t="inlineStr">
+      <c r="D60" s="7" t="inlineStr">
         <is>
           <t>Thép thanh + thép ống vít + thép tấm bản nắp</t>
         </is>
       </c>
-      <c r="E59" s="6" t="inlineStr">
+      <c r="E60" s="6" t="inlineStr">
         <is>
           <t>kg</t>
         </is>
       </c>
-      <c r="F59" s="9" t="n">
+      <c r="F60" s="9" t="n">
         <v>85455</v>
       </c>
-      <c r="G59" s="6" t="inlineStr">
+      <c r="G60" s="6" t="inlineStr">
         <is>
           <t>theo từng loại</t>
         </is>
       </c>
-      <c r="H59" s="9" t="n">
+      <c r="H60" s="9" t="n">
         <v>88636</v>
       </c>
-      <c r="I59" s="7" t="inlineStr">
+      <c r="I60" s="7" t="inlineStr">
         <is>
           <t>Chưa gồm nắp khóa vít, tấm chia (chưa có kích thước chi tiết)</t>
         </is>

--- a/public/docs_ban_mong/HOBANMONG_THONG_KE_VAT_TU_NEO.xlsx
+++ b/public/docs_ban_mong/HOBANMONG_THONG_KE_VAT_TU_NEO.xlsx
@@ -3891,7 +3891,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O12"/>
+  <dimension ref="A1:P12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8.83203125" customWidth="1" min="1" max="1"/>
@@ -3904,11 +3904,12 @@
     <col width="14.83203125" customWidth="1" min="8" max="8"/>
     <col width="14.83203125" customWidth="1" min="9" max="9"/>
     <col width="14.83203125" customWidth="1" min="10" max="10"/>
-    <col width="12.83203125" customWidth="1" min="11" max="11"/>
+    <col width="14.83203125" customWidth="1" min="11" max="11"/>
     <col width="12.83203125" customWidth="1" min="12" max="12"/>
-    <col width="9.83203125" customWidth="1" min="13" max="13"/>
+    <col width="12.83203125" customWidth="1" min="13" max="13"/>
     <col width="9.83203125" customWidth="1" min="14" max="14"/>
     <col width="9.83203125" customWidth="1" min="15" max="15"/>
+    <col width="9.83203125" customWidth="1" min="16" max="16"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3921,7 +3922,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Mỗi cọc: D350 đổ tại chỗ, lồng thép theo bè, đai xoắn Φ8 a150 CB240-T, mũ cọc + bản nắp 400×400×20 + tai neo + 4Φ25 L600 ngàm bản nắp.</t>
+          <t>Mỗi cọc: D350 đổ tại chỗ, lồng thép theo bè, đai xoắn Φ8 a150 CB240-T. Mỗi điểm neo một đầu cọc (bản mã + tai neo + thép neo, shorePileHead.ts) hoặc, ở điểm cọc đôi, một đài BTCT nối hai đầu cọc (twinPileCap.ts).</t>
         </is>
       </c>
     </row>
@@ -3973,30 +3974,35 @@
       </c>
       <c r="J3" s="3" t="inlineStr">
         <is>
-          <t>Râu thép 4Φ25 L600 (kg)</t>
+          <t>Thép neo bản mã (kg)</t>
         </is>
       </c>
       <c r="K3" s="3" t="inlineStr">
         <is>
-          <t>Bản nắp SS400 (kg)</t>
+          <t>Bản mã + tai neo SS400 (kg)</t>
         </is>
       </c>
       <c r="L3" s="3" t="inlineStr">
         <is>
+          <t>Thép đài cọc đôi (kg)</t>
+        </is>
+      </c>
+      <c r="M3" s="3" t="inlineStr">
+        <is>
           <t>Tổng thép (kg)</t>
         </is>
       </c>
-      <c r="M3" s="3" t="inlineStr">
+      <c r="N3" s="3" t="inlineStr">
         <is>
           <t>T dây (kN)</t>
         </is>
       </c>
-      <c r="N3" s="3" t="inlineStr">
+      <c r="O3" s="3" t="inlineStr">
         <is>
           <t>BP-1 ngang</t>
         </is>
       </c>
-      <c r="O3" s="3" t="inlineStr">
+      <c r="P3" s="3" t="inlineStr">
         <is>
           <t>BP-2 uốn</t>
         </is>
@@ -4035,21 +4041,24 @@
         <v>615</v>
       </c>
       <c r="J4" s="11" t="n">
-        <v>351</v>
+        <v>136</v>
       </c>
       <c r="K4" s="11" t="n">
-        <v>955</v>
+        <v>559</v>
       </c>
       <c r="L4" s="11" t="n">
-        <v>7720</v>
+        <v>718</v>
       </c>
       <c r="M4" s="11" t="n">
+        <v>7827</v>
+      </c>
+      <c r="N4" s="11" t="n">
         <v>104.9</v>
       </c>
-      <c r="N4" s="11" t="n">
+      <c r="O4" s="11" t="n">
         <v>0.5</v>
       </c>
-      <c r="O4" s="11" t="n">
+      <c r="P4" s="11" t="n">
         <v>0.8100000000000001</v>
       </c>
     </row>
@@ -4086,21 +4095,24 @@
         <v>405</v>
       </c>
       <c r="J5" s="11" t="n">
-        <v>231</v>
+        <v>179</v>
       </c>
       <c r="K5" s="11" t="n">
-        <v>628</v>
+        <v>736</v>
       </c>
       <c r="L5" s="11" t="n">
-        <v>6049</v>
+        <v>0</v>
       </c>
       <c r="M5" s="11" t="n">
+        <v>6105</v>
+      </c>
+      <c r="N5" s="11" t="n">
         <v>73.7</v>
       </c>
-      <c r="N5" s="11" t="n">
+      <c r="O5" s="11" t="n">
         <v>0.64</v>
       </c>
-      <c r="O5" s="11" t="n">
+      <c r="P5" s="11" t="n">
         <v>0.87</v>
       </c>
     </row>
@@ -4137,21 +4149,24 @@
         <v>551</v>
       </c>
       <c r="J6" s="11" t="n">
-        <v>314</v>
+        <v>122</v>
       </c>
       <c r="K6" s="11" t="n">
-        <v>854</v>
+        <v>500</v>
       </c>
       <c r="L6" s="11" t="n">
-        <v>6907</v>
+        <v>642</v>
       </c>
       <c r="M6" s="11" t="n">
+        <v>7003</v>
+      </c>
+      <c r="N6" s="11" t="n">
         <v>106.9</v>
       </c>
-      <c r="N6" s="11" t="n">
+      <c r="O6" s="11" t="n">
         <v>0.51</v>
       </c>
-      <c r="O6" s="11" t="n">
+      <c r="P6" s="11" t="n">
         <v>0.82</v>
       </c>
     </row>
@@ -4188,21 +4203,24 @@
         <v>518</v>
       </c>
       <c r="J7" s="11" t="n">
-        <v>296</v>
+        <v>115</v>
       </c>
       <c r="K7" s="11" t="n">
-        <v>804</v>
+        <v>471</v>
       </c>
       <c r="L7" s="11" t="n">
-        <v>6501</v>
+        <v>605</v>
       </c>
       <c r="M7" s="11" t="n">
+        <v>6591</v>
+      </c>
+      <c r="N7" s="11" t="n">
         <v>94.59999999999999</v>
       </c>
-      <c r="N7" s="11" t="n">
+      <c r="O7" s="11" t="n">
         <v>0.45</v>
       </c>
-      <c r="O7" s="11" t="n">
+      <c r="P7" s="11" t="n">
         <v>0.71</v>
       </c>
     </row>
@@ -4239,21 +4257,24 @@
         <v>292</v>
       </c>
       <c r="J8" s="11" t="n">
-        <v>166</v>
+        <v>129</v>
       </c>
       <c r="K8" s="11" t="n">
-        <v>452</v>
+        <v>530</v>
       </c>
       <c r="L8" s="11" t="n">
-        <v>4356</v>
+        <v>0</v>
       </c>
       <c r="M8" s="11" t="n">
+        <v>4396</v>
+      </c>
+      <c r="N8" s="11" t="n">
         <v>75</v>
       </c>
-      <c r="N8" s="11" t="n">
+      <c r="O8" s="11" t="n">
         <v>0.65</v>
       </c>
-      <c r="O8" s="11" t="n">
+      <c r="P8" s="11" t="n">
         <v>0.89</v>
       </c>
     </row>
@@ -4290,21 +4311,24 @@
         <v>49</v>
       </c>
       <c r="J9" s="11" t="n">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="K9" s="11" t="n">
-        <v>75</v>
+        <v>88</v>
       </c>
       <c r="L9" s="11" t="n">
-        <v>609</v>
+        <v>0</v>
       </c>
       <c r="M9" s="11" t="n">
+        <v>616</v>
+      </c>
+      <c r="N9" s="11" t="n">
         <v>54.9</v>
       </c>
-      <c r="N9" s="11" t="n">
+      <c r="O9" s="11" t="n">
         <v>0.47</v>
       </c>
-      <c r="O9" s="11" t="n">
+      <c r="P9" s="11" t="n">
         <v>0.75</v>
       </c>
     </row>
@@ -4341,21 +4365,24 @@
         <v>648</v>
       </c>
       <c r="J10" s="11" t="n">
-        <v>370</v>
+        <v>143</v>
       </c>
       <c r="K10" s="11" t="n">
-        <v>1005</v>
+        <v>589</v>
       </c>
       <c r="L10" s="11" t="n">
-        <v>8126</v>
+        <v>756</v>
       </c>
       <c r="M10" s="11" t="n">
+        <v>8239</v>
+      </c>
+      <c r="N10" s="11" t="n">
         <v>107</v>
       </c>
-      <c r="N10" s="11" t="n">
+      <c r="O10" s="11" t="n">
         <v>0.51</v>
       </c>
-      <c r="O10" s="11" t="n">
+      <c r="P10" s="11" t="n">
         <v>0.82</v>
       </c>
     </row>
@@ -4392,21 +4419,24 @@
         <v>486</v>
       </c>
       <c r="J11" s="11" t="n">
-        <v>277</v>
+        <v>107</v>
       </c>
       <c r="K11" s="11" t="n">
-        <v>754</v>
+        <v>442</v>
       </c>
       <c r="L11" s="11" t="n">
-        <v>6095</v>
+        <v>567</v>
       </c>
       <c r="M11" s="11" t="n">
+        <v>6180</v>
+      </c>
+      <c r="N11" s="11" t="n">
         <v>94</v>
       </c>
-      <c r="N11" s="11" t="n">
+      <c r="O11" s="11" t="n">
         <v>0.45</v>
       </c>
-      <c r="O11" s="11" t="n">
+      <c r="P11" s="11" t="n">
         <v>0.7</v>
       </c>
     </row>
@@ -4435,17 +4465,20 @@
         <v>3563</v>
       </c>
       <c r="J12" s="11" t="n">
-        <v>2035</v>
+        <v>953</v>
       </c>
       <c r="K12" s="11" t="n">
-        <v>5526</v>
+        <v>3915</v>
       </c>
       <c r="L12" s="11" t="n">
-        <v>46364</v>
-      </c>
-      <c r="M12" s="11" t="str"/>
+        <v>3288</v>
+      </c>
+      <c r="M12" s="11" t="n">
+        <v>46958</v>
+      </c>
       <c r="N12" s="11" t="str"/>
       <c r="O12" s="11" t="str"/>
+      <c r="P12" s="11" t="str"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/public/docs_ban_mong/HOBANMONG_THONG_KE_VAT_TU_NEO.xlsx
+++ b/public/docs_ban_mong/HOBANMONG_THONG_KE_VAT_TU_NEO.xlsx
@@ -1828,13 +1828,13 @@
       </c>
       <c r="B9" s="7" t="inlineStr">
         <is>
-          <t>Cáp chính dây bờ PES-40</t>
+          <t>Cáp chính dây bờ PES-48</t>
         </is>
       </c>
       <c r="C9" s="6" t="n"/>
       <c r="D9" s="7" t="inlineStr">
         <is>
-          <t>Polyester PES-40, MBL 475 kN, bện 8–12 tao, chống UV</t>
+          <t>Polyester PES-48, MBL undefined kN, bện 8–12 tao, chống UV</t>
         </is>
       </c>
       <c r="E9" s="6" t="inlineStr">
@@ -1939,13 +1939,13 @@
       </c>
       <c r="B12" s="7" t="inlineStr">
         <is>
-          <t>Cáp chính dây đáy PES-40</t>
+          <t>Cáp chính dây đáy PES-48</t>
         </is>
       </c>
       <c r="C12" s="6" t="n"/>
       <c r="D12" s="7" t="inlineStr">
         <is>
-          <t>Polyester PES-40, MBL 475 kN</t>
+          <t>Polyester PES-48, MBL undefined kN</t>
         </is>
       </c>
       <c r="E12" s="6" t="inlineStr">
@@ -2297,7 +2297,7 @@
       <c r="C22" s="6" t="n"/>
       <c r="D22" s="7" t="inlineStr">
         <is>
-          <t>SS400 t = 25, rộng 200, lỗ chốt Ø32 / Ø36 (= chốt ma-nê + 4 mm); tim chốt cách mặt đất 100 mm; hàn góc 10 mm hai phía</t>
+          <t>SS400 t = 25, rộng 200, lỗ chốt Ø32 / Ø36 / Ø39 (= chốt ma-nê + 4 mm); tim chốt cách mặt đất 100 mm; hàn góc 10 mm hai phía</t>
         </is>
       </c>
       <c r="E22" s="6" t="inlineStr">
@@ -2318,7 +2318,7 @@
       </c>
       <c r="I22" s="7" t="inlineStr">
         <is>
-          <t>1 cái mỗi điểm neo, chịu cả T của dây (tới 150,4 kN); ma-nê 8.5 / 9.5 t</t>
+          <t>1 cái mỗi điểm neo, chịu cả T của dây (tới 152,1 kN); ma-nê 8.5 / 9.5 / 12 t</t>
         </is>
       </c>
     </row>
@@ -2390,7 +2390,7 @@
       <c r="C25" s="6" t="n"/>
       <c r="D25" s="7" t="inlineStr">
         <is>
-          <t>C25/30 chống thấm; 10 đế 2,50 m, 1 đế 2,75 m, 5 đế 3,00 m, 6 đế 3,25 m, 3 đế 3,50 m, 2 đế 3,75 m, 6 đế 4,00 m, 1 đế 4,75 m, 1 đế 5,25 m; dày 0,4 / 0,5 / 0,6 m</t>
+          <t>C25/30 chống thấm; 10 đế 2,50 m, 1 đế 2,75 m, 6 đế 3,00 m, 5 đế 3,25 m, 3 đế 3,50 m, 1 đế 3,75 m, 6 đế 4,00 m, 1 đế 4,25 m, 1 đế 4,75 m, 1 đế 5,25 m; dày 0,4 / 0,5 / 0,6 m</t>
         </is>
       </c>
       <c r="E25" s="6" t="inlineStr">
@@ -2399,7 +2399,7 @@
         </is>
       </c>
       <c r="F25" s="8" t="n">
-        <v>173.3</v>
+        <v>173.6</v>
       </c>
       <c r="G25" s="6" t="inlineStr">
         <is>
@@ -2407,7 +2407,7 @@
         </is>
       </c>
       <c r="H25" s="8" t="n">
-        <v>178.5</v>
+        <v>178.8</v>
       </c>
       <c r="I25" s="7" t="inlineStr">
         <is>
@@ -2436,7 +2436,7 @@
         </is>
       </c>
       <c r="F26" s="9" t="n">
-        <v>7249</v>
+        <v>7292</v>
       </c>
       <c r="G26" s="6" t="inlineStr">
         <is>
@@ -2444,7 +2444,7 @@
         </is>
       </c>
       <c r="H26" s="9" t="n">
-        <v>7467</v>
+        <v>7511</v>
       </c>
       <c r="I26" s="7" t="inlineStr">
         <is>
@@ -3323,7 +3323,7 @@
       </c>
       <c r="I51" s="7" t="inlineStr">
         <is>
-          <t>Yêu cầu của mô hình cân bằng (mooringEquilibrium.ts): dây luôn vừa căng ở mọi mực nước. Đối trọng treo một mình KHÔNG giữ được bè: nếu không khóa, bè trôi 4,3–6,7 m hết hành trình dư rồi lực dây vọt tới 91–359 kN</t>
+          <t>Yêu cầu của mô hình cân bằng (mooringEquilibrium.ts): dây luôn vừa căng ở mọi mực nước. Đối trọng treo một mình KHÔNG giữ được bè: nếu không khóa, bè trôi 4,3–6,7 m hết hành trình dư rồi lực dây vọt tới 89–379 kN</t>
         </is>
       </c>
     </row>
@@ -3343,7 +3343,7 @@
       </c>
       <c r="D52" s="7" t="inlineStr">
         <is>
-          <t>Khóa cáp khi gió vượt ngưỡng, giữ tới lực đứt của cáp chính (PES-32: 305 kN; PES-36: 385 kN; PES-40: 475 kN) để khóa không yếu hơn cáp; mất điện / mất tín hiệu thì tự khóa (lò xo ép phanh)</t>
+          <t>Khóa cáp khi gió vượt ngưỡng, giữ tới lực đứt của cáp chính (PES-32: 305 kN; PES-36: 385 kN; PES-48: undefined kN) để khóa không yếu hơn cáp; mất điện / mất tín hiệu thì tự khóa (lò xo ép phanh)</t>
         </is>
       </c>
       <c r="E52" s="6" t="inlineStr">
@@ -3364,7 +3364,7 @@
       </c>
       <c r="I52" s="7" t="inlineStr">
         <is>
-          <t>Lực dây, đế, cọc của bảng này chỉ đúng khi khóa làm việc. Cần: tín hiệu gió + dự phòng, kiểm tra định kỳ, thử tải; khóa hỏng thì hệ số an toàn cáp chỉ còn 1,3–3,4 (xem cảnh báo ở Header). Pre-FS gợi ý phao chỉ hướng ~2,5 t — chưa đánh giá</t>
+          <t>Lực dây, đế, cọc của bảng này chỉ đúng khi khóa làm việc. Cần: tín hiệu gió + dự phòng, kiểm tra định kỳ, thử tải; khóa hỏng thì hệ số an toàn cáp chỉ còn NaN–NaN (xem cảnh báo ở Header). Pre-FS gợi ý phao chỉ hướng ~2,5 t — chưa đánh giá</t>
         </is>
       </c>
     </row>
@@ -3519,7 +3519,7 @@
         </is>
       </c>
       <c r="F57" s="9" t="n">
-        <v>7249</v>
+        <v>7292</v>
       </c>
       <c r="G57" s="6" t="inlineStr">
         <is>
@@ -3527,7 +3527,7 @@
         </is>
       </c>
       <c r="H57" s="9" t="n">
-        <v>7467</v>
+        <v>7511</v>
       </c>
       <c r="I57" s="7" t="inlineStr">
         <is>
@@ -3634,7 +3634,7 @@
         </is>
       </c>
       <c r="F60" s="9" t="n">
-        <v>1592</v>
+        <v>1593</v>
       </c>
       <c r="G60" s="6" t="inlineStr">
         <is>
@@ -3642,7 +3642,7 @@
         </is>
       </c>
       <c r="H60" s="9" t="n">
-        <v>1640</v>
+        <v>1641</v>
       </c>
       <c r="I60" s="7" t="inlineStr">
         <is>
@@ -3675,7 +3675,7 @@
         </is>
       </c>
       <c r="F61" s="9" t="n">
-        <v>59725</v>
+        <v>59769</v>
       </c>
       <c r="G61" s="6" t="inlineStr">
         <is>
@@ -3683,7 +3683,7 @@
         </is>
       </c>
       <c r="H61" s="9" t="n">
-        <v>61834</v>
+        <v>61879</v>
       </c>
       <c r="I61" s="7" t="inlineStr">
         <is>
@@ -3861,7 +3861,7 @@
         </is>
       </c>
       <c r="C7" s="11" t="n">
-        <v>7249</v>
+        <v>7292</v>
       </c>
       <c r="D7" s="11" t="inlineStr">
         <is>
@@ -3869,7 +3869,7 @@
         </is>
       </c>
       <c r="E7" s="11" t="n">
-        <v>7467</v>
+        <v>7511</v>
       </c>
       <c r="F7" s="11" t="inlineStr">
         <is>
@@ -3945,7 +3945,7 @@
         </is>
       </c>
       <c r="C10" s="11" t="n">
-        <v>1592</v>
+        <v>1593</v>
       </c>
       <c r="D10" s="11" t="inlineStr">
         <is>
@@ -3953,7 +3953,7 @@
         </is>
       </c>
       <c r="E10" s="11" t="n">
-        <v>1640</v>
+        <v>1641</v>
       </c>
       <c r="F10" s="11" t="inlineStr">
         <is>
@@ -3969,11 +3969,11 @@
       </c>
       <c r="B11" s="11" t="str"/>
       <c r="C11" s="11" t="n">
-        <v>59725</v>
+        <v>59769</v>
       </c>
       <c r="D11" s="11" t="str"/>
       <c r="E11" s="11" t="n">
-        <v>61834</v>
+        <v>61879</v>
       </c>
       <c r="F11" s="11" t="str"/>
     </row>
@@ -4156,7 +4156,7 @@
         <v>0.74</v>
       </c>
       <c r="P4" s="11" t="n">
-        <v>0.86</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="5">
@@ -4204,7 +4204,7 @@
         <v>10013</v>
       </c>
       <c r="N5" s="11" t="n">
-        <v>81.09999999999999</v>
+        <v>81.3</v>
       </c>
       <c r="O5" s="11" t="n">
         <v>0.7</v>
@@ -4258,13 +4258,13 @@
         <v>3663</v>
       </c>
       <c r="N6" s="11" t="n">
-        <v>77.59999999999999</v>
+        <v>76.5</v>
       </c>
       <c r="O6" s="11" t="n">
-        <v>0.67</v>
+        <v>0.66</v>
       </c>
       <c r="P6" s="11" t="n">
-        <v>0.93</v>
+        <v>0.91</v>
       </c>
     </row>
     <row r="7">
@@ -4312,13 +4312,13 @@
         <v>5373</v>
       </c>
       <c r="N7" s="11" t="n">
-        <v>82.59999999999999</v>
+        <v>82.8</v>
       </c>
       <c r="O7" s="11" t="n">
         <v>0.71</v>
       </c>
       <c r="P7" s="11" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.82</v>
       </c>
     </row>
     <row r="8">
@@ -4366,13 +4366,13 @@
         <v>6594</v>
       </c>
       <c r="N8" s="11" t="n">
-        <v>106.2</v>
+        <v>105.9</v>
       </c>
       <c r="O8" s="11" t="n">
-        <v>0.67</v>
+        <v>0.66</v>
       </c>
       <c r="P8" s="11" t="n">
-        <v>0.93</v>
+        <v>0.92</v>
       </c>
     </row>
     <row r="9">
@@ -4420,13 +4420,13 @@
         <v>10989</v>
       </c>
       <c r="N9" s="11" t="n">
-        <v>150.4</v>
+        <v>152.1</v>
       </c>
       <c r="O9" s="11" t="n">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="P9" s="11" t="n">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="10">
@@ -12679,7 +12679,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M50"/>
+  <dimension ref="A1:M51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10.83203125" customWidth="1" min="1" max="1"/>
@@ -13386,7 +13386,7 @@
         <v>24.46</v>
       </c>
       <c r="M16" s="11" t="n">
-        <v>0.98</v>
+        <v>0.97</v>
       </c>
     </row>
     <row r="17">
@@ -13433,7 +13433,7 @@
         <v>20.39</v>
       </c>
       <c r="M17" s="11" t="n">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
     </row>
     <row r="18">
@@ -13621,7 +13621,7 @@
         <v>20.39</v>
       </c>
       <c r="M21" s="11" t="n">
-        <v>0.99</v>
+        <v>0.98</v>
       </c>
     </row>
     <row r="22">
@@ -13762,7 +13762,7 @@
         <v>6.37</v>
       </c>
       <c r="M24" s="11" t="n">
-        <v>0.82</v>
+        <v>0.8100000000000001</v>
       </c>
     </row>
     <row r="25">
@@ -13832,31 +13832,31 @@
         </is>
       </c>
       <c r="E26" s="11" t="n">
-        <v>3.25</v>
+        <v>3</v>
       </c>
       <c r="F26" s="11" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="G26" s="11" t="n">
-        <v>5.26</v>
+        <v>5.37</v>
       </c>
       <c r="H26" s="11" t="n">
-        <v>201.5</v>
+        <v>164.9</v>
       </c>
       <c r="I26" s="11" t="n">
         <v>4</v>
       </c>
       <c r="J26" s="11" t="n">
-        <v>15.2</v>
+        <v>15.6</v>
       </c>
       <c r="K26" s="11" t="n">
-        <v>157</v>
+        <v>162</v>
       </c>
       <c r="L26" s="11" t="n">
-        <v>13.46</v>
+        <v>13.76</v>
       </c>
       <c r="M26" s="11" t="n">
-        <v>1</v>
+        <v>0.99</v>
       </c>
     </row>
     <row r="27">
@@ -14232,7 +14232,7 @@
         <v>35.12</v>
       </c>
       <c r="M34" s="11" t="n">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
     </row>
     <row r="35">
@@ -14279,7 +14279,7 @@
         <v>16.31</v>
       </c>
       <c r="M35" s="11" t="n">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
     </row>
     <row r="36">
@@ -14302,31 +14302,31 @@
         </is>
       </c>
       <c r="E36" s="11" t="n">
-        <v>3.75</v>
+        <v>4.25</v>
       </c>
       <c r="F36" s="11" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="G36" s="11" t="n">
-        <v>7.01</v>
+        <v>7.21</v>
       </c>
       <c r="H36" s="11" t="n">
-        <v>259.4</v>
+        <v>339.2</v>
       </c>
       <c r="I36" s="11" t="n">
         <v>4</v>
       </c>
       <c r="J36" s="11" t="n">
-        <v>15.2</v>
+        <v>14.8</v>
       </c>
       <c r="K36" s="11" t="n">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="L36" s="11" t="n">
-        <v>17.92</v>
+        <v>18.41</v>
       </c>
       <c r="M36" s="11" t="n">
-        <v>0.99</v>
+        <v>0.93</v>
       </c>
     </row>
     <row r="37">
@@ -14373,7 +14373,7 @@
         <v>7.71</v>
       </c>
       <c r="M37" s="11" t="n">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
     </row>
     <row r="38">
@@ -14420,7 +14420,7 @@
         <v>16.31</v>
       </c>
       <c r="M38" s="11" t="n">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
     </row>
     <row r="39">
@@ -14439,10 +14439,10 @@
       <c r="E39" s="11" t="str"/>
       <c r="F39" s="11" t="str"/>
       <c r="G39" s="11" t="n">
-        <v>173.27</v>
+        <v>173.58</v>
       </c>
       <c r="H39" s="11" t="n">
-        <v>7249</v>
+        <v>7292</v>
       </c>
       <c r="I39" s="11" t="n">
         <v>140</v>
@@ -14571,7 +14571,7 @@
       <c r="B44" s="11" t="str"/>
       <c r="C44" s="11" t="str"/>
       <c r="D44" s="11" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E44" s="11" t="n">
         <v>3</v>
@@ -14580,13 +14580,13 @@
         <v>0.4</v>
       </c>
       <c r="G44" s="11" t="n">
-        <v>18.8</v>
+        <v>24.18</v>
       </c>
       <c r="H44" s="11" t="n">
-        <v>825</v>
+        <v>989</v>
       </c>
       <c r="I44" s="11" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="J44" s="11" t="n"/>
       <c r="K44" s="11" t="n"/>
@@ -14602,7 +14602,7 @@
       <c r="B45" s="11" t="str"/>
       <c r="C45" s="11" t="str"/>
       <c r="D45" s="11" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E45" s="11" t="n">
         <v>3.25</v>
@@ -14611,13 +14611,13 @@
         <v>0.5</v>
       </c>
       <c r="G45" s="11" t="n">
-        <v>27.34</v>
+        <v>22.09</v>
       </c>
       <c r="H45" s="11" t="n">
-        <v>1209</v>
+        <v>1008</v>
       </c>
       <c r="I45" s="11" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="J45" s="11" t="n"/>
       <c r="K45" s="11" t="n"/>
@@ -14664,7 +14664,7 @@
       <c r="B47" s="11" t="str"/>
       <c r="C47" s="11" t="str"/>
       <c r="D47" s="11" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E47" s="11" t="n">
         <v>3.75</v>
@@ -14673,13 +14673,13 @@
         <v>0.5</v>
       </c>
       <c r="G47" s="11" t="n">
-        <v>14.02</v>
+        <v>7.01</v>
       </c>
       <c r="H47" s="11" t="n">
-        <v>519</v>
+        <v>259</v>
       </c>
       <c r="I47" s="11" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="J47" s="11" t="n"/>
       <c r="K47" s="11" t="n"/>
@@ -14720,7 +14720,7 @@
     <row r="49">
       <c r="A49" s="11" t="inlineStr">
         <is>
-          <t>Đế 4,75 m</t>
+          <t>Đế 4,25 m</t>
         </is>
       </c>
       <c r="B49" s="11" t="str"/>
@@ -14729,16 +14729,16 @@
         <v>1</v>
       </c>
       <c r="E49" s="11" t="n">
-        <v>4.75</v>
+        <v>4.25</v>
       </c>
       <c r="F49" s="11" t="n">
         <v>0.4</v>
       </c>
       <c r="G49" s="11" t="n">
-        <v>9.01</v>
+        <v>7.21</v>
       </c>
       <c r="H49" s="11" t="n">
-        <v>413</v>
+        <v>339</v>
       </c>
       <c r="I49" s="11" t="n">
         <v>4</v>
@@ -14751,7 +14751,7 @@
     <row r="50">
       <c r="A50" s="11" t="inlineStr">
         <is>
-          <t>Đế 5,25 m</t>
+          <t>Đế 4,75 m</t>
         </is>
       </c>
       <c r="B50" s="11" t="str"/>
@@ -14760,16 +14760,16 @@
         <v>1</v>
       </c>
       <c r="E50" s="11" t="n">
-        <v>5.25</v>
+        <v>4.75</v>
       </c>
       <c r="F50" s="11" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="G50" s="11" t="n">
-        <v>13.76</v>
+        <v>9.01</v>
       </c>
       <c r="H50" s="11" t="n">
-        <v>512</v>
+        <v>413</v>
       </c>
       <c r="I50" s="11" t="n">
         <v>4</v>
@@ -14778,6 +14778,37 @@
       <c r="K50" s="11" t="n"/>
       <c r="L50" s="11" t="n"/>
       <c r="M50" s="11" t="n"/>
+    </row>
+    <row r="51">
+      <c r="A51" s="11" t="inlineStr">
+        <is>
+          <t>Đế 5,25 m</t>
+        </is>
+      </c>
+      <c r="B51" s="11" t="str"/>
+      <c r="C51" s="11" t="str"/>
+      <c r="D51" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="E51" s="11" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="F51" s="11" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G51" s="11" t="n">
+        <v>13.76</v>
+      </c>
+      <c r="H51" s="11" t="n">
+        <v>512</v>
+      </c>
+      <c r="I51" s="11" t="n">
+        <v>4</v>
+      </c>
+      <c r="J51" s="11" t="n"/>
+      <c r="K51" s="11" t="n"/>
+      <c r="L51" s="11" t="n"/>
+      <c r="M51" s="11" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -14945,7 +14976,7 @@
         </is>
       </c>
       <c r="B5" s="11" t="n">
-        <v>81.09999999999999</v>
+        <v>81.3</v>
       </c>
       <c r="C5" s="11" t="inlineStr">
         <is>
@@ -14956,10 +14987,10 @@
         <v>305</v>
       </c>
       <c r="E5" s="11" t="n">
-        <v>46.8</v>
+        <v>46.9</v>
       </c>
       <c r="F5" s="11" t="n">
-        <v>56.8</v>
+        <v>56.9</v>
       </c>
       <c r="G5" s="11" t="inlineStr">
         <is>
@@ -14970,7 +15001,7 @@
         <v>172</v>
       </c>
       <c r="I5" s="11" t="n">
-        <v>3.03</v>
+        <v>3.02</v>
       </c>
       <c r="J5" s="11" t="n">
         <v>2.12</v>
@@ -14994,7 +15025,7 @@
         </is>
       </c>
       <c r="B6" s="11" t="n">
-        <v>77.59999999999999</v>
+        <v>76.5</v>
       </c>
       <c r="C6" s="11" t="inlineStr">
         <is>
@@ -15005,10 +15036,10 @@
         <v>305</v>
       </c>
       <c r="E6" s="11" t="n">
-        <v>44.8</v>
+        <v>44.2</v>
       </c>
       <c r="F6" s="11" t="n">
-        <v>54.3</v>
+        <v>53.6</v>
       </c>
       <c r="G6" s="11" t="inlineStr">
         <is>
@@ -15019,10 +15050,10 @@
         <v>172</v>
       </c>
       <c r="I6" s="11" t="n">
-        <v>3.17</v>
+        <v>3.21</v>
       </c>
       <c r="J6" s="11" t="n">
-        <v>2.22</v>
+        <v>2.25</v>
       </c>
       <c r="K6" s="11" t="n">
         <v>9.5</v>
@@ -15043,7 +15074,7 @@
         </is>
       </c>
       <c r="B7" s="11" t="n">
-        <v>82.59999999999999</v>
+        <v>82.8</v>
       </c>
       <c r="C7" s="11" t="inlineStr">
         <is>
@@ -15054,10 +15085,10 @@
         <v>305</v>
       </c>
       <c r="E7" s="11" t="n">
-        <v>47.7</v>
+        <v>47.8</v>
       </c>
       <c r="F7" s="11" t="n">
-        <v>57.8</v>
+        <v>57.9</v>
       </c>
       <c r="G7" s="11" t="inlineStr">
         <is>
@@ -15071,7 +15102,7 @@
         <v>4.06</v>
       </c>
       <c r="J7" s="11" t="n">
-        <v>2.85</v>
+        <v>2.84</v>
       </c>
       <c r="K7" s="11" t="n">
         <v>9.5</v>
@@ -15092,7 +15123,7 @@
         </is>
       </c>
       <c r="B8" s="11" t="n">
-        <v>106.2</v>
+        <v>105.9</v>
       </c>
       <c r="C8" s="11" t="inlineStr">
         <is>
@@ -15103,10 +15134,10 @@
         <v>385</v>
       </c>
       <c r="E8" s="11" t="n">
-        <v>61.3</v>
+        <v>61.2</v>
       </c>
       <c r="F8" s="11" t="n">
-        <v>74.40000000000001</v>
+        <v>74.2</v>
       </c>
       <c r="G8" s="11" t="inlineStr">
         <is>
@@ -15117,10 +15148,10 @@
         <v>235</v>
       </c>
       <c r="I8" s="11" t="n">
-        <v>3.16</v>
+        <v>3.17</v>
       </c>
       <c r="J8" s="11" t="n">
-        <v>2.21</v>
+        <v>2.22</v>
       </c>
       <c r="K8" s="11" t="n">
         <v>12</v>
@@ -15141,21 +15172,21 @@
         </is>
       </c>
       <c r="B9" s="11" t="n">
-        <v>150.4</v>
+        <v>152.1</v>
       </c>
       <c r="C9" s="11" t="inlineStr">
         <is>
-          <t>PES-40</t>
+          <t>PES-48</t>
         </is>
       </c>
       <c r="D9" s="11" t="n">
-        <v>475</v>
+        <v>688</v>
       </c>
       <c r="E9" s="11" t="n">
-        <v>86.8</v>
+        <v>87.8</v>
       </c>
       <c r="F9" s="11" t="n">
-        <v>105.3</v>
+        <v>106.5</v>
       </c>
       <c r="G9" s="11" t="inlineStr">
         <is>
@@ -15166,10 +15197,10 @@
         <v>385</v>
       </c>
       <c r="I9" s="11" t="n">
-        <v>3.66</v>
+        <v>3.62</v>
       </c>
       <c r="J9" s="11" t="n">
-        <v>2.56</v>
+        <v>2.53</v>
       </c>
       <c r="K9" s="11" t="n">
         <v>17</v>
@@ -26176,7 +26207,7 @@
       </c>
       <c r="J197" s="11" t="inlineStr">
         <is>
-          <t>PES-40</t>
+          <t>PES-48</t>
         </is>
       </c>
       <c r="K197" s="11" t="inlineStr">
@@ -26231,7 +26262,7 @@
       </c>
       <c r="J198" s="11" t="inlineStr">
         <is>
-          <t>PES-40</t>
+          <t>PES-48</t>
         </is>
       </c>
       <c r="K198" s="11" t="inlineStr">
@@ -26286,7 +26317,7 @@
       </c>
       <c r="J199" s="11" t="inlineStr">
         <is>
-          <t>PES-40</t>
+          <t>PES-48</t>
         </is>
       </c>
       <c r="K199" s="11" t="inlineStr">
@@ -26341,7 +26372,7 @@
       </c>
       <c r="J200" s="11" t="inlineStr">
         <is>
-          <t>PES-40</t>
+          <t>PES-48</t>
         </is>
       </c>
       <c r="K200" s="11" t="inlineStr">
@@ -26396,7 +26427,7 @@
       </c>
       <c r="J201" s="11" t="inlineStr">
         <is>
-          <t>PES-40</t>
+          <t>PES-48</t>
         </is>
       </c>
       <c r="K201" s="11" t="inlineStr">
@@ -26451,7 +26482,7 @@
       </c>
       <c r="J202" s="11" t="inlineStr">
         <is>
-          <t>PES-40</t>
+          <t>PES-48</t>
         </is>
       </c>
       <c r="K202" s="11" t="inlineStr">
@@ -26510,7 +26541,7 @@
       </c>
       <c r="J203" s="11" t="inlineStr">
         <is>
-          <t>PES-40</t>
+          <t>PES-48</t>
         </is>
       </c>
       <c r="K203" s="11" t="inlineStr">
@@ -26565,7 +26596,7 @@
       </c>
       <c r="J204" s="11" t="inlineStr">
         <is>
-          <t>PES-40</t>
+          <t>PES-48</t>
         </is>
       </c>
       <c r="K204" s="11" t="inlineStr">
@@ -26620,7 +26651,7 @@
       </c>
       <c r="J205" s="11" t="inlineStr">
         <is>
-          <t>PES-40</t>
+          <t>PES-48</t>
         </is>
       </c>
       <c r="K205" s="11" t="inlineStr">
@@ -26675,7 +26706,7 @@
       </c>
       <c r="J206" s="11" t="inlineStr">
         <is>
-          <t>PES-40</t>
+          <t>PES-48</t>
         </is>
       </c>
       <c r="K206" s="11" t="inlineStr">
@@ -26730,7 +26761,7 @@
       </c>
       <c r="J207" s="11" t="inlineStr">
         <is>
-          <t>PES-40</t>
+          <t>PES-48</t>
         </is>
       </c>
       <c r="K207" s="11" t="inlineStr">
@@ -26785,7 +26816,7 @@
       </c>
       <c r="J208" s="11" t="inlineStr">
         <is>
-          <t>PES-40</t>
+          <t>PES-48</t>
         </is>
       </c>
       <c r="K208" s="11" t="inlineStr">
@@ -26840,7 +26871,7 @@
       </c>
       <c r="J209" s="11" t="inlineStr">
         <is>
-          <t>PES-40</t>
+          <t>PES-48</t>
         </is>
       </c>
       <c r="K209" s="11" t="inlineStr">
@@ -26899,7 +26930,7 @@
       </c>
       <c r="J210" s="11" t="inlineStr">
         <is>
-          <t>PES-40</t>
+          <t>PES-48</t>
         </is>
       </c>
       <c r="K210" s="11" t="inlineStr">
@@ -26954,7 +26985,7 @@
       </c>
       <c r="J211" s="11" t="inlineStr">
         <is>
-          <t>PES-40</t>
+          <t>PES-48</t>
         </is>
       </c>
       <c r="K211" s="11" t="inlineStr">
@@ -27009,7 +27040,7 @@
       </c>
       <c r="J212" s="11" t="inlineStr">
         <is>
-          <t>PES-40</t>
+          <t>PES-48</t>
         </is>
       </c>
       <c r="K212" s="11" t="inlineStr">
@@ -27064,7 +27095,7 @@
       </c>
       <c r="J213" s="11" t="inlineStr">
         <is>
-          <t>PES-40</t>
+          <t>PES-48</t>
         </is>
       </c>
       <c r="K213" s="11" t="inlineStr">
@@ -27119,7 +27150,7 @@
       </c>
       <c r="J214" s="11" t="inlineStr">
         <is>
-          <t>PES-40</t>
+          <t>PES-48</t>
         </is>
       </c>
       <c r="K214" s="11" t="inlineStr">
@@ -27174,7 +27205,7 @@
       </c>
       <c r="J215" s="11" t="inlineStr">
         <is>
-          <t>PES-40</t>
+          <t>PES-48</t>
         </is>
       </c>
       <c r="K215" s="11" t="inlineStr">
@@ -27229,7 +27260,7 @@
       </c>
       <c r="J216" s="11" t="inlineStr">
         <is>
-          <t>PES-40</t>
+          <t>PES-48</t>
         </is>
       </c>
       <c r="K216" s="11" t="inlineStr">
@@ -27284,7 +27315,7 @@
       </c>
       <c r="J217" s="11" t="inlineStr">
         <is>
-          <t>PES-40</t>
+          <t>PES-48</t>
         </is>
       </c>
       <c r="K217" s="11" t="inlineStr">
@@ -27339,7 +27370,7 @@
       </c>
       <c r="J218" s="11" t="inlineStr">
         <is>
-          <t>PES-40</t>
+          <t>PES-48</t>
         </is>
       </c>
       <c r="K218" s="11" t="inlineStr">
@@ -27394,7 +27425,7 @@
       </c>
       <c r="J219" s="11" t="inlineStr">
         <is>
-          <t>PES-40</t>
+          <t>PES-48</t>
         </is>
       </c>
       <c r="K219" s="11" t="inlineStr">
@@ -27449,7 +27480,7 @@
       </c>
       <c r="J220" s="11" t="inlineStr">
         <is>
-          <t>PES-40</t>
+          <t>PES-48</t>
         </is>
       </c>
       <c r="K220" s="11" t="inlineStr">
@@ -27504,7 +27535,7 @@
       </c>
       <c r="J221" s="11" t="inlineStr">
         <is>
-          <t>PES-40</t>
+          <t>PES-48</t>
         </is>
       </c>
       <c r="K221" s="11" t="inlineStr">
@@ -27563,7 +27594,7 @@
       </c>
       <c r="J222" s="11" t="inlineStr">
         <is>
-          <t>PES-40</t>
+          <t>PES-48</t>
         </is>
       </c>
       <c r="K222" s="11" t="inlineStr">
@@ -27618,7 +27649,7 @@
       </c>
       <c r="J223" s="11" t="inlineStr">
         <is>
-          <t>PES-40</t>
+          <t>PES-48</t>
         </is>
       </c>
       <c r="K223" s="11" t="inlineStr">
@@ -27673,7 +27704,7 @@
       </c>
       <c r="J224" s="11" t="inlineStr">
         <is>
-          <t>PES-40</t>
+          <t>PES-48</t>
         </is>
       </c>
       <c r="K224" s="11" t="inlineStr">
@@ -27728,7 +27759,7 @@
       </c>
       <c r="J225" s="11" t="inlineStr">
         <is>
-          <t>PES-40</t>
+          <t>PES-48</t>
         </is>
       </c>
       <c r="K225" s="11" t="inlineStr">
@@ -27783,7 +27814,7 @@
       </c>
       <c r="J226" s="11" t="inlineStr">
         <is>
-          <t>PES-40</t>
+          <t>PES-48</t>
         </is>
       </c>
       <c r="K226" s="11" t="inlineStr">
@@ -27838,7 +27869,7 @@
       </c>
       <c r="J227" s="11" t="inlineStr">
         <is>
-          <t>PES-40</t>
+          <t>PES-48</t>
         </is>
       </c>
       <c r="K227" s="11" t="inlineStr">
@@ -27893,7 +27924,7 @@
       </c>
       <c r="J228" s="11" t="inlineStr">
         <is>
-          <t>PES-40</t>
+          <t>PES-48</t>
         </is>
       </c>
       <c r="K228" s="11" t="inlineStr">
@@ -27948,7 +27979,7 @@
       </c>
       <c r="J229" s="11" t="inlineStr">
         <is>
-          <t>PES-40</t>
+          <t>PES-48</t>
         </is>
       </c>
       <c r="K229" s="11" t="inlineStr">
@@ -28003,7 +28034,7 @@
       </c>
       <c r="J230" s="11" t="inlineStr">
         <is>
-          <t>PES-40</t>
+          <t>PES-48</t>
         </is>
       </c>
       <c r="K230" s="11" t="inlineStr">
@@ -28058,7 +28089,7 @@
       </c>
       <c r="J231" s="11" t="inlineStr">
         <is>
-          <t>PES-40</t>
+          <t>PES-48</t>
         </is>
       </c>
       <c r="K231" s="11" t="inlineStr">
@@ -28113,7 +28144,7 @@
       </c>
       <c r="J232" s="11" t="inlineStr">
         <is>
-          <t>PES-40</t>
+          <t>PES-48</t>
         </is>
       </c>
       <c r="K232" s="11" t="inlineStr">
@@ -28168,7 +28199,7 @@
       </c>
       <c r="J233" s="11" t="inlineStr">
         <is>
-          <t>PES-40</t>
+          <t>PES-48</t>
         </is>
       </c>
       <c r="K233" s="11" t="inlineStr">
@@ -28223,7 +28254,7 @@
       </c>
       <c r="J234" s="11" t="inlineStr">
         <is>
-          <t>PES-40</t>
+          <t>PES-48</t>
         </is>
       </c>
       <c r="K234" s="11" t="inlineStr">
@@ -28278,7 +28309,7 @@
       </c>
       <c r="J235" s="11" t="inlineStr">
         <is>
-          <t>PES-40</t>
+          <t>PES-48</t>
         </is>
       </c>
       <c r="K235" s="11" t="inlineStr">
@@ -28333,7 +28364,7 @@
       </c>
       <c r="J236" s="11" t="inlineStr">
         <is>
-          <t>PES-40</t>
+          <t>PES-48</t>
         </is>
       </c>
       <c r="K236" s="11" t="inlineStr">
@@ -28388,7 +28419,7 @@
       </c>
       <c r="J237" s="11" t="inlineStr">
         <is>
-          <t>PES-40</t>
+          <t>PES-48</t>
         </is>
       </c>
       <c r="K237" s="11" t="inlineStr">
@@ -28443,7 +28474,7 @@
       </c>
       <c r="J238" s="11" t="inlineStr">
         <is>
-          <t>PES-40</t>
+          <t>PES-48</t>
         </is>
       </c>
       <c r="K238" s="11" t="inlineStr">
@@ -28498,7 +28529,7 @@
       </c>
       <c r="J239" s="11" t="inlineStr">
         <is>
-          <t>PES-40</t>
+          <t>PES-48</t>
         </is>
       </c>
       <c r="K239" s="11" t="inlineStr">
@@ -28553,7 +28584,7 @@
       </c>
       <c r="J240" s="11" t="inlineStr">
         <is>
-          <t>PES-40</t>
+          <t>PES-48</t>
         </is>
       </c>
       <c r="K240" s="11" t="inlineStr">
@@ -28612,7 +28643,7 @@
       </c>
       <c r="J241" s="11" t="inlineStr">
         <is>
-          <t>PES-40</t>
+          <t>PES-48</t>
         </is>
       </c>
       <c r="K241" s="11" t="inlineStr">
@@ -28667,7 +28698,7 @@
       </c>
       <c r="J242" s="11" t="inlineStr">
         <is>
-          <t>PES-40</t>
+          <t>PES-48</t>
         </is>
       </c>
       <c r="K242" s="11" t="inlineStr">
@@ -28726,7 +28757,7 @@
       </c>
       <c r="J243" s="11" t="inlineStr">
         <is>
-          <t>PES-40</t>
+          <t>PES-48</t>
         </is>
       </c>
       <c r="K243" s="11" t="inlineStr">
@@ -28781,7 +28812,7 @@
       </c>
       <c r="J244" s="11" t="inlineStr">
         <is>
-          <t>PES-40</t>
+          <t>PES-48</t>
         </is>
       </c>
       <c r="K244" s="11" t="inlineStr">
@@ -28836,7 +28867,7 @@
       </c>
       <c r="J245" s="11" t="inlineStr">
         <is>
-          <t>PES-40</t>
+          <t>PES-48</t>
         </is>
       </c>
       <c r="K245" s="11" t="inlineStr">
@@ -28891,7 +28922,7 @@
       </c>
       <c r="J246" s="11" t="inlineStr">
         <is>
-          <t>PES-40</t>
+          <t>PES-48</t>
         </is>
       </c>
       <c r="K246" s="11" t="inlineStr">
@@ -29165,7 +29196,7 @@
         <v>41</v>
       </c>
       <c r="D6" s="11" t="n">
-        <v>81.09999999999999</v>
+        <v>81.3</v>
       </c>
       <c r="E6" s="11" t="n">
         <v>0</v>
@@ -29217,7 +29248,7 @@
         <v>17</v>
       </c>
       <c r="D7" s="11" t="n">
-        <v>79.2</v>
+        <v>79.40000000000001</v>
       </c>
       <c r="E7" s="11" t="n">
         <v>63</v>
@@ -29269,7 +29300,7 @@
         <v>15</v>
       </c>
       <c r="D8" s="11" t="n">
-        <v>77.59999999999999</v>
+        <v>76.5</v>
       </c>
       <c r="E8" s="11" t="n">
         <v>0</v>
@@ -29284,10 +29315,10 @@
         <v>600</v>
       </c>
       <c r="I8" s="11" t="n">
-        <v>0.93</v>
+        <v>0.92</v>
       </c>
       <c r="J8" s="11" t="n">
-        <v>0.63</v>
+        <v>0.62</v>
       </c>
       <c r="K8" s="11" t="n">
         <v>0.18</v>
@@ -29321,7 +29352,7 @@
         <v>4</v>
       </c>
       <c r="D9" s="11" t="n">
-        <v>30.4</v>
+        <v>30</v>
       </c>
       <c r="E9" s="11" t="n">
         <v>39</v>
@@ -29336,7 +29367,7 @@
         <v>350</v>
       </c>
       <c r="I9" s="11" t="n">
-        <v>0.37</v>
+        <v>0.36</v>
       </c>
       <c r="J9" s="11" t="n">
         <v>0.25</v>
@@ -29345,7 +29376,7 @@
         <v>0.07000000000000001</v>
       </c>
       <c r="L9" s="11" t="n">
-        <v>0.24</v>
+        <v>0.23</v>
       </c>
       <c r="M9" s="11" t="n">
         <v>0.02</v>
@@ -29373,7 +29404,7 @@
         <v>22</v>
       </c>
       <c r="D10" s="11" t="n">
-        <v>82.59999999999999</v>
+        <v>82.8</v>
       </c>
       <c r="E10" s="11" t="n">
         <v>0</v>
@@ -29391,13 +29422,13 @@
         <v>0.99</v>
       </c>
       <c r="J10" s="11" t="n">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="K10" s="11" t="n">
         <v>0.19</v>
       </c>
       <c r="L10" s="11" t="n">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="M10" s="11" t="n">
         <v>0.08</v>
@@ -29425,7 +29456,7 @@
         <v>14</v>
       </c>
       <c r="D11" s="11" t="n">
-        <v>82.59999999999999</v>
+        <v>82.8</v>
       </c>
       <c r="E11" s="11" t="n">
         <v>56</v>
@@ -29443,7 +29474,7 @@
         <v>0.99</v>
       </c>
       <c r="J11" s="11" t="n">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="K11" s="11" t="n">
         <v>0.19</v>
@@ -29477,7 +29508,7 @@
         <v>27</v>
       </c>
       <c r="D12" s="11" t="n">
-        <v>77.2</v>
+        <v>77</v>
       </c>
       <c r="E12" s="11" t="n">
         <v>0</v>
@@ -29492,7 +29523,7 @@
         <v>600</v>
       </c>
       <c r="I12" s="11" t="n">
-        <v>0.93</v>
+        <v>0.92</v>
       </c>
       <c r="J12" s="11" t="n">
         <v>0.63</v>
@@ -29529,7 +29560,7 @@
         <v>10</v>
       </c>
       <c r="D13" s="11" t="n">
-        <v>42.9</v>
+        <v>42.8</v>
       </c>
       <c r="E13" s="11" t="n">
         <v>33</v>
@@ -29581,25 +29612,25 @@
         <v>45</v>
       </c>
       <c r="D14" s="11" t="n">
-        <v>74.8</v>
+        <v>75.40000000000001</v>
       </c>
       <c r="E14" s="11" t="n">
         <v>0</v>
       </c>
       <c r="F14" s="11" t="n">
-        <v>8.5</v>
+        <v>12</v>
       </c>
       <c r="G14" s="11" t="n">
-        <v>32</v>
+        <v>39</v>
       </c>
       <c r="H14" s="11" t="n">
         <v>600</v>
       </c>
       <c r="I14" s="11" t="n">
-        <v>0.9</v>
+        <v>0.64</v>
       </c>
       <c r="J14" s="11" t="n">
-        <v>0.61</v>
+        <v>0.49</v>
       </c>
       <c r="K14" s="11" t="n">
         <v>0.18</v>
@@ -29633,7 +29664,7 @@
         <v>5</v>
       </c>
       <c r="D15" s="11" t="n">
-        <v>113.9</v>
+        <v>114.9</v>
       </c>
       <c r="E15" s="11" t="n">
         <v>49</v>
@@ -29645,25 +29676,25 @@
         <v>39</v>
       </c>
       <c r="H15" s="11" t="n">
-        <v>450</v>
+        <v>350</v>
       </c>
       <c r="I15" s="11" t="n">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="J15" s="11" t="n">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="K15" s="11" t="n">
         <v>0.28</v>
       </c>
       <c r="L15" s="11" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.82</v>
       </c>
       <c r="M15" s="11" t="n">
         <v>0.24</v>
       </c>
       <c r="N15" s="11" t="n">
-        <v>0.73</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="O15" s="11" t="str"/>
       <c r="P15" s="11" t="str"/>

--- a/public/docs_ban_mong/HOBANMONG_THONG_KE_VAT_TU_NEO.xlsx
+++ b/public/docs_ban_mong/HOBANMONG_THONG_KE_VAT_TU_NEO.xlsx
@@ -1645,7 +1645,7 @@
     <row r="2" ht="34" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Lấy số từ engine tính toán (gió 20 m/s): 215 dây (186 dây bờ, 29 dây đáy), 186 cọc khoan nhồi D350, 19 đế BTCT + 76 vít xoắn. Mỗi dây chia 2 nhánh 3,5 m tại tấm chia tam giác, góc giữa 2 nhánh 60°, 2 bích bè cách nhau 3,50 m.</t>
+          <t>Lấy số từ engine tính toán (gió 20 m/s): 215 dây (188 dây bờ, 27 dây đáy), 188 cọc khoan nhồi D350, 17 đế BTCT + 68 vít xoắn. Mỗi dây chia 2 nhánh 3,5 m tại tấm chia tam giác, góc giữa 2 nhánh 60°, 2 bích bè cách nhau 3,50 m.</t>
         </is>
       </c>
     </row>
@@ -1744,7 +1744,7 @@
         </is>
       </c>
       <c r="F7" s="8" t="n">
-        <v>1849.2</v>
+        <v>1939.3</v>
       </c>
       <c r="G7" s="6" t="inlineStr">
         <is>
@@ -1752,11 +1752,11 @@
         </is>
       </c>
       <c r="H7" s="8" t="n">
-        <v>1941.7</v>
+        <v>2036.3</v>
       </c>
       <c r="I7" s="7" t="inlineStr">
         <is>
-          <t>49 dây; từ tấm chia Y tới chốt cọc bờ (dài nhất ở MNC)</t>
+          <t>51 dây; từ tấm chia Y tới chốt cọc bờ (dài nhất ở MNC)</t>
         </is>
       </c>
     </row>
@@ -1855,7 +1855,7 @@
         </is>
       </c>
       <c r="F10" s="8" t="n">
-        <v>340.2</v>
+        <v>293.2</v>
       </c>
       <c r="G10" s="6" t="inlineStr">
         <is>
@@ -1863,11 +1863,11 @@
         </is>
       </c>
       <c r="H10" s="8" t="n">
-        <v>357.2</v>
+        <v>307.9</v>
       </c>
       <c r="I10" s="7" t="inlineStr">
         <is>
-          <t>13 dây; tới tai neo đế (dài nhất ở MNLKT). ĐO CAO ĐỘ ĐÁY trước khi cắt</t>
+          <t>11 dây; tới tai neo đế (dài nhất ở MNLKT). ĐO CAO ĐỘ ĐÁY trước khi cắt</t>
         </is>
       </c>
     </row>
@@ -2133,7 +2133,7 @@
         </is>
       </c>
       <c r="F18" s="8" t="n">
-        <v>1227.6</v>
+        <v>1240.8</v>
       </c>
       <c r="G18" s="6" t="inlineStr">
         <is>
@@ -2141,11 +2141,11 @@
         </is>
       </c>
       <c r="H18" s="8" t="n">
-        <v>1227.6</v>
+        <v>1240.8</v>
       </c>
       <c r="I18" s="7" t="inlineStr">
         <is>
-          <t>186 cọc; 171/186 điểm đất thấp hơn MNDB → thi công mùa nước thấp</t>
+          <t>188 cọc; 172/188 điểm đất thấp hơn MNDB → thi công mùa nước thấp</t>
         </is>
       </c>
     </row>
@@ -2170,7 +2170,7 @@
         </is>
       </c>
       <c r="F19" s="8" t="n">
-        <v>118.1</v>
+        <v>119.4</v>
       </c>
       <c r="G19" s="6" t="inlineStr">
         <is>
@@ -2178,7 +2178,7 @@
         </is>
       </c>
       <c r="H19" s="8" t="n">
-        <v>124</v>
+        <v>125.3</v>
       </c>
       <c r="I19" s="7" t="inlineStr">
         <is>
@@ -2207,7 +2207,7 @@
         </is>
       </c>
       <c r="F20" s="9" t="n">
-        <v>33157</v>
+        <v>33540</v>
       </c>
       <c r="G20" s="6" t="inlineStr">
         <is>
@@ -2215,7 +2215,7 @@
         </is>
       </c>
       <c r="H20" s="9" t="n">
-        <v>34152</v>
+        <v>34547</v>
       </c>
       <c r="I20" s="7" t="inlineStr">
         <is>
@@ -2244,7 +2244,7 @@
         </is>
       </c>
       <c r="F21" s="9" t="n">
-        <v>3013</v>
+        <v>3045</v>
       </c>
       <c r="G21" s="6" t="inlineStr">
         <is>
@@ -2252,7 +2252,7 @@
         </is>
       </c>
       <c r="H21" s="9" t="n">
-        <v>3164</v>
+        <v>3198</v>
       </c>
       <c r="I21" s="7" t="inlineStr">
         <is>
@@ -2281,7 +2281,7 @@
         </is>
       </c>
       <c r="F22" s="9" t="n">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="G22" s="6" t="inlineStr">
         <is>
@@ -2289,11 +2289,11 @@
         </is>
       </c>
       <c r="H22" s="9" t="n">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="I22" s="7" t="inlineStr">
         <is>
-          <t>186 đầu cọc đơn + 0 đài cọc đôi; thiết kế sơ bộ src/lib/calc/shorePileHead.ts (γ = 1.2, T của loại cọc: lực của bè, hoặc lực thiết kế của cọc đơn ở điểm dây nhẹ), mức sử dụng lớn nhất 0,97</t>
+          <t>188 đầu cọc đơn + 0 đài cọc đôi; thiết kế sơ bộ src/lib/calc/shorePileHead.ts (γ = 1.2, T của loại cọc: lực của bè, hoặc lực thiết kế của cọc đơn ở điểm dây nhẹ), mức sử dụng lớn nhất 0,97</t>
         </is>
       </c>
     </row>
@@ -2318,7 +2318,7 @@
         </is>
       </c>
       <c r="F23" s="9" t="n">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="G23" s="6" t="inlineStr">
         <is>
@@ -2326,7 +2326,7 @@
         </is>
       </c>
       <c r="H23" s="9" t="n">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="I23" s="7" t="inlineStr">
         <is>
@@ -2355,7 +2355,7 @@
         </is>
       </c>
       <c r="F24" s="9" t="n">
-        <v>744</v>
+        <v>752</v>
       </c>
       <c r="G24" s="6" t="inlineStr">
         <is>
@@ -2363,7 +2363,7 @@
         </is>
       </c>
       <c r="H24" s="9" t="n">
-        <v>759</v>
+        <v>768</v>
       </c>
       <c r="I24" s="7" t="inlineStr">
         <is>
@@ -2402,7 +2402,7 @@
       <c r="C26" s="6" t="n"/>
       <c r="D26" s="7" t="inlineStr">
         <is>
-          <t>C25/30 chống thấm; 2 đế 2,50 m, 2 đế 2,75 m, 2 đế 3,50 m, 1 đế 3,75 m, 6 đế 4,00 m, 3 đế 4,25 m, 2 đế 5,75 m, 1 đế 6,00 m; dày 0,4 / 0,5 m</t>
+          <t>C25/30 chống thấm; 2 đế 2,75 m, 2 đế 3,50 m, 1 đế 3,75 m, 6 đế 4,00 m, 3 đế 4,25 m, 2 đế 5,75 m, 1 đế 6,00 m; dày 0,4 / 0,5 m</t>
         </is>
       </c>
       <c r="E26" s="6" t="inlineStr">
@@ -2411,7 +2411,7 @@
         </is>
       </c>
       <c r="F26" s="8" t="n">
-        <v>133.2</v>
+        <v>128.3</v>
       </c>
       <c r="G26" s="6" t="inlineStr">
         <is>
@@ -2419,11 +2419,11 @@
         </is>
       </c>
       <c r="H26" s="8" t="n">
-        <v>137.2</v>
+        <v>132.1</v>
       </c>
       <c r="I26" s="7" t="inlineStr">
         <is>
-          <t>19 đế, đế nặng nhất 36,7 t khi cẩu</t>
+          <t>17 đế, đế nặng nhất 36,7 t khi cẩu</t>
         </is>
       </c>
     </row>
@@ -2448,7 +2448,7 @@
         </is>
       </c>
       <c r="F27" s="9" t="n">
-        <v>5859</v>
+        <v>5620</v>
       </c>
       <c r="G27" s="6" t="inlineStr">
         <is>
@@ -2456,7 +2456,7 @@
         </is>
       </c>
       <c r="H27" s="9" t="n">
-        <v>6035</v>
+        <v>5789</v>
       </c>
       <c r="I27" s="7" t="inlineStr">
         <is>
@@ -2485,7 +2485,7 @@
         </is>
       </c>
       <c r="F28" s="8" t="n">
-        <v>282.8</v>
+        <v>253.2</v>
       </c>
       <c r="G28" s="6" t="inlineStr">
         <is>
@@ -2493,11 +2493,11 @@
         </is>
       </c>
       <c r="H28" s="8" t="n">
-        <v>296.9</v>
+        <v>265.9</v>
       </c>
       <c r="I28" s="7" t="inlineStr">
         <is>
-          <t>76 vít</t>
+          <t>68 vít</t>
         </is>
       </c>
     </row>
@@ -2522,7 +2522,7 @@
         </is>
       </c>
       <c r="F29" s="9" t="n">
-        <v>76</v>
+        <v>68</v>
       </c>
       <c r="G29" s="6" t="inlineStr">
         <is>
@@ -2530,7 +2530,7 @@
         </is>
       </c>
       <c r="H29" s="9" t="n">
-        <v>76</v>
+        <v>68</v>
       </c>
       <c r="I29" s="7" t="inlineStr">
         <is>
@@ -2550,7 +2550,7 @@
       <c r="C30" s="6" t="n"/>
       <c r="D30" s="7" t="inlineStr">
         <is>
-          <t>Bản mã SS400 400×400×20, tai t = 25 lỗ Ø32 / Ø36 / Ø39 / Ø42 / Ø46, 4Φ22 (28 bộ), 6Φ22 (1 bộ) L = 350–450 móc vào lưới đáy đế; hàn góc 10 mm (28 bộ), 12 mm (1 bộ) hai phía; đặt sẵn khi đúc đế</t>
+          <t>Bản mã SS400 400×400×20, tai t = 25 lỗ Ø32 / Ø36 / Ø39 / Ø42 / Ø46, 4Φ22 (26 bộ), 6Φ22 (1 bộ) L = 350–450 móc vào lưới đáy đế; hàn góc 10 mm (26 bộ), 12 mm (1 bộ) hai phía; đặt sẵn khi đúc đế</t>
         </is>
       </c>
       <c r="E30" s="6" t="inlineStr">
@@ -2559,7 +2559,7 @@
         </is>
       </c>
       <c r="F30" s="9" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="G30" s="6" t="inlineStr">
         <is>
@@ -2567,11 +2567,11 @@
         </is>
       </c>
       <c r="H30" s="9" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="I30" s="7" t="inlineStr">
         <is>
-          <t>10 đế dùng chung có 2 bộ, 9 đế đơn có 1 bộ; tính cho lực lớn nhất của chính dây, cáp dốc tới 68° (có thành phần nhổ); mức sử dụng lớn nhất 1,00</t>
+          <t>10 đế dùng chung có 2 bộ, 7 đế đơn có 1 bộ; tính cho lực lớn nhất của chính dây, cáp dốc tới 68° (có thành phần nhổ); mức sử dụng lớn nhất 1,00</t>
         </is>
       </c>
     </row>
@@ -2967,7 +2967,7 @@
         </is>
       </c>
       <c r="F42" s="9" t="n">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="G42" s="6" t="inlineStr">
         <is>
@@ -2975,7 +2975,7 @@
         </is>
       </c>
       <c r="H42" s="9" t="n">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="I42" s="7" t="inlineStr">
         <is>
@@ -3041,7 +3041,7 @@
         </is>
       </c>
       <c r="F44" s="9" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="G44" s="6" t="inlineStr">
         <is>
@@ -3049,7 +3049,7 @@
         </is>
       </c>
       <c r="H44" s="9" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="I44" s="7" t="inlineStr">
         <is>
@@ -3127,7 +3127,7 @@
       </c>
       <c r="I46" s="7" t="inlineStr">
         <is>
-          <t>Không bắt buộc, chưa tính toán; nếu dùng: 29 quả, treo cách đế 3 m</t>
+          <t>Không bắt buộc, chưa tính toán; nếu dùng: 27 quả, treo cách đế 3 m</t>
         </is>
       </c>
     </row>
@@ -3275,15 +3275,15 @@
         </is>
       </c>
       <c r="F50" s="9" t="n">
+        <v>17</v>
+      </c>
+      <c r="G50" s="6" t="inlineStr">
+        <is>
+          <t>10%</t>
+        </is>
+      </c>
+      <c r="H50" s="9" t="n">
         <v>19</v>
-      </c>
-      <c r="G50" s="6" t="inlineStr">
-        <is>
-          <t>10%</t>
-        </is>
-      </c>
-      <c r="H50" s="9" t="n">
-        <v>21</v>
       </c>
       <c r="I50" s="7" t="inlineStr">
         <is>
@@ -3347,7 +3347,7 @@
       </c>
       <c r="I52" s="7" t="inlineStr">
         <is>
-          <t>Yêu cầu của mô hình cân bằng (mooringEquilibrium.ts): dây luôn vừa căng ở mọi mực nước. Đối trọng treo một mình KHÔNG giữ được bè: nếu không khóa, bè trôi 3,6–6,7 m hết hành trình dư rồi lực dây vọt tới 89–383 kN</t>
+          <t>Yêu cầu của mô hình cân bằng (mooringEquilibrium.ts): dây luôn vừa căng ở mọi mực nước. Đối trọng treo một mình KHÔNG giữ được bè: nếu không khóa, bè trôi 3,6–6,7 m hết hành trình dư rồi lực dây vọt tới 90–383 kN</t>
         </is>
       </c>
     </row>
@@ -3469,7 +3469,7 @@
         </is>
       </c>
       <c r="F56" s="9" t="n">
-        <v>17036</v>
+        <v>17419</v>
       </c>
       <c r="G56" s="6" t="inlineStr">
         <is>
@@ -3477,7 +3477,7 @@
         </is>
       </c>
       <c r="H56" s="9" t="n">
-        <v>17547</v>
+        <v>17942</v>
       </c>
       <c r="I56" s="7" t="inlineStr">
         <is>
@@ -3543,7 +3543,7 @@
         </is>
       </c>
       <c r="F58" s="9" t="n">
-        <v>3013</v>
+        <v>3045</v>
       </c>
       <c r="G58" s="6" t="inlineStr">
         <is>
@@ -3551,7 +3551,7 @@
         </is>
       </c>
       <c r="H58" s="9" t="n">
-        <v>3164</v>
+        <v>3198</v>
       </c>
       <c r="I58" s="7" t="inlineStr">
         <is>
@@ -3580,7 +3580,7 @@
         </is>
       </c>
       <c r="F59" s="9" t="n">
-        <v>5859</v>
+        <v>5620</v>
       </c>
       <c r="G59" s="6" t="inlineStr">
         <is>
@@ -3588,7 +3588,7 @@
         </is>
       </c>
       <c r="H59" s="9" t="n">
-        <v>6035</v>
+        <v>5789</v>
       </c>
       <c r="I59" s="7" t="inlineStr">
         <is>
@@ -3621,7 +3621,7 @@
         </is>
       </c>
       <c r="F60" s="9" t="n">
-        <v>2929</v>
+        <v>2623</v>
       </c>
       <c r="G60" s="6" t="inlineStr">
         <is>
@@ -3629,7 +3629,7 @@
         </is>
       </c>
       <c r="H60" s="9" t="n">
-        <v>3076</v>
+        <v>2754</v>
       </c>
       <c r="I60" s="7" t="inlineStr">
         <is>
@@ -3658,7 +3658,7 @@
         </is>
       </c>
       <c r="F61" s="9" t="n">
-        <v>6386</v>
+        <v>6382</v>
       </c>
       <c r="G61" s="6" t="inlineStr">
         <is>
@@ -3666,7 +3666,7 @@
         </is>
       </c>
       <c r="H61" s="9" t="n">
-        <v>6706</v>
+        <v>6702</v>
       </c>
       <c r="I61" s="7" t="inlineStr">
         <is>
@@ -3695,7 +3695,7 @@
         </is>
       </c>
       <c r="F62" s="9" t="n">
-        <v>1465</v>
+        <v>1471</v>
       </c>
       <c r="G62" s="6" t="inlineStr">
         <is>
@@ -3703,7 +3703,7 @@
         </is>
       </c>
       <c r="H62" s="9" t="n">
-        <v>1509</v>
+        <v>1515</v>
       </c>
       <c r="I62" s="7" t="inlineStr">
         <is>
@@ -3736,7 +3736,7 @@
         </is>
       </c>
       <c r="F63" s="9" t="n">
-        <v>52809</v>
+        <v>52680</v>
       </c>
       <c r="G63" s="6" t="inlineStr">
         <is>
@@ -3744,7 +3744,7 @@
         </is>
       </c>
       <c r="H63" s="9" t="n">
-        <v>54643</v>
+        <v>54506</v>
       </c>
       <c r="I63" s="7" t="inlineStr">
         <is>
@@ -3866,7 +3866,7 @@
         </is>
       </c>
       <c r="C5" s="11" t="n">
-        <v>17036</v>
+        <v>17419</v>
       </c>
       <c r="D5" s="11" t="inlineStr">
         <is>
@@ -3874,7 +3874,7 @@
         </is>
       </c>
       <c r="E5" s="11" t="n">
-        <v>17547</v>
+        <v>17942</v>
       </c>
       <c r="F5" s="11" t="inlineStr">
         <is>
@@ -3922,7 +3922,7 @@
         </is>
       </c>
       <c r="C7" s="11" t="n">
-        <v>3013</v>
+        <v>3045</v>
       </c>
       <c r="D7" s="11" t="inlineStr">
         <is>
@@ -3930,7 +3930,7 @@
         </is>
       </c>
       <c r="E7" s="11" t="n">
-        <v>3164</v>
+        <v>3198</v>
       </c>
       <c r="F7" s="11" t="inlineStr">
         <is>
@@ -3950,7 +3950,7 @@
         </is>
       </c>
       <c r="C8" s="11" t="n">
-        <v>5859</v>
+        <v>5620</v>
       </c>
       <c r="D8" s="11" t="inlineStr">
         <is>
@@ -3958,7 +3958,7 @@
         </is>
       </c>
       <c r="E8" s="11" t="n">
-        <v>6035</v>
+        <v>5789</v>
       </c>
       <c r="F8" s="11" t="inlineStr">
         <is>
@@ -3978,7 +3978,7 @@
         </is>
       </c>
       <c r="C9" s="11" t="n">
-        <v>2929</v>
+        <v>2623</v>
       </c>
       <c r="D9" s="11" t="inlineStr">
         <is>
@@ -3986,7 +3986,7 @@
         </is>
       </c>
       <c r="E9" s="11" t="n">
-        <v>3076</v>
+        <v>2754</v>
       </c>
       <c r="F9" s="11" t="inlineStr">
         <is>
@@ -4006,7 +4006,7 @@
         </is>
       </c>
       <c r="C10" s="11" t="n">
-        <v>6386</v>
+        <v>6382</v>
       </c>
       <c r="D10" s="11" t="inlineStr">
         <is>
@@ -4014,7 +4014,7 @@
         </is>
       </c>
       <c r="E10" s="11" t="n">
-        <v>6706</v>
+        <v>6702</v>
       </c>
       <c r="F10" s="11" t="inlineStr">
         <is>
@@ -4034,7 +4034,7 @@
         </is>
       </c>
       <c r="C11" s="11" t="n">
-        <v>1465</v>
+        <v>1471</v>
       </c>
       <c r="D11" s="11" t="inlineStr">
         <is>
@@ -4042,7 +4042,7 @@
         </is>
       </c>
       <c r="E11" s="11" t="n">
-        <v>1509</v>
+        <v>1515</v>
       </c>
       <c r="F11" s="11" t="inlineStr">
         <is>
@@ -4058,11 +4058,11 @@
       </c>
       <c r="B12" s="11" t="str"/>
       <c r="C12" s="11" t="n">
-        <v>52809</v>
+        <v>52680</v>
       </c>
       <c r="D12" s="11" t="str"/>
       <c r="E12" s="11" t="n">
-        <v>54643</v>
+        <v>54506</v>
       </c>
       <c r="F12" s="11" t="str"/>
     </row>
@@ -4309,7 +4309,7 @@
         </is>
       </c>
       <c r="B6" s="11" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C6" s="11" t="n">
         <v>350</v>
@@ -4318,10 +4318,10 @@
         <v>6.6</v>
       </c>
       <c r="E6" s="11" t="n">
-        <v>99</v>
+        <v>112.2</v>
       </c>
       <c r="F6" s="11" t="n">
-        <v>9.52</v>
+        <v>10.79</v>
       </c>
       <c r="G6" s="11" t="inlineStr">
         <is>
@@ -4329,31 +4329,31 @@
         </is>
       </c>
       <c r="H6" s="11" t="n">
-        <v>2871</v>
+        <v>3254</v>
       </c>
       <c r="I6" s="11" t="n">
-        <v>243</v>
+        <v>275</v>
       </c>
       <c r="J6" s="11" t="n">
-        <v>107</v>
+        <v>122</v>
       </c>
       <c r="K6" s="11" t="n">
-        <v>442</v>
+        <v>500</v>
       </c>
       <c r="L6" s="11" t="n">
         <v>0</v>
       </c>
       <c r="M6" s="11" t="n">
-        <v>3663</v>
+        <v>4152</v>
       </c>
       <c r="N6" s="11" t="n">
-        <v>76.5</v>
+        <v>78.7</v>
       </c>
       <c r="O6" s="11" t="n">
-        <v>0.66</v>
+        <v>0.68</v>
       </c>
       <c r="P6" s="11" t="n">
-        <v>0.91</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="7">
@@ -4525,34 +4525,34 @@
         </is>
       </c>
       <c r="B10" s="11" t="n">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="C10" s="11" t="str"/>
       <c r="D10" s="11" t="str"/>
       <c r="E10" s="11" t="n">
-        <v>1227.6</v>
+        <v>1240.8</v>
       </c>
       <c r="F10" s="11" t="n">
-        <v>118.11</v>
+        <v>119.38</v>
       </c>
       <c r="G10" s="11" t="str"/>
       <c r="H10" s="11" t="n">
-        <v>33157</v>
+        <v>33540</v>
       </c>
       <c r="I10" s="11" t="n">
-        <v>3013</v>
+        <v>3045</v>
       </c>
       <c r="J10" s="11" t="n">
-        <v>1332</v>
+        <v>1346</v>
       </c>
       <c r="K10" s="11" t="n">
-        <v>5475</v>
+        <v>5534</v>
       </c>
       <c r="L10" s="11" t="n">
         <v>0</v>
       </c>
       <c r="M10" s="11" t="n">
-        <v>42977</v>
+        <v>43466</v>
       </c>
       <c r="N10" s="11" t="str"/>
       <c r="O10" s="11" t="str"/>
@@ -4569,7 +4569,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L189"/>
+  <dimension ref="A1:L191"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6.83203125" customWidth="1" min="1" max="1"/>
@@ -4588,7 +4588,7 @@
     <row r="1">
       <c r="A1" s="10" t="inlineStr">
         <is>
-          <t>CỌC KHOAN NHỒI — TỪNG ĐIỂM NEO BỜ (186 điểm, 186 cọc)</t>
+          <t>CỌC KHOAN NHỒI — TỪNG ĐIỂM NEO BỜ (188 điểm, 188 cọc)</t>
         </is>
       </c>
     </row>
@@ -8539,7 +8539,7 @@
       </c>
       <c r="B92" s="11" t="inlineStr">
         <is>
-          <t>BM-P112</t>
+          <t>BM-P111</t>
         </is>
       </c>
       <c r="C92" s="11" t="inlineStr">
@@ -8548,13 +8548,13 @@
         </is>
       </c>
       <c r="D92" s="11" t="n">
-        <v>49.61</v>
+        <v>44</v>
       </c>
       <c r="E92" s="11" t="n">
-        <v>130.87</v>
+        <v>147</v>
       </c>
       <c r="F92" s="11" t="n">
-        <v>662.26</v>
+        <v>663.08</v>
       </c>
       <c r="G92" s="11" t="n">
         <v>1</v>
@@ -8583,7 +8583,7 @@
       </c>
       <c r="B93" s="11" t="inlineStr">
         <is>
-          <t>BM-P114</t>
+          <t>BM-P112</t>
         </is>
       </c>
       <c r="C93" s="11" t="inlineStr">
@@ -8592,13 +8592,13 @@
         </is>
       </c>
       <c r="D93" s="11" t="n">
-        <v>48.41</v>
+        <v>49.61</v>
       </c>
       <c r="E93" s="11" t="n">
-        <v>140.31</v>
+        <v>130.87</v>
       </c>
       <c r="F93" s="11" t="n">
-        <v>662.3200000000001</v>
+        <v>662.26</v>
       </c>
       <c r="G93" s="11" t="n">
         <v>1</v>
@@ -8627,22 +8627,22 @@
       </c>
       <c r="B94" s="11" t="inlineStr">
         <is>
-          <t>BM-P115</t>
+          <t>BM-P113</t>
         </is>
       </c>
       <c r="C94" s="11" t="inlineStr">
         <is>
-          <t>BÈ 4</t>
+          <t>BÈ 3</t>
         </is>
       </c>
       <c r="D94" s="11" t="n">
-        <v>-18.45</v>
+        <v>88.95999999999999</v>
       </c>
       <c r="E94" s="11" t="n">
-        <v>-8.609999999999999</v>
+        <v>48.33</v>
       </c>
       <c r="F94" s="11" t="n">
-        <v>662.34</v>
+        <v>662.3200000000001</v>
       </c>
       <c r="G94" s="11" t="n">
         <v>1</v>
@@ -8652,11 +8652,11 @@
       </c>
       <c r="I94" s="11" t="inlineStr">
         <is>
-          <t>6Φ25 CB400-V</t>
+          <t>6Φ28 CB400-V</t>
         </is>
       </c>
       <c r="J94" s="11" t="n">
-        <v>152.6</v>
+        <v>191.4</v>
       </c>
       <c r="K94" s="11" t="n">
         <v>16.2</v>
@@ -8671,22 +8671,22 @@
       </c>
       <c r="B95" s="11" t="inlineStr">
         <is>
-          <t>BM-P116</t>
+          <t>BM-P114</t>
         </is>
       </c>
       <c r="C95" s="11" t="inlineStr">
         <is>
-          <t>BÈ 4</t>
+          <t>BÈ 3</t>
         </is>
       </c>
       <c r="D95" s="11" t="n">
-        <v>22.11</v>
+        <v>48.41</v>
       </c>
       <c r="E95" s="11" t="n">
-        <v>87.59999999999999</v>
+        <v>140.31</v>
       </c>
       <c r="F95" s="11" t="n">
-        <v>662.4</v>
+        <v>662.3200000000001</v>
       </c>
       <c r="G95" s="11" t="n">
         <v>1</v>
@@ -8696,11 +8696,11 @@
       </c>
       <c r="I95" s="11" t="inlineStr">
         <is>
-          <t>6Φ25 CB400-V</t>
+          <t>6Φ28 CB400-V</t>
         </is>
       </c>
       <c r="J95" s="11" t="n">
-        <v>152.6</v>
+        <v>191.4</v>
       </c>
       <c r="K95" s="11" t="n">
         <v>16.2</v>
@@ -8715,7 +8715,7 @@
       </c>
       <c r="B96" s="11" t="inlineStr">
         <is>
-          <t>BM-P117</t>
+          <t>BM-P115</t>
         </is>
       </c>
       <c r="C96" s="11" t="inlineStr">
@@ -8724,13 +8724,13 @@
         </is>
       </c>
       <c r="D96" s="11" t="n">
-        <v>-159.5</v>
+        <v>-18.45</v>
       </c>
       <c r="E96" s="11" t="n">
-        <v>133.5</v>
+        <v>-8.609999999999999</v>
       </c>
       <c r="F96" s="11" t="n">
-        <v>663.53</v>
+        <v>662.34</v>
       </c>
       <c r="G96" s="11" t="n">
         <v>1</v>
@@ -8759,7 +8759,7 @@
       </c>
       <c r="B97" s="11" t="inlineStr">
         <is>
-          <t>BM-P118</t>
+          <t>BM-P116</t>
         </is>
       </c>
       <c r="C97" s="11" t="inlineStr">
@@ -8768,13 +8768,13 @@
         </is>
       </c>
       <c r="D97" s="11" t="n">
-        <v>-6.61</v>
+        <v>22.11</v>
       </c>
       <c r="E97" s="11" t="n">
-        <v>18.31</v>
+        <v>87.59999999999999</v>
       </c>
       <c r="F97" s="11" t="n">
-        <v>662.34</v>
+        <v>662.4</v>
       </c>
       <c r="G97" s="11" t="n">
         <v>1</v>
@@ -8803,7 +8803,7 @@
       </c>
       <c r="B98" s="11" t="inlineStr">
         <is>
-          <t>BM-P119</t>
+          <t>BM-P117</t>
         </is>
       </c>
       <c r="C98" s="11" t="inlineStr">
@@ -8812,13 +8812,13 @@
         </is>
       </c>
       <c r="D98" s="11" t="n">
-        <v>8.15</v>
+        <v>-159.5</v>
       </c>
       <c r="E98" s="11" t="n">
-        <v>148.59</v>
+        <v>133.5</v>
       </c>
       <c r="F98" s="11" t="n">
-        <v>662.4</v>
+        <v>663.53</v>
       </c>
       <c r="G98" s="11" t="n">
         <v>1</v>
@@ -8847,7 +8847,7 @@
       </c>
       <c r="B99" s="11" t="inlineStr">
         <is>
-          <t>BM-P120</t>
+          <t>BM-P118</t>
         </is>
       </c>
       <c r="C99" s="11" t="inlineStr">
@@ -8856,13 +8856,13 @@
         </is>
       </c>
       <c r="D99" s="11" t="n">
-        <v>-11.91</v>
+        <v>-6.61</v>
       </c>
       <c r="E99" s="11" t="n">
-        <v>6.21</v>
+        <v>18.31</v>
       </c>
       <c r="F99" s="11" t="n">
-        <v>662.36</v>
+        <v>662.34</v>
       </c>
       <c r="G99" s="11" t="n">
         <v>1</v>
@@ -8891,7 +8891,7 @@
       </c>
       <c r="B100" s="11" t="inlineStr">
         <is>
-          <t>BM-P121</t>
+          <t>BM-P119</t>
         </is>
       </c>
       <c r="C100" s="11" t="inlineStr">
@@ -8900,13 +8900,13 @@
         </is>
       </c>
       <c r="D100" s="11" t="n">
-        <v>13.05</v>
+        <v>8.15</v>
       </c>
       <c r="E100" s="11" t="n">
-        <v>120.54</v>
+        <v>148.59</v>
       </c>
       <c r="F100" s="11" t="n">
-        <v>662.52</v>
+        <v>662.4</v>
       </c>
       <c r="G100" s="11" t="n">
         <v>1</v>
@@ -8935,7 +8935,7 @@
       </c>
       <c r="B101" s="11" t="inlineStr">
         <is>
-          <t>BM-P122</t>
+          <t>BM-P120</t>
         </is>
       </c>
       <c r="C101" s="11" t="inlineStr">
@@ -8944,13 +8944,13 @@
         </is>
       </c>
       <c r="D101" s="11" t="n">
-        <v>-20.53</v>
+        <v>-11.91</v>
       </c>
       <c r="E101" s="11" t="n">
-        <v>-41.32</v>
+        <v>6.21</v>
       </c>
       <c r="F101" s="11" t="n">
-        <v>666.83</v>
+        <v>662.36</v>
       </c>
       <c r="G101" s="11" t="n">
         <v>1</v>
@@ -8979,7 +8979,7 @@
       </c>
       <c r="B102" s="11" t="inlineStr">
         <is>
-          <t>BM-P123</t>
+          <t>BM-P121</t>
         </is>
       </c>
       <c r="C102" s="11" t="inlineStr">
@@ -8988,13 +8988,13 @@
         </is>
       </c>
       <c r="D102" s="11" t="n">
-        <v>-153.9</v>
+        <v>13.05</v>
       </c>
       <c r="E102" s="11" t="n">
-        <v>125.01</v>
+        <v>120.54</v>
       </c>
       <c r="F102" s="11" t="n">
-        <v>662.27</v>
+        <v>662.52</v>
       </c>
       <c r="G102" s="11" t="n">
         <v>1</v>
@@ -9023,7 +9023,7 @@
       </c>
       <c r="B103" s="11" t="inlineStr">
         <is>
-          <t>BM-P124</t>
+          <t>BM-P122</t>
         </is>
       </c>
       <c r="C103" s="11" t="inlineStr">
@@ -9032,13 +9032,13 @@
         </is>
       </c>
       <c r="D103" s="11" t="n">
-        <v>5.82</v>
+        <v>-20.53</v>
       </c>
       <c r="E103" s="11" t="n">
-        <v>50.02</v>
+        <v>-41.32</v>
       </c>
       <c r="F103" s="11" t="n">
-        <v>662.29</v>
+        <v>666.83</v>
       </c>
       <c r="G103" s="11" t="n">
         <v>1</v>
@@ -9067,7 +9067,7 @@
       </c>
       <c r="B104" s="11" t="inlineStr">
         <is>
-          <t>BM-P125</t>
+          <t>BM-P123</t>
         </is>
       </c>
       <c r="C104" s="11" t="inlineStr">
@@ -9076,13 +9076,13 @@
         </is>
       </c>
       <c r="D104" s="11" t="n">
-        <v>10.15</v>
+        <v>-153.9</v>
       </c>
       <c r="E104" s="11" t="n">
-        <v>136.21</v>
+        <v>125.01</v>
       </c>
       <c r="F104" s="11" t="n">
-        <v>662.26</v>
+        <v>662.27</v>
       </c>
       <c r="G104" s="11" t="n">
         <v>1</v>
@@ -9111,7 +9111,7 @@
       </c>
       <c r="B105" s="11" t="inlineStr">
         <is>
-          <t>BM-P126</t>
+          <t>BM-P124</t>
         </is>
       </c>
       <c r="C105" s="11" t="inlineStr">
@@ -9120,13 +9120,13 @@
         </is>
       </c>
       <c r="D105" s="11" t="n">
-        <v>-8.4</v>
+        <v>5.82</v>
       </c>
       <c r="E105" s="11" t="n">
-        <v>12.44</v>
+        <v>50.02</v>
       </c>
       <c r="F105" s="11" t="n">
-        <v>662.58</v>
+        <v>662.29</v>
       </c>
       <c r="G105" s="11" t="n">
         <v>1</v>
@@ -9155,7 +9155,7 @@
       </c>
       <c r="B106" s="11" t="inlineStr">
         <is>
-          <t>BM-P127</t>
+          <t>BM-P125</t>
         </is>
       </c>
       <c r="C106" s="11" t="inlineStr">
@@ -9164,13 +9164,13 @@
         </is>
       </c>
       <c r="D106" s="11" t="n">
-        <v>-155.96</v>
+        <v>10.15</v>
       </c>
       <c r="E106" s="11" t="n">
-        <v>134.01</v>
+        <v>136.21</v>
       </c>
       <c r="F106" s="11" t="n">
-        <v>662.36</v>
+        <v>662.26</v>
       </c>
       <c r="G106" s="11" t="n">
         <v>1</v>
@@ -9199,7 +9199,7 @@
       </c>
       <c r="B107" s="11" t="inlineStr">
         <is>
-          <t>BM-P128</t>
+          <t>BM-P126</t>
         </is>
       </c>
       <c r="C107" s="11" t="inlineStr">
@@ -9208,13 +9208,13 @@
         </is>
       </c>
       <c r="D107" s="11" t="n">
-        <v>7.25</v>
+        <v>-8.4</v>
       </c>
       <c r="E107" s="11" t="n">
-        <v>159.7</v>
+        <v>12.44</v>
       </c>
       <c r="F107" s="11" t="n">
-        <v>662.3</v>
+        <v>662.58</v>
       </c>
       <c r="G107" s="11" t="n">
         <v>1</v>
@@ -9243,7 +9243,7 @@
       </c>
       <c r="B108" s="11" t="inlineStr">
         <is>
-          <t>BM-P129</t>
+          <t>BM-P127</t>
         </is>
       </c>
       <c r="C108" s="11" t="inlineStr">
@@ -9252,13 +9252,13 @@
         </is>
       </c>
       <c r="D108" s="11" t="n">
-        <v>-156.76</v>
+        <v>-155.96</v>
       </c>
       <c r="E108" s="11" t="n">
-        <v>123.62</v>
+        <v>134.01</v>
       </c>
       <c r="F108" s="11" t="n">
-        <v>662.73</v>
+        <v>662.36</v>
       </c>
       <c r="G108" s="11" t="n">
         <v>1</v>
@@ -9287,7 +9287,7 @@
       </c>
       <c r="B109" s="11" t="inlineStr">
         <is>
-          <t>BM-P130</t>
+          <t>BM-P128</t>
         </is>
       </c>
       <c r="C109" s="11" t="inlineStr">
@@ -9296,13 +9296,13 @@
         </is>
       </c>
       <c r="D109" s="11" t="n">
-        <v>1.58</v>
+        <v>7.25</v>
       </c>
       <c r="E109" s="11" t="n">
-        <v>36.17</v>
+        <v>159.7</v>
       </c>
       <c r="F109" s="11" t="n">
-        <v>662.27</v>
+        <v>662.3</v>
       </c>
       <c r="G109" s="11" t="n">
         <v>1</v>
@@ -9331,7 +9331,7 @@
       </c>
       <c r="B110" s="11" t="inlineStr">
         <is>
-          <t>BM-P131</t>
+          <t>BM-P129</t>
         </is>
       </c>
       <c r="C110" s="11" t="inlineStr">
@@ -9340,13 +9340,13 @@
         </is>
       </c>
       <c r="D110" s="11" t="n">
-        <v>16.3</v>
+        <v>-156.76</v>
       </c>
       <c r="E110" s="11" t="n">
-        <v>111.85</v>
+        <v>123.62</v>
       </c>
       <c r="F110" s="11" t="n">
-        <v>662.34</v>
+        <v>662.73</v>
       </c>
       <c r="G110" s="11" t="n">
         <v>1</v>
@@ -9375,7 +9375,7 @@
       </c>
       <c r="B111" s="11" t="inlineStr">
         <is>
-          <t>BM-P132</t>
+          <t>BM-P130</t>
         </is>
       </c>
       <c r="C111" s="11" t="inlineStr">
@@ -9384,13 +9384,13 @@
         </is>
       </c>
       <c r="D111" s="11" t="n">
-        <v>-15.85</v>
+        <v>1.58</v>
       </c>
       <c r="E111" s="11" t="n">
-        <v>-1.15</v>
+        <v>36.17</v>
       </c>
       <c r="F111" s="11" t="n">
-        <v>662.48</v>
+        <v>662.27</v>
       </c>
       <c r="G111" s="11" t="n">
         <v>1</v>
@@ -9419,7 +9419,7 @@
       </c>
       <c r="B112" s="11" t="inlineStr">
         <is>
-          <t>BM-P133</t>
+          <t>BM-P131</t>
         </is>
       </c>
       <c r="C112" s="11" t="inlineStr">
@@ -9428,13 +9428,13 @@
         </is>
       </c>
       <c r="D112" s="11" t="n">
-        <v>-22.46</v>
+        <v>16.3</v>
       </c>
       <c r="E112" s="11" t="n">
-        <v>-36.01</v>
+        <v>111.85</v>
       </c>
       <c r="F112" s="11" t="n">
-        <v>662.6</v>
+        <v>662.34</v>
       </c>
       <c r="G112" s="11" t="n">
         <v>1</v>
@@ -9463,7 +9463,7 @@
       </c>
       <c r="B113" s="11" t="inlineStr">
         <is>
-          <t>BM-P134</t>
+          <t>BM-P132</t>
         </is>
       </c>
       <c r="C113" s="11" t="inlineStr">
@@ -9472,13 +9472,13 @@
         </is>
       </c>
       <c r="D113" s="11" t="n">
-        <v>8.49</v>
+        <v>-15.85</v>
       </c>
       <c r="E113" s="11" t="n">
-        <v>54.87</v>
+        <v>-1.15</v>
       </c>
       <c r="F113" s="11" t="n">
-        <v>662.4</v>
+        <v>662.48</v>
       </c>
       <c r="G113" s="11" t="n">
         <v>1</v>
@@ -9507,7 +9507,7 @@
       </c>
       <c r="B114" s="11" t="inlineStr">
         <is>
-          <t>BM-P135</t>
+          <t>BM-P133</t>
         </is>
       </c>
       <c r="C114" s="11" t="inlineStr">
@@ -9516,13 +9516,13 @@
         </is>
       </c>
       <c r="D114" s="11" t="n">
-        <v>-155.29</v>
+        <v>-22.46</v>
       </c>
       <c r="E114" s="11" t="n">
-        <v>129.79</v>
+        <v>-36.01</v>
       </c>
       <c r="F114" s="11" t="n">
-        <v>662.45</v>
+        <v>662.6</v>
       </c>
       <c r="G114" s="11" t="n">
         <v>1</v>
@@ -9551,7 +9551,7 @@
       </c>
       <c r="B115" s="11" t="inlineStr">
         <is>
-          <t>BM-P136</t>
+          <t>BM-P134</t>
         </is>
       </c>
       <c r="C115" s="11" t="inlineStr">
@@ -9560,13 +9560,13 @@
         </is>
       </c>
       <c r="D115" s="11" t="n">
-        <v>-159.58</v>
+        <v>8.49</v>
       </c>
       <c r="E115" s="11" t="n">
-        <v>142.25</v>
+        <v>54.87</v>
       </c>
       <c r="F115" s="11" t="n">
-        <v>662.34</v>
+        <v>662.4</v>
       </c>
       <c r="G115" s="11" t="n">
         <v>1</v>
@@ -9595,22 +9595,22 @@
       </c>
       <c r="B116" s="11" t="inlineStr">
         <is>
-          <t>BM-P137</t>
+          <t>BM-P135</t>
         </is>
       </c>
       <c r="C116" s="11" t="inlineStr">
         <is>
-          <t>BÈ 5</t>
+          <t>BÈ 4</t>
         </is>
       </c>
       <c r="D116" s="11" t="n">
-        <v>-285.42</v>
+        <v>-155.29</v>
       </c>
       <c r="E116" s="11" t="n">
-        <v>33.43</v>
+        <v>129.79</v>
       </c>
       <c r="F116" s="11" t="n">
-        <v>662.33</v>
+        <v>662.45</v>
       </c>
       <c r="G116" s="11" t="n">
         <v>1</v>
@@ -9620,11 +9620,11 @@
       </c>
       <c r="I116" s="11" t="inlineStr">
         <is>
-          <t>6Φ28 CB400-V</t>
+          <t>6Φ25 CB400-V</t>
         </is>
       </c>
       <c r="J116" s="11" t="n">
-        <v>191.4</v>
+        <v>152.6</v>
       </c>
       <c r="K116" s="11" t="n">
         <v>16.2</v>
@@ -9639,22 +9639,22 @@
       </c>
       <c r="B117" s="11" t="inlineStr">
         <is>
-          <t>BM-P138</t>
+          <t>BM-P136</t>
         </is>
       </c>
       <c r="C117" s="11" t="inlineStr">
         <is>
-          <t>BÈ 5</t>
+          <t>BÈ 4</t>
         </is>
       </c>
       <c r="D117" s="11" t="n">
-        <v>-83.14</v>
+        <v>-159.58</v>
       </c>
       <c r="E117" s="11" t="n">
-        <v>-94.28</v>
+        <v>142.25</v>
       </c>
       <c r="F117" s="11" t="n">
-        <v>662.27</v>
+        <v>662.34</v>
       </c>
       <c r="G117" s="11" t="n">
         <v>1</v>
@@ -9664,11 +9664,11 @@
       </c>
       <c r="I117" s="11" t="inlineStr">
         <is>
-          <t>6Φ28 CB400-V</t>
+          <t>6Φ25 CB400-V</t>
         </is>
       </c>
       <c r="J117" s="11" t="n">
-        <v>191.4</v>
+        <v>152.6</v>
       </c>
       <c r="K117" s="11" t="n">
         <v>16.2</v>
@@ -9683,7 +9683,7 @@
       </c>
       <c r="B118" s="11" t="inlineStr">
         <is>
-          <t>BM-P139</t>
+          <t>BM-P137</t>
         </is>
       </c>
       <c r="C118" s="11" t="inlineStr">
@@ -9692,13 +9692,13 @@
         </is>
       </c>
       <c r="D118" s="11" t="n">
-        <v>-244.09</v>
+        <v>-285.42</v>
       </c>
       <c r="E118" s="11" t="n">
-        <v>-78.78</v>
+        <v>33.43</v>
       </c>
       <c r="F118" s="11" t="n">
-        <v>662.3099999999999</v>
+        <v>662.33</v>
       </c>
       <c r="G118" s="11" t="n">
         <v>1</v>
@@ -9727,7 +9727,7 @@
       </c>
       <c r="B119" s="11" t="inlineStr">
         <is>
-          <t>BM-P140</t>
+          <t>BM-P138</t>
         </is>
       </c>
       <c r="C119" s="11" t="inlineStr">
@@ -9736,13 +9736,13 @@
         </is>
       </c>
       <c r="D119" s="11" t="n">
-        <v>-271.2</v>
+        <v>-83.14</v>
       </c>
       <c r="E119" s="11" t="n">
-        <v>-27.86</v>
+        <v>-94.28</v>
       </c>
       <c r="F119" s="11" t="n">
-        <v>663.51</v>
+        <v>662.27</v>
       </c>
       <c r="G119" s="11" t="n">
         <v>1</v>
@@ -9771,7 +9771,7 @@
       </c>
       <c r="B120" s="11" t="inlineStr">
         <is>
-          <t>BM-P141</t>
+          <t>BM-P139</t>
         </is>
       </c>
       <c r="C120" s="11" t="inlineStr">
@@ -9780,13 +9780,13 @@
         </is>
       </c>
       <c r="D120" s="11" t="n">
-        <v>-26.58</v>
+        <v>-244.09</v>
       </c>
       <c r="E120" s="11" t="n">
-        <v>-41.62</v>
+        <v>-78.78</v>
       </c>
       <c r="F120" s="11" t="n">
-        <v>662.36</v>
+        <v>662.3099999999999</v>
       </c>
       <c r="G120" s="11" t="n">
         <v>1</v>
@@ -9815,7 +9815,7 @@
       </c>
       <c r="B121" s="11" t="inlineStr">
         <is>
-          <t>BM-P142</t>
+          <t>BM-P140</t>
         </is>
       </c>
       <c r="C121" s="11" t="inlineStr">
@@ -9824,13 +9824,13 @@
         </is>
       </c>
       <c r="D121" s="11" t="n">
-        <v>-164.96</v>
+        <v>-271.2</v>
       </c>
       <c r="E121" s="11" t="n">
-        <v>-120.25</v>
+        <v>-27.86</v>
       </c>
       <c r="F121" s="11" t="n">
-        <v>662.3200000000001</v>
+        <v>663.51</v>
       </c>
       <c r="G121" s="11" t="n">
         <v>1</v>
@@ -9859,7 +9859,7 @@
       </c>
       <c r="B122" s="11" t="inlineStr">
         <is>
-          <t>BM-P143</t>
+          <t>BM-P141</t>
         </is>
       </c>
       <c r="C122" s="11" t="inlineStr">
@@ -9868,13 +9868,13 @@
         </is>
       </c>
       <c r="D122" s="11" t="n">
-        <v>-161.8</v>
+        <v>-26.58</v>
       </c>
       <c r="E122" s="11" t="n">
-        <v>119.68</v>
+        <v>-41.62</v>
       </c>
       <c r="F122" s="11" t="n">
-        <v>662.3200000000001</v>
+        <v>662.36</v>
       </c>
       <c r="G122" s="11" t="n">
         <v>1</v>
@@ -9903,7 +9903,7 @@
       </c>
       <c r="B123" s="11" t="inlineStr">
         <is>
-          <t>BM-P144</t>
+          <t>BM-P142</t>
         </is>
       </c>
       <c r="C123" s="11" t="inlineStr">
@@ -9912,13 +9912,13 @@
         </is>
       </c>
       <c r="D123" s="11" t="n">
-        <v>-272.4</v>
+        <v>-164.96</v>
       </c>
       <c r="E123" s="11" t="n">
-        <v>-22.55</v>
+        <v>-120.25</v>
       </c>
       <c r="F123" s="11" t="n">
-        <v>662.4299999999999</v>
+        <v>662.3200000000001</v>
       </c>
       <c r="G123" s="11" t="n">
         <v>1</v>
@@ -9947,7 +9947,7 @@
       </c>
       <c r="B124" s="11" t="inlineStr">
         <is>
-          <t>BM-P145</t>
+          <t>BM-P143</t>
         </is>
       </c>
       <c r="C124" s="11" t="inlineStr">
@@ -9956,13 +9956,13 @@
         </is>
       </c>
       <c r="D124" s="11" t="n">
-        <v>-145.22</v>
+        <v>-161.8</v>
       </c>
       <c r="E124" s="11" t="n">
-        <v>-124.85</v>
+        <v>119.68</v>
       </c>
       <c r="F124" s="11" t="n">
-        <v>662.46</v>
+        <v>662.3200000000001</v>
       </c>
       <c r="G124" s="11" t="n">
         <v>1</v>
@@ -9991,7 +9991,7 @@
       </c>
       <c r="B125" s="11" t="inlineStr">
         <is>
-          <t>BM-P146</t>
+          <t>BM-P144</t>
         </is>
       </c>
       <c r="C125" s="11" t="inlineStr">
@@ -10000,13 +10000,13 @@
         </is>
       </c>
       <c r="D125" s="11" t="n">
-        <v>-173.38</v>
+        <v>-272.4</v>
       </c>
       <c r="E125" s="11" t="n">
-        <v>122.89</v>
+        <v>-22.55</v>
       </c>
       <c r="F125" s="11" t="n">
-        <v>662.37</v>
+        <v>662.4299999999999</v>
       </c>
       <c r="G125" s="11" t="n">
         <v>1</v>
@@ -10035,7 +10035,7 @@
       </c>
       <c r="B126" s="11" t="inlineStr">
         <is>
-          <t>BM-P147</t>
+          <t>BM-P145</t>
         </is>
       </c>
       <c r="C126" s="11" t="inlineStr">
@@ -10044,13 +10044,13 @@
         </is>
       </c>
       <c r="D126" s="11" t="n">
-        <v>-64.45999999999999</v>
+        <v>-145.22</v>
       </c>
       <c r="E126" s="11" t="n">
-        <v>-76.95999999999999</v>
+        <v>-124.85</v>
       </c>
       <c r="F126" s="11" t="n">
-        <v>662.4400000000001</v>
+        <v>662.46</v>
       </c>
       <c r="G126" s="11" t="n">
         <v>1</v>
@@ -10079,7 +10079,7 @@
       </c>
       <c r="B127" s="11" t="inlineStr">
         <is>
-          <t>BM-P148</t>
+          <t>BM-P146</t>
         </is>
       </c>
       <c r="C127" s="11" t="inlineStr">
@@ -10088,13 +10088,13 @@
         </is>
       </c>
       <c r="D127" s="11" t="n">
-        <v>-196.39</v>
+        <v>-173.38</v>
       </c>
       <c r="E127" s="11" t="n">
-        <v>-117.23</v>
+        <v>122.89</v>
       </c>
       <c r="F127" s="11" t="n">
-        <v>662.3099999999999</v>
+        <v>662.37</v>
       </c>
       <c r="G127" s="11" t="n">
         <v>1</v>
@@ -10123,7 +10123,7 @@
       </c>
       <c r="B128" s="11" t="inlineStr">
         <is>
-          <t>BM-P149</t>
+          <t>BM-P147</t>
         </is>
       </c>
       <c r="C128" s="11" t="inlineStr">
@@ -10132,13 +10132,13 @@
         </is>
       </c>
       <c r="D128" s="11" t="n">
-        <v>-257.2</v>
+        <v>-64.45999999999999</v>
       </c>
       <c r="E128" s="11" t="n">
-        <v>-49.7</v>
+        <v>-76.95999999999999</v>
       </c>
       <c r="F128" s="11" t="n">
-        <v>662.27</v>
+        <v>662.4400000000001</v>
       </c>
       <c r="G128" s="11" t="n">
         <v>1</v>
@@ -10167,7 +10167,7 @@
       </c>
       <c r="B129" s="11" t="inlineStr">
         <is>
-          <t>BM-P151</t>
+          <t>BM-P148</t>
         </is>
       </c>
       <c r="C129" s="11" t="inlineStr">
@@ -10176,13 +10176,13 @@
         </is>
       </c>
       <c r="D129" s="11" t="n">
-        <v>-270.24</v>
+        <v>-196.39</v>
       </c>
       <c r="E129" s="11" t="n">
-        <v>-24.68</v>
+        <v>-117.23</v>
       </c>
       <c r="F129" s="11" t="n">
-        <v>662.36</v>
+        <v>662.3099999999999</v>
       </c>
       <c r="G129" s="11" t="n">
         <v>1</v>
@@ -10211,7 +10211,7 @@
       </c>
       <c r="B130" s="11" t="inlineStr">
         <is>
-          <t>BM-P152</t>
+          <t>BM-P149</t>
         </is>
       </c>
       <c r="C130" s="11" t="inlineStr">
@@ -10220,13 +10220,13 @@
         </is>
       </c>
       <c r="D130" s="11" t="n">
-        <v>-157.06</v>
+        <v>-257.2</v>
       </c>
       <c r="E130" s="11" t="n">
-        <v>-121.46</v>
+        <v>-49.7</v>
       </c>
       <c r="F130" s="11" t="n">
-        <v>662.39</v>
+        <v>662.27</v>
       </c>
       <c r="G130" s="11" t="n">
         <v>1</v>
@@ -10255,7 +10255,7 @@
       </c>
       <c r="B131" s="11" t="inlineStr">
         <is>
-          <t>BM-P153</t>
+          <t>BM-P151</t>
         </is>
       </c>
       <c r="C131" s="11" t="inlineStr">
@@ -10264,13 +10264,13 @@
         </is>
       </c>
       <c r="D131" s="11" t="n">
-        <v>-200.97</v>
+        <v>-270.24</v>
       </c>
       <c r="E131" s="11" t="n">
-        <v>-116.63</v>
+        <v>-24.68</v>
       </c>
       <c r="F131" s="11" t="n">
-        <v>662.29</v>
+        <v>662.36</v>
       </c>
       <c r="G131" s="11" t="n">
         <v>1</v>
@@ -10299,7 +10299,7 @@
       </c>
       <c r="B132" s="11" t="inlineStr">
         <is>
-          <t>BM-P154</t>
+          <t>BM-P152</t>
         </is>
       </c>
       <c r="C132" s="11" t="inlineStr">
@@ -10308,13 +10308,13 @@
         </is>
       </c>
       <c r="D132" s="11" t="n">
-        <v>-76.13</v>
+        <v>-157.06</v>
       </c>
       <c r="E132" s="11" t="n">
-        <v>-87.58</v>
+        <v>-121.46</v>
       </c>
       <c r="F132" s="11" t="n">
-        <v>662.36</v>
+        <v>662.39</v>
       </c>
       <c r="G132" s="11" t="n">
         <v>1</v>
@@ -10343,7 +10343,7 @@
       </c>
       <c r="B133" s="11" t="inlineStr">
         <is>
-          <t>BM-P155</t>
+          <t>BM-P153</t>
         </is>
       </c>
       <c r="C133" s="11" t="inlineStr">
@@ -10352,13 +10352,13 @@
         </is>
       </c>
       <c r="D133" s="11" t="n">
-        <v>-155.77</v>
+        <v>-200.97</v>
       </c>
       <c r="E133" s="11" t="n">
-        <v>120.08</v>
+        <v>-116.63</v>
       </c>
       <c r="F133" s="11" t="n">
-        <v>662.35</v>
+        <v>662.29</v>
       </c>
       <c r="G133" s="11" t="n">
         <v>1</v>
@@ -10387,7 +10387,7 @@
       </c>
       <c r="B134" s="11" t="inlineStr">
         <is>
-          <t>BM-P156</t>
+          <t>BM-P154</t>
         </is>
       </c>
       <c r="C134" s="11" t="inlineStr">
@@ -10396,13 +10396,13 @@
         </is>
       </c>
       <c r="D134" s="11" t="n">
-        <v>-23.74</v>
+        <v>-76.13</v>
       </c>
       <c r="E134" s="11" t="n">
-        <v>-40.16</v>
+        <v>-87.58</v>
       </c>
       <c r="F134" s="11" t="n">
-        <v>663.65</v>
+        <v>662.36</v>
       </c>
       <c r="G134" s="11" t="n">
         <v>1</v>
@@ -10431,7 +10431,7 @@
       </c>
       <c r="B135" s="11" t="inlineStr">
         <is>
-          <t>BM-P157</t>
+          <t>BM-P155</t>
         </is>
       </c>
       <c r="C135" s="11" t="inlineStr">
@@ -10440,13 +10440,13 @@
         </is>
       </c>
       <c r="D135" s="11" t="n">
-        <v>-51.6</v>
+        <v>-155.77</v>
       </c>
       <c r="E135" s="11" t="n">
-        <v>-62.2</v>
+        <v>120.08</v>
       </c>
       <c r="F135" s="11" t="n">
-        <v>662.28</v>
+        <v>662.35</v>
       </c>
       <c r="G135" s="11" t="n">
         <v>1</v>
@@ -10475,7 +10475,7 @@
       </c>
       <c r="B136" s="11" t="inlineStr">
         <is>
-          <t>BM-P158</t>
+          <t>BM-P156</t>
         </is>
       </c>
       <c r="C136" s="11" t="inlineStr">
@@ -10484,13 +10484,13 @@
         </is>
       </c>
       <c r="D136" s="11" t="n">
-        <v>-90.73999999999999</v>
+        <v>-23.74</v>
       </c>
       <c r="E136" s="11" t="n">
-        <v>-104.05</v>
+        <v>-40.16</v>
       </c>
       <c r="F136" s="11" t="n">
-        <v>662.47</v>
+        <v>663.65</v>
       </c>
       <c r="G136" s="11" t="n">
         <v>1</v>
@@ -10519,7 +10519,7 @@
       </c>
       <c r="B137" s="11" t="inlineStr">
         <is>
-          <t>BM-P159</t>
+          <t>BM-P157</t>
         </is>
       </c>
       <c r="C137" s="11" t="inlineStr">
@@ -10528,13 +10528,13 @@
         </is>
       </c>
       <c r="D137" s="11" t="n">
-        <v>-180.49</v>
+        <v>-51.6</v>
       </c>
       <c r="E137" s="11" t="n">
-        <v>-118.86</v>
+        <v>-62.2</v>
       </c>
       <c r="F137" s="11" t="n">
-        <v>662.3</v>
+        <v>662.28</v>
       </c>
       <c r="G137" s="11" t="n">
         <v>1</v>
@@ -10563,7 +10563,7 @@
       </c>
       <c r="B138" s="11" t="inlineStr">
         <is>
-          <t>BM-P160</t>
+          <t>BM-P158</t>
         </is>
       </c>
       <c r="C138" s="11" t="inlineStr">
@@ -10572,13 +10572,13 @@
         </is>
       </c>
       <c r="D138" s="11" t="n">
-        <v>-267.59</v>
+        <v>-90.73999999999999</v>
       </c>
       <c r="E138" s="11" t="n">
-        <v>-28.54</v>
+        <v>-104.05</v>
       </c>
       <c r="F138" s="11" t="n">
-        <v>662.3200000000001</v>
+        <v>662.47</v>
       </c>
       <c r="G138" s="11" t="n">
         <v>1</v>
@@ -10607,7 +10607,7 @@
       </c>
       <c r="B139" s="11" t="inlineStr">
         <is>
-          <t>BM-P161</t>
+          <t>BM-P159</t>
         </is>
       </c>
       <c r="C139" s="11" t="inlineStr">
@@ -10616,13 +10616,13 @@
         </is>
       </c>
       <c r="D139" s="11" t="n">
-        <v>-248.38</v>
+        <v>-180.49</v>
       </c>
       <c r="E139" s="11" t="n">
-        <v>-67.56</v>
+        <v>-118.86</v>
       </c>
       <c r="F139" s="11" t="n">
-        <v>662.29</v>
+        <v>662.3</v>
       </c>
       <c r="G139" s="11" t="n">
         <v>1</v>
@@ -10651,7 +10651,7 @@
       </c>
       <c r="B140" s="11" t="inlineStr">
         <is>
-          <t>BM-P162</t>
+          <t>BM-P160</t>
         </is>
       </c>
       <c r="C140" s="11" t="inlineStr">
@@ -10660,13 +10660,13 @@
         </is>
       </c>
       <c r="D140" s="11" t="n">
-        <v>-284.12</v>
+        <v>-267.59</v>
       </c>
       <c r="E140" s="11" t="n">
-        <v>12.11</v>
+        <v>-28.54</v>
       </c>
       <c r="F140" s="11" t="n">
-        <v>662.29</v>
+        <v>662.3200000000001</v>
       </c>
       <c r="G140" s="11" t="n">
         <v>1</v>
@@ -10695,7 +10695,7 @@
       </c>
       <c r="B141" s="11" t="inlineStr">
         <is>
-          <t>BM-P163</t>
+          <t>BM-P161</t>
         </is>
       </c>
       <c r="C141" s="11" t="inlineStr">
@@ -10704,13 +10704,13 @@
         </is>
       </c>
       <c r="D141" s="11" t="n">
-        <v>-166.36</v>
+        <v>-248.38</v>
       </c>
       <c r="E141" s="11" t="n">
-        <v>121.17</v>
+        <v>-67.56</v>
       </c>
       <c r="F141" s="11" t="n">
-        <v>662.34</v>
+        <v>662.29</v>
       </c>
       <c r="G141" s="11" t="n">
         <v>1</v>
@@ -10739,7 +10739,7 @@
       </c>
       <c r="B142" s="11" t="inlineStr">
         <is>
-          <t>BM-P164</t>
+          <t>BM-P162</t>
         </is>
       </c>
       <c r="C142" s="11" t="inlineStr">
@@ -10748,13 +10748,13 @@
         </is>
       </c>
       <c r="D142" s="11" t="n">
-        <v>-79.68000000000001</v>
+        <v>-284.12</v>
       </c>
       <c r="E142" s="11" t="n">
-        <v>-91.14</v>
+        <v>12.11</v>
       </c>
       <c r="F142" s="11" t="n">
-        <v>662.46</v>
+        <v>662.29</v>
       </c>
       <c r="G142" s="11" t="n">
         <v>1</v>
@@ -10783,7 +10783,7 @@
       </c>
       <c r="B143" s="11" t="inlineStr">
         <is>
-          <t>BM-P165</t>
+          <t>BM-P163</t>
         </is>
       </c>
       <c r="C143" s="11" t="inlineStr">
@@ -10792,13 +10792,13 @@
         </is>
       </c>
       <c r="D143" s="11" t="n">
-        <v>-252.34</v>
+        <v>-166.36</v>
       </c>
       <c r="E143" s="11" t="n">
-        <v>-60.61</v>
+        <v>121.17</v>
       </c>
       <c r="F143" s="11" t="n">
-        <v>662.29</v>
+        <v>662.34</v>
       </c>
       <c r="G143" s="11" t="n">
         <v>1</v>
@@ -10827,22 +10827,22 @@
       </c>
       <c r="B144" s="11" t="inlineStr">
         <is>
-          <t>BM-P166</t>
+          <t>BM-P164</t>
         </is>
       </c>
       <c r="C144" s="11" t="inlineStr">
         <is>
-          <t>BÈ 6</t>
+          <t>BÈ 5</t>
         </is>
       </c>
       <c r="D144" s="11" t="n">
-        <v>-316.94</v>
+        <v>-79.68000000000001</v>
       </c>
       <c r="E144" s="11" t="n">
-        <v>62.16</v>
+        <v>-91.14</v>
       </c>
       <c r="F144" s="11" t="n">
-        <v>662.4</v>
+        <v>662.46</v>
       </c>
       <c r="G144" s="11" t="n">
         <v>1</v>
@@ -10871,22 +10871,22 @@
       </c>
       <c r="B145" s="11" t="inlineStr">
         <is>
-          <t>BM-P167</t>
+          <t>BM-P165</t>
         </is>
       </c>
       <c r="C145" s="11" t="inlineStr">
         <is>
-          <t>BÈ 6</t>
+          <t>BÈ 5</t>
         </is>
       </c>
       <c r="D145" s="11" t="n">
-        <v>-352.96</v>
+        <v>-252.34</v>
       </c>
       <c r="E145" s="11" t="n">
-        <v>286.03</v>
+        <v>-60.61</v>
       </c>
       <c r="F145" s="11" t="n">
-        <v>662.26</v>
+        <v>662.29</v>
       </c>
       <c r="G145" s="11" t="n">
         <v>1</v>
@@ -10915,7 +10915,7 @@
       </c>
       <c r="B146" s="11" t="inlineStr">
         <is>
-          <t>BM-P168</t>
+          <t>BM-P166</t>
         </is>
       </c>
       <c r="C146" s="11" t="inlineStr">
@@ -10924,13 +10924,13 @@
         </is>
       </c>
       <c r="D146" s="11" t="n">
-        <v>-186.38</v>
+        <v>-316.94</v>
       </c>
       <c r="E146" s="11" t="n">
-        <v>152.59</v>
+        <v>62.16</v>
       </c>
       <c r="F146" s="11" t="n">
-        <v>662.3099999999999</v>
+        <v>662.4</v>
       </c>
       <c r="G146" s="11" t="n">
         <v>1</v>
@@ -10959,7 +10959,7 @@
       </c>
       <c r="B147" s="11" t="inlineStr">
         <is>
-          <t>BM-P169</t>
+          <t>BM-P167</t>
         </is>
       </c>
       <c r="C147" s="11" t="inlineStr">
@@ -10968,13 +10968,13 @@
         </is>
       </c>
       <c r="D147" s="11" t="n">
-        <v>-469.17</v>
+        <v>-352.96</v>
       </c>
       <c r="E147" s="11" t="n">
-        <v>155</v>
+        <v>286.03</v>
       </c>
       <c r="F147" s="11" t="n">
-        <v>662.3200000000001</v>
+        <v>662.26</v>
       </c>
       <c r="G147" s="11" t="n">
         <v>1</v>
@@ -11003,7 +11003,7 @@
       </c>
       <c r="B148" s="11" t="inlineStr">
         <is>
-          <t>BM-P170</t>
+          <t>BM-P168</t>
         </is>
       </c>
       <c r="C148" s="11" t="inlineStr">
@@ -11012,13 +11012,13 @@
         </is>
       </c>
       <c r="D148" s="11" t="n">
-        <v>-425.91</v>
+        <v>-186.38</v>
       </c>
       <c r="E148" s="11" t="n">
-        <v>122.6</v>
+        <v>152.59</v>
       </c>
       <c r="F148" s="11" t="n">
-        <v>662.26</v>
+        <v>662.3099999999999</v>
       </c>
       <c r="G148" s="11" t="n">
         <v>1</v>
@@ -11047,7 +11047,7 @@
       </c>
       <c r="B149" s="11" t="inlineStr">
         <is>
-          <t>BM-P172</t>
+          <t>BM-P169</t>
         </is>
       </c>
       <c r="C149" s="11" t="inlineStr">
@@ -11056,13 +11056,13 @@
         </is>
       </c>
       <c r="D149" s="11" t="n">
-        <v>-297.12</v>
+        <v>-469.17</v>
       </c>
       <c r="E149" s="11" t="n">
-        <v>245.07</v>
+        <v>155</v>
       </c>
       <c r="F149" s="11" t="n">
-        <v>662.51</v>
+        <v>662.3200000000001</v>
       </c>
       <c r="G149" s="11" t="n">
         <v>1</v>
@@ -11091,7 +11091,7 @@
       </c>
       <c r="B150" s="11" t="inlineStr">
         <is>
-          <t>BM-P173</t>
+          <t>BM-P170</t>
         </is>
       </c>
       <c r="C150" s="11" t="inlineStr">
@@ -11100,13 +11100,13 @@
         </is>
       </c>
       <c r="D150" s="11" t="n">
-        <v>-453.74</v>
+        <v>-425.91</v>
       </c>
       <c r="E150" s="11" t="n">
-        <v>332.65</v>
+        <v>122.6</v>
       </c>
       <c r="F150" s="11" t="n">
-        <v>662.5</v>
+        <v>662.26</v>
       </c>
       <c r="G150" s="11" t="n">
         <v>1</v>
@@ -11135,7 +11135,7 @@
       </c>
       <c r="B151" s="11" t="inlineStr">
         <is>
-          <t>BM-P174</t>
+          <t>BM-P172</t>
         </is>
       </c>
       <c r="C151" s="11" t="inlineStr">
@@ -11144,13 +11144,13 @@
         </is>
       </c>
       <c r="D151" s="11" t="n">
-        <v>-297.58</v>
+        <v>-297.12</v>
       </c>
       <c r="E151" s="11" t="n">
-        <v>51.33</v>
+        <v>245.07</v>
       </c>
       <c r="F151" s="11" t="n">
-        <v>662.4299999999999</v>
+        <v>662.51</v>
       </c>
       <c r="G151" s="11" t="n">
         <v>1</v>
@@ -11179,7 +11179,7 @@
       </c>
       <c r="B152" s="11" t="inlineStr">
         <is>
-          <t>BM-P175</t>
+          <t>BM-P173</t>
         </is>
       </c>
       <c r="C152" s="11" t="inlineStr">
@@ -11188,13 +11188,13 @@
         </is>
       </c>
       <c r="D152" s="11" t="n">
-        <v>-343.33</v>
+        <v>-453.74</v>
       </c>
       <c r="E152" s="11" t="n">
-        <v>58.55</v>
+        <v>332.65</v>
       </c>
       <c r="F152" s="11" t="n">
-        <v>662.33</v>
+        <v>662.5</v>
       </c>
       <c r="G152" s="11" t="n">
         <v>1</v>
@@ -11223,7 +11223,7 @@
       </c>
       <c r="B153" s="11" t="inlineStr">
         <is>
-          <t>BM-P176</t>
+          <t>BM-P174</t>
         </is>
       </c>
       <c r="C153" s="11" t="inlineStr">
@@ -11232,13 +11232,13 @@
         </is>
       </c>
       <c r="D153" s="11" t="n">
-        <v>-313.09</v>
+        <v>-297.58</v>
       </c>
       <c r="E153" s="11" t="n">
-        <v>253.55</v>
+        <v>51.33</v>
       </c>
       <c r="F153" s="11" t="n">
-        <v>662.29</v>
+        <v>662.4299999999999</v>
       </c>
       <c r="G153" s="11" t="n">
         <v>1</v>
@@ -11267,7 +11267,7 @@
       </c>
       <c r="B154" s="11" t="inlineStr">
         <is>
-          <t>BM-P177</t>
+          <t>BM-P175</t>
         </is>
       </c>
       <c r="C154" s="11" t="inlineStr">
@@ -11276,13 +11276,13 @@
         </is>
       </c>
       <c r="D154" s="11" t="n">
-        <v>-391.49</v>
+        <v>-343.33</v>
       </c>
       <c r="E154" s="11" t="n">
-        <v>311.18</v>
+        <v>58.55</v>
       </c>
       <c r="F154" s="11" t="n">
-        <v>662.54</v>
+        <v>662.33</v>
       </c>
       <c r="G154" s="11" t="n">
         <v>1</v>
@@ -11311,7 +11311,7 @@
       </c>
       <c r="B155" s="11" t="inlineStr">
         <is>
-          <t>BM-P179</t>
+          <t>BM-P176</t>
         </is>
       </c>
       <c r="C155" s="11" t="inlineStr">
@@ -11320,13 +11320,13 @@
         </is>
       </c>
       <c r="D155" s="11" t="n">
-        <v>-444.01</v>
+        <v>-313.09</v>
       </c>
       <c r="E155" s="11" t="n">
-        <v>142.95</v>
+        <v>253.55</v>
       </c>
       <c r="F155" s="11" t="n">
-        <v>662.33</v>
+        <v>662.29</v>
       </c>
       <c r="G155" s="11" t="n">
         <v>1</v>
@@ -11355,7 +11355,7 @@
       </c>
       <c r="B156" s="11" t="inlineStr">
         <is>
-          <t>BM-P180</t>
+          <t>BM-P177</t>
         </is>
       </c>
       <c r="C156" s="11" t="inlineStr">
@@ -11364,13 +11364,13 @@
         </is>
       </c>
       <c r="D156" s="11" t="n">
-        <v>-180.83</v>
+        <v>-391.49</v>
       </c>
       <c r="E156" s="11" t="n">
-        <v>129.89</v>
+        <v>311.18</v>
       </c>
       <c r="F156" s="11" t="n">
-        <v>662.4299999999999</v>
+        <v>662.54</v>
       </c>
       <c r="G156" s="11" t="n">
         <v>1</v>
@@ -11399,7 +11399,7 @@
       </c>
       <c r="B157" s="11" t="inlineStr">
         <is>
-          <t>BM-P181</t>
+          <t>BM-P179</t>
         </is>
       </c>
       <c r="C157" s="11" t="inlineStr">
@@ -11408,13 +11408,13 @@
         </is>
       </c>
       <c r="D157" s="11" t="n">
-        <v>-201.45</v>
+        <v>-444.01</v>
       </c>
       <c r="E157" s="11" t="n">
-        <v>181.83</v>
+        <v>142.95</v>
       </c>
       <c r="F157" s="11" t="n">
-        <v>662.3200000000001</v>
+        <v>662.33</v>
       </c>
       <c r="G157" s="11" t="n">
         <v>1</v>
@@ -11443,7 +11443,7 @@
       </c>
       <c r="B158" s="11" t="inlineStr">
         <is>
-          <t>BM-P182</t>
+          <t>BM-P180</t>
         </is>
       </c>
       <c r="C158" s="11" t="inlineStr">
@@ -11452,13 +11452,13 @@
         </is>
       </c>
       <c r="D158" s="11" t="n">
-        <v>-302.89</v>
+        <v>-180.83</v>
       </c>
       <c r="E158" s="11" t="n">
-        <v>246.42</v>
+        <v>129.89</v>
       </c>
       <c r="F158" s="11" t="n">
-        <v>662.45</v>
+        <v>662.4299999999999</v>
       </c>
       <c r="G158" s="11" t="n">
         <v>1</v>
@@ -11487,7 +11487,7 @@
       </c>
       <c r="B159" s="11" t="inlineStr">
         <is>
-          <t>BM-P183</t>
+          <t>BM-P181</t>
         </is>
       </c>
       <c r="C159" s="11" t="inlineStr">
@@ -11496,13 +11496,13 @@
         </is>
       </c>
       <c r="D159" s="11" t="n">
-        <v>-312.26</v>
+        <v>-201.45</v>
       </c>
       <c r="E159" s="11" t="n">
-        <v>60.96</v>
+        <v>181.83</v>
       </c>
       <c r="F159" s="11" t="n">
-        <v>662.34</v>
+        <v>662.3200000000001</v>
       </c>
       <c r="G159" s="11" t="n">
         <v>1</v>
@@ -11531,7 +11531,7 @@
       </c>
       <c r="B160" s="11" t="inlineStr">
         <is>
-          <t>BM-P184</t>
+          <t>BM-P182</t>
         </is>
       </c>
       <c r="C160" s="11" t="inlineStr">
@@ -11540,13 +11540,13 @@
         </is>
       </c>
       <c r="D160" s="11" t="n">
-        <v>-420.67</v>
+        <v>-302.89</v>
       </c>
       <c r="E160" s="11" t="n">
-        <v>103.07</v>
+        <v>246.42</v>
       </c>
       <c r="F160" s="11" t="n">
-        <v>662.35</v>
+        <v>662.45</v>
       </c>
       <c r="G160" s="11" t="n">
         <v>1</v>
@@ -11575,7 +11575,7 @@
       </c>
       <c r="B161" s="11" t="inlineStr">
         <is>
-          <t>BM-P185</t>
+          <t>BM-P183</t>
         </is>
       </c>
       <c r="C161" s="11" t="inlineStr">
@@ -11584,13 +11584,13 @@
         </is>
       </c>
       <c r="D161" s="11" t="n">
-        <v>-185.46</v>
+        <v>-312.26</v>
       </c>
       <c r="E161" s="11" t="n">
-        <v>134.87</v>
+        <v>60.96</v>
       </c>
       <c r="F161" s="11" t="n">
-        <v>662.3200000000001</v>
+        <v>662.34</v>
       </c>
       <c r="G161" s="11" t="n">
         <v>1</v>
@@ -11619,7 +11619,7 @@
       </c>
       <c r="B162" s="11" t="inlineStr">
         <is>
-          <t>BM-P186</t>
+          <t>BM-P184</t>
         </is>
       </c>
       <c r="C162" s="11" t="inlineStr">
@@ -11628,13 +11628,13 @@
         </is>
       </c>
       <c r="D162" s="11" t="n">
-        <v>-475.49</v>
+        <v>-420.67</v>
       </c>
       <c r="E162" s="11" t="n">
-        <v>152.36</v>
+        <v>103.07</v>
       </c>
       <c r="F162" s="11" t="n">
-        <v>662.34</v>
+        <v>662.35</v>
       </c>
       <c r="G162" s="11" t="n">
         <v>1</v>
@@ -11663,7 +11663,7 @@
       </c>
       <c r="B163" s="11" t="inlineStr">
         <is>
-          <t>BM-P187</t>
+          <t>BM-P185</t>
         </is>
       </c>
       <c r="C163" s="11" t="inlineStr">
@@ -11672,13 +11672,13 @@
         </is>
       </c>
       <c r="D163" s="11" t="n">
-        <v>-376.99</v>
+        <v>-185.46</v>
       </c>
       <c r="E163" s="11" t="n">
-        <v>301.35</v>
+        <v>134.87</v>
       </c>
       <c r="F163" s="11" t="n">
-        <v>662.3</v>
+        <v>662.3200000000001</v>
       </c>
       <c r="G163" s="11" t="n">
         <v>1</v>
@@ -11707,7 +11707,7 @@
       </c>
       <c r="B164" s="11" t="inlineStr">
         <is>
-          <t>BM-P188</t>
+          <t>BM-P186</t>
         </is>
       </c>
       <c r="C164" s="11" t="inlineStr">
@@ -11716,13 +11716,13 @@
         </is>
       </c>
       <c r="D164" s="11" t="n">
-        <v>-431.32</v>
+        <v>-475.49</v>
       </c>
       <c r="E164" s="11" t="n">
-        <v>130.36</v>
+        <v>152.36</v>
       </c>
       <c r="F164" s="11" t="n">
-        <v>662.3</v>
+        <v>662.34</v>
       </c>
       <c r="G164" s="11" t="n">
         <v>1</v>
@@ -11751,7 +11751,7 @@
       </c>
       <c r="B165" s="11" t="inlineStr">
         <is>
-          <t>BM-P189</t>
+          <t>BM-P187</t>
         </is>
       </c>
       <c r="C165" s="11" t="inlineStr">
@@ -11760,13 +11760,13 @@
         </is>
       </c>
       <c r="D165" s="11" t="n">
-        <v>-289.1</v>
+        <v>-376.99</v>
       </c>
       <c r="E165" s="11" t="n">
-        <v>43.62</v>
+        <v>301.35</v>
       </c>
       <c r="F165" s="11" t="n">
-        <v>662.33</v>
+        <v>662.3</v>
       </c>
       <c r="G165" s="11" t="n">
         <v>1</v>
@@ -11795,7 +11795,7 @@
       </c>
       <c r="B166" s="11" t="inlineStr">
         <is>
-          <t>BM-P191</t>
+          <t>BM-P188</t>
         </is>
       </c>
       <c r="C166" s="11" t="inlineStr">
@@ -11804,13 +11804,13 @@
         </is>
       </c>
       <c r="D166" s="11" t="n">
-        <v>-176.01</v>
+        <v>-431.32</v>
       </c>
       <c r="E166" s="11" t="n">
-        <v>126.16</v>
+        <v>130.36</v>
       </c>
       <c r="F166" s="11" t="n">
-        <v>662.45</v>
+        <v>662.3</v>
       </c>
       <c r="G166" s="11" t="n">
         <v>1</v>
@@ -11839,7 +11839,7 @@
       </c>
       <c r="B167" s="11" t="inlineStr">
         <is>
-          <t>BM-P192</t>
+          <t>BM-P189</t>
         </is>
       </c>
       <c r="C167" s="11" t="inlineStr">
@@ -11848,13 +11848,13 @@
         </is>
       </c>
       <c r="D167" s="11" t="n">
-        <v>-197.6</v>
+        <v>-289.1</v>
       </c>
       <c r="E167" s="11" t="n">
-        <v>176.02</v>
+        <v>43.62</v>
       </c>
       <c r="F167" s="11" t="n">
-        <v>662.3</v>
+        <v>662.33</v>
       </c>
       <c r="G167" s="11" t="n">
         <v>1</v>
@@ -11883,7 +11883,7 @@
       </c>
       <c r="B168" s="11" t="inlineStr">
         <is>
-          <t>BM-P193</t>
+          <t>BM-P191</t>
         </is>
       </c>
       <c r="C168" s="11" t="inlineStr">
@@ -11892,13 +11892,13 @@
         </is>
       </c>
       <c r="D168" s="11" t="n">
-        <v>-436.03</v>
+        <v>-176.01</v>
       </c>
       <c r="E168" s="11" t="n">
-        <v>330.79</v>
+        <v>126.16</v>
       </c>
       <c r="F168" s="11" t="n">
-        <v>662.28</v>
+        <v>662.45</v>
       </c>
       <c r="G168" s="11" t="n">
         <v>1</v>
@@ -11927,7 +11927,7 @@
       </c>
       <c r="B169" s="11" t="inlineStr">
         <is>
-          <t>BM-P194</t>
+          <t>BM-P192</t>
         </is>
       </c>
       <c r="C169" s="11" t="inlineStr">
@@ -11936,13 +11936,13 @@
         </is>
       </c>
       <c r="D169" s="11" t="n">
-        <v>-337.48</v>
+        <v>-197.6</v>
       </c>
       <c r="E169" s="11" t="n">
-        <v>60.17</v>
+        <v>176.02</v>
       </c>
       <c r="F169" s="11" t="n">
-        <v>662.3099999999999</v>
+        <v>662.3</v>
       </c>
       <c r="G169" s="11" t="n">
         <v>1</v>
@@ -11971,7 +11971,7 @@
       </c>
       <c r="B170" s="11" t="inlineStr">
         <is>
-          <t>BM-P195</t>
+          <t>BM-P193</t>
         </is>
       </c>
       <c r="C170" s="11" t="inlineStr">
@@ -11980,13 +11980,13 @@
         </is>
       </c>
       <c r="D170" s="11" t="n">
-        <v>-457.18</v>
+        <v>-436.03</v>
       </c>
       <c r="E170" s="11" t="n">
-        <v>150.95</v>
+        <v>330.79</v>
       </c>
       <c r="F170" s="11" t="n">
-        <v>662.34</v>
+        <v>662.28</v>
       </c>
       <c r="G170" s="11" t="n">
         <v>1</v>
@@ -12015,7 +12015,7 @@
       </c>
       <c r="B171" s="11" t="inlineStr">
         <is>
-          <t>BM-P196</t>
+          <t>BM-P194</t>
         </is>
       </c>
       <c r="C171" s="11" t="inlineStr">
@@ -12024,13 +12024,13 @@
         </is>
       </c>
       <c r="D171" s="11" t="n">
-        <v>-330.66</v>
+        <v>-337.48</v>
       </c>
       <c r="E171" s="11" t="n">
-        <v>268.29</v>
+        <v>60.17</v>
       </c>
       <c r="F171" s="11" t="n">
-        <v>662.3200000000001</v>
+        <v>662.3099999999999</v>
       </c>
       <c r="G171" s="11" t="n">
         <v>1</v>
@@ -12059,7 +12059,7 @@
       </c>
       <c r="B172" s="11" t="inlineStr">
         <is>
-          <t>BM-P197</t>
+          <t>BM-P195</t>
         </is>
       </c>
       <c r="C172" s="11" t="inlineStr">
@@ -12068,13 +12068,13 @@
         </is>
       </c>
       <c r="D172" s="11" t="n">
-        <v>-288.83</v>
+        <v>-457.18</v>
       </c>
       <c r="E172" s="11" t="n">
-        <v>243.85</v>
+        <v>150.95</v>
       </c>
       <c r="F172" s="11" t="n">
-        <v>662.28</v>
+        <v>662.34</v>
       </c>
       <c r="G172" s="11" t="n">
         <v>1</v>
@@ -12103,7 +12103,7 @@
       </c>
       <c r="B173" s="11" t="inlineStr">
         <is>
-          <t>BM-P198</t>
+          <t>BM-P196</t>
         </is>
       </c>
       <c r="C173" s="11" t="inlineStr">
@@ -12112,13 +12112,13 @@
         </is>
       </c>
       <c r="D173" s="11" t="n">
-        <v>-324.22</v>
+        <v>-330.66</v>
       </c>
       <c r="E173" s="11" t="n">
-        <v>63.13</v>
+        <v>268.29</v>
       </c>
       <c r="F173" s="11" t="n">
-        <v>662.3099999999999</v>
+        <v>662.3200000000001</v>
       </c>
       <c r="G173" s="11" t="n">
         <v>1</v>
@@ -12147,7 +12147,7 @@
       </c>
       <c r="B174" s="11" t="inlineStr">
         <is>
-          <t>BM-P199</t>
+          <t>BM-P197</t>
         </is>
       </c>
       <c r="C174" s="11" t="inlineStr">
@@ -12156,13 +12156,13 @@
         </is>
       </c>
       <c r="D174" s="11" t="n">
-        <v>-300.75</v>
+        <v>-288.83</v>
       </c>
       <c r="E174" s="11" t="n">
-        <v>249.16</v>
+        <v>243.85</v>
       </c>
       <c r="F174" s="11" t="n">
-        <v>664.4400000000001</v>
+        <v>662.28</v>
       </c>
       <c r="G174" s="11" t="n">
         <v>1</v>
@@ -12191,7 +12191,7 @@
       </c>
       <c r="B175" s="11" t="inlineStr">
         <is>
-          <t>BM-P200</t>
+          <t>BM-P198</t>
         </is>
       </c>
       <c r="C175" s="11" t="inlineStr">
@@ -12200,13 +12200,13 @@
         </is>
       </c>
       <c r="D175" s="11" t="n">
-        <v>-428.65</v>
+        <v>-324.22</v>
       </c>
       <c r="E175" s="11" t="n">
-        <v>126.18</v>
+        <v>63.13</v>
       </c>
       <c r="F175" s="11" t="n">
-        <v>662.4299999999999</v>
+        <v>662.3099999999999</v>
       </c>
       <c r="G175" s="11" t="n">
         <v>1</v>
@@ -12235,7 +12235,7 @@
       </c>
       <c r="B176" s="11" t="inlineStr">
         <is>
-          <t>BM-P201</t>
+          <t>BM-P199</t>
         </is>
       </c>
       <c r="C176" s="11" t="inlineStr">
@@ -12244,13 +12244,13 @@
         </is>
       </c>
       <c r="D176" s="11" t="n">
-        <v>-362.49</v>
+        <v>-300.75</v>
       </c>
       <c r="E176" s="11" t="n">
-        <v>293.31</v>
+        <v>249.16</v>
       </c>
       <c r="F176" s="11" t="n">
-        <v>662.35</v>
+        <v>664.4400000000001</v>
       </c>
       <c r="G176" s="11" t="n">
         <v>1</v>
@@ -12279,7 +12279,7 @@
       </c>
       <c r="B177" s="11" t="inlineStr">
         <is>
-          <t>BM-P202</t>
+          <t>BM-P200</t>
         </is>
       </c>
       <c r="C177" s="11" t="inlineStr">
@@ -12288,13 +12288,13 @@
         </is>
       </c>
       <c r="D177" s="11" t="n">
-        <v>-292.07</v>
+        <v>-428.65</v>
       </c>
       <c r="E177" s="11" t="n">
-        <v>244.36</v>
+        <v>126.18</v>
       </c>
       <c r="F177" s="11" t="n">
-        <v>662.53</v>
+        <v>662.4299999999999</v>
       </c>
       <c r="G177" s="11" t="n">
         <v>1</v>
@@ -12323,7 +12323,7 @@
       </c>
       <c r="B178" s="11" t="inlineStr">
         <is>
-          <t>BM-P203</t>
+          <t>BM-P201</t>
         </is>
       </c>
       <c r="C178" s="11" t="inlineStr">
@@ -12332,13 +12332,13 @@
         </is>
       </c>
       <c r="D178" s="11" t="n">
-        <v>-314.53</v>
+        <v>-362.49</v>
       </c>
       <c r="E178" s="11" t="n">
-        <v>58.38</v>
+        <v>293.31</v>
       </c>
       <c r="F178" s="11" t="n">
-        <v>663.8200000000001</v>
+        <v>662.35</v>
       </c>
       <c r="G178" s="11" t="n">
         <v>1</v>
@@ -12367,7 +12367,7 @@
       </c>
       <c r="B179" s="11" t="inlineStr">
         <is>
-          <t>BM-P204</t>
+          <t>BM-P202</t>
         </is>
       </c>
       <c r="C179" s="11" t="inlineStr">
@@ -12376,13 +12376,13 @@
         </is>
       </c>
       <c r="D179" s="11" t="n">
-        <v>-308.55</v>
+        <v>-292.07</v>
       </c>
       <c r="E179" s="11" t="n">
-        <v>250.05</v>
+        <v>244.36</v>
       </c>
       <c r="F179" s="11" t="n">
-        <v>662.4299999999999</v>
+        <v>662.53</v>
       </c>
       <c r="G179" s="11" t="n">
         <v>1</v>
@@ -12411,7 +12411,7 @@
       </c>
       <c r="B180" s="11" t="inlineStr">
         <is>
-          <t>BM-P205</t>
+          <t>BM-P203</t>
         </is>
       </c>
       <c r="C180" s="11" t="inlineStr">
@@ -12420,13 +12420,13 @@
         </is>
       </c>
       <c r="D180" s="11" t="n">
-        <v>-439.03</v>
+        <v>-314.53</v>
       </c>
       <c r="E180" s="11" t="n">
-        <v>139.36</v>
+        <v>58.38</v>
       </c>
       <c r="F180" s="11" t="n">
-        <v>662.27</v>
+        <v>663.8200000000001</v>
       </c>
       <c r="G180" s="11" t="n">
         <v>1</v>
@@ -12455,7 +12455,7 @@
       </c>
       <c r="B181" s="11" t="inlineStr">
         <is>
-          <t>BM-P206</t>
+          <t>BM-P204</t>
         </is>
       </c>
       <c r="C181" s="11" t="inlineStr">
@@ -12464,13 +12464,13 @@
         </is>
       </c>
       <c r="D181" s="11" t="n">
-        <v>-187.88</v>
+        <v>-308.55</v>
       </c>
       <c r="E181" s="11" t="n">
-        <v>140.43</v>
+        <v>250.05</v>
       </c>
       <c r="F181" s="11" t="n">
-        <v>662.27</v>
+        <v>662.4299999999999</v>
       </c>
       <c r="G181" s="11" t="n">
         <v>1</v>
@@ -12499,7 +12499,7 @@
       </c>
       <c r="B182" s="11" t="inlineStr">
         <is>
-          <t>BM-P207</t>
+          <t>BM-P205</t>
         </is>
       </c>
       <c r="C182" s="11" t="inlineStr">
@@ -12508,13 +12508,13 @@
         </is>
       </c>
       <c r="D182" s="11" t="n">
-        <v>-411.87</v>
+        <v>-439.03</v>
       </c>
       <c r="E182" s="11" t="n">
-        <v>85.19</v>
+        <v>139.36</v>
       </c>
       <c r="F182" s="11" t="n">
-        <v>662.34</v>
+        <v>662.27</v>
       </c>
       <c r="G182" s="11" t="n">
         <v>1</v>
@@ -12543,7 +12543,7 @@
       </c>
       <c r="B183" s="11" t="inlineStr">
         <is>
-          <t>BM-P208</t>
+          <t>BM-P206</t>
         </is>
       </c>
       <c r="C183" s="11" t="inlineStr">
@@ -12552,13 +12552,13 @@
         </is>
       </c>
       <c r="D183" s="11" t="n">
-        <v>-382.48</v>
+        <v>-187.88</v>
       </c>
       <c r="E183" s="11" t="n">
-        <v>304.87</v>
+        <v>140.43</v>
       </c>
       <c r="F183" s="11" t="n">
-        <v>662.37</v>
+        <v>662.27</v>
       </c>
       <c r="G183" s="11" t="n">
         <v>1</v>
@@ -12587,7 +12587,7 @@
       </c>
       <c r="B184" s="11" t="inlineStr">
         <is>
-          <t>BM-P209</t>
+          <t>BM-P207</t>
         </is>
       </c>
       <c r="C184" s="11" t="inlineStr">
@@ -12596,13 +12596,13 @@
         </is>
       </c>
       <c r="D184" s="11" t="n">
-        <v>-271.32</v>
+        <v>-411.87</v>
       </c>
       <c r="E184" s="11" t="n">
-        <v>242.01</v>
+        <v>85.19</v>
       </c>
       <c r="F184" s="11" t="n">
-        <v>662.3099999999999</v>
+        <v>662.34</v>
       </c>
       <c r="G184" s="11" t="n">
         <v>1</v>
@@ -12631,7 +12631,7 @@
       </c>
       <c r="B185" s="11" t="inlineStr">
         <is>
-          <t>BM-P210</t>
+          <t>BM-P208</t>
         </is>
       </c>
       <c r="C185" s="11" t="inlineStr">
@@ -12640,13 +12640,13 @@
         </is>
       </c>
       <c r="D185" s="11" t="n">
-        <v>-286.77</v>
+        <v>-382.48</v>
       </c>
       <c r="E185" s="11" t="n">
-        <v>39.76</v>
+        <v>304.87</v>
       </c>
       <c r="F185" s="11" t="n">
-        <v>662.27</v>
+        <v>662.37</v>
       </c>
       <c r="G185" s="11" t="n">
         <v>1</v>
@@ -12675,7 +12675,7 @@
       </c>
       <c r="B186" s="11" t="inlineStr">
         <is>
-          <t>BM-P212</t>
+          <t>BM-P209</t>
         </is>
       </c>
       <c r="C186" s="11" t="inlineStr">
@@ -12684,13 +12684,13 @@
         </is>
       </c>
       <c r="D186" s="11" t="n">
-        <v>-303.42</v>
+        <v>-271.32</v>
       </c>
       <c r="E186" s="11" t="n">
-        <v>55.13</v>
+        <v>242.01</v>
       </c>
       <c r="F186" s="11" t="n">
-        <v>662.27</v>
+        <v>662.3099999999999</v>
       </c>
       <c r="G186" s="11" t="n">
         <v>1</v>
@@ -12719,7 +12719,7 @@
       </c>
       <c r="B187" s="11" t="inlineStr">
         <is>
-          <t>BM-P213</t>
+          <t>BM-P210</t>
         </is>
       </c>
       <c r="C187" s="11" t="inlineStr">
@@ -12728,13 +12728,13 @@
         </is>
       </c>
       <c r="D187" s="11" t="n">
-        <v>-322.29</v>
+        <v>-286.77</v>
       </c>
       <c r="E187" s="11" t="n">
-        <v>261.21</v>
+        <v>39.76</v>
       </c>
       <c r="F187" s="11" t="n">
-        <v>662.42</v>
+        <v>662.27</v>
       </c>
       <c r="G187" s="11" t="n">
         <v>1</v>
@@ -12763,7 +12763,7 @@
       </c>
       <c r="B188" s="11" t="inlineStr">
         <is>
-          <t>BM-P214</t>
+          <t>BM-P212</t>
         </is>
       </c>
       <c r="C188" s="11" t="inlineStr">
@@ -12772,13 +12772,13 @@
         </is>
       </c>
       <c r="D188" s="11" t="n">
-        <v>-451.83</v>
+        <v>-303.42</v>
       </c>
       <c r="E188" s="11" t="n">
-        <v>148.54</v>
+        <v>55.13</v>
       </c>
       <c r="F188" s="11" t="n">
-        <v>662.29</v>
+        <v>662.27</v>
       </c>
       <c r="G188" s="11" t="n">
         <v>1</v>
@@ -12807,7 +12807,7 @@
       </c>
       <c r="B189" s="11" t="inlineStr">
         <is>
-          <t>BM-P215</t>
+          <t>BM-P213</t>
         </is>
       </c>
       <c r="C189" s="11" t="inlineStr">
@@ -12816,13 +12816,13 @@
         </is>
       </c>
       <c r="D189" s="11" t="n">
-        <v>-424.31</v>
+        <v>-322.29</v>
       </c>
       <c r="E189" s="11" t="n">
-        <v>117.21</v>
+        <v>261.21</v>
       </c>
       <c r="F189" s="11" t="n">
-        <v>662.38</v>
+        <v>662.42</v>
       </c>
       <c r="G189" s="11" t="n">
         <v>1</v>
@@ -12842,6 +12842,94 @@
         <v>16.2</v>
       </c>
       <c r="L189" s="11" t="n">
+        <v>0.635</v>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" s="11" t="n">
+        <v>187</v>
+      </c>
+      <c r="B190" s="11" t="inlineStr">
+        <is>
+          <t>BM-P214</t>
+        </is>
+      </c>
+      <c r="C190" s="11" t="inlineStr">
+        <is>
+          <t>BÈ 6</t>
+        </is>
+      </c>
+      <c r="D190" s="11" t="n">
+        <v>-451.83</v>
+      </c>
+      <c r="E190" s="11" t="n">
+        <v>148.54</v>
+      </c>
+      <c r="F190" s="11" t="n">
+        <v>662.29</v>
+      </c>
+      <c r="G190" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="H190" s="11" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="I190" s="11" t="inlineStr">
+        <is>
+          <t>6Φ28 CB400-V</t>
+        </is>
+      </c>
+      <c r="J190" s="11" t="n">
+        <v>191.4</v>
+      </c>
+      <c r="K190" s="11" t="n">
+        <v>16.2</v>
+      </c>
+      <c r="L190" s="11" t="n">
+        <v>0.635</v>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" s="11" t="n">
+        <v>188</v>
+      </c>
+      <c r="B191" s="11" t="inlineStr">
+        <is>
+          <t>BM-P215</t>
+        </is>
+      </c>
+      <c r="C191" s="11" t="inlineStr">
+        <is>
+          <t>BÈ 6</t>
+        </is>
+      </c>
+      <c r="D191" s="11" t="n">
+        <v>-424.31</v>
+      </c>
+      <c r="E191" s="11" t="n">
+        <v>117.21</v>
+      </c>
+      <c r="F191" s="11" t="n">
+        <v>662.38</v>
+      </c>
+      <c r="G191" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="H191" s="11" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="I191" s="11" t="inlineStr">
+        <is>
+          <t>6Φ28 CB400-V</t>
+        </is>
+      </c>
+      <c r="J191" s="11" t="n">
+        <v>191.4</v>
+      </c>
+      <c r="K191" s="11" t="n">
+        <v>16.2</v>
+      </c>
+      <c r="L191" s="11" t="n">
         <v>0.635</v>
       </c>
     </row>
@@ -12856,7 +12944,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M33"/>
+  <dimension ref="A1:M30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10.83203125" customWidth="1" min="1" max="1"/>
@@ -12877,14 +12965,14 @@
     <row r="1">
       <c r="A1" s="10" t="inlineStr">
         <is>
-          <t>ĐẾ NEO ĐÁY BTCT + VÍT XOẮN — TỪNG ĐẾ (19 đế: 10 đế dùng chung, 9 đế một dây)</t>
+          <t>ĐẾ NEO ĐÁY BTCT + VÍT XOẮN — TỪNG ĐẾ (17 đế: 10 đế dùng chung, 7 đế một dây)</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Bê tông C25/30 chống thấm; thép bản Φ12 a200; 4 vít ống Ø89×5 ren Ø105 ngàm 3 m mỗi đế; tai neo đôi (đế dùng chung) / đơn. Cao độ đặt đế 646,3–654,4 m.</t>
+          <t>Bê tông C25/30 chống thấm; thép bản Φ12 a200; 4 vít ống Ø89×5 ren Ø105 ngàm 3 m mỗi đế; tai neo đôi (đế dùng chung) / đơn. Cao độ đặt đế 646,3–650,5 m.</t>
         </is>
       </c>
     </row>
@@ -13469,7 +13557,7 @@
         <v>36.7</v>
       </c>
       <c r="M14" s="11" t="n">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
     </row>
     <row r="15">
@@ -13563,7 +13651,7 @@
         <v>33.7</v>
       </c>
       <c r="M16" s="11" t="n">
-        <v>0.99</v>
+        <v>1</v>
       </c>
     </row>
     <row r="17">
@@ -13577,25 +13665,25 @@
       </c>
       <c r="C17" s="11" t="inlineStr">
         <is>
-          <t>B3-D16</t>
+          <t>B5-D17 + B6-D06</t>
         </is>
       </c>
       <c r="D17" s="11" t="inlineStr">
         <is>
-          <t>BÈ 3</t>
+          <t>BÈ 5 + BÈ 6</t>
         </is>
       </c>
       <c r="E17" s="11" t="n">
-        <v>2.5</v>
+        <v>5.75</v>
       </c>
       <c r="F17" s="11" t="n">
         <v>0.4</v>
       </c>
       <c r="G17" s="11" t="n">
-        <v>2.48</v>
+        <v>13.21</v>
       </c>
       <c r="H17" s="11" t="n">
-        <v>119.4</v>
+        <v>602.4</v>
       </c>
       <c r="I17" s="11" t="n">
         <v>4</v>
@@ -13607,10 +13695,10 @@
         <v>153</v>
       </c>
       <c r="L17" s="11" t="n">
-        <v>6.37</v>
+        <v>33.7</v>
       </c>
       <c r="M17" s="11" t="n">
-        <v>0.44</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="18">
@@ -13624,25 +13712,25 @@
       </c>
       <c r="C18" s="11" t="inlineStr">
         <is>
-          <t>B3-D18</t>
+          <t>B6-D13</t>
         </is>
       </c>
       <c r="D18" s="11" t="inlineStr">
         <is>
-          <t>BÈ 3</t>
+          <t>BÈ 6</t>
         </is>
       </c>
       <c r="E18" s="11" t="n">
-        <v>2.5</v>
+        <v>4</v>
       </c>
       <c r="F18" s="11" t="n">
         <v>0.4</v>
       </c>
       <c r="G18" s="11" t="n">
-        <v>2.48</v>
+        <v>6.38</v>
       </c>
       <c r="H18" s="11" t="n">
-        <v>119.4</v>
+        <v>291.1</v>
       </c>
       <c r="I18" s="11" t="n">
         <v>4</v>
@@ -13654,10 +13742,10 @@
         <v>153</v>
       </c>
       <c r="L18" s="11" t="n">
-        <v>6.37</v>
+        <v>16.31</v>
       </c>
       <c r="M18" s="11" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.97</v>
       </c>
     </row>
     <row r="19">
@@ -13671,25 +13759,25 @@
       </c>
       <c r="C19" s="11" t="inlineStr">
         <is>
-          <t>B5-D17 + B6-D06</t>
+          <t>B6-D25</t>
         </is>
       </c>
       <c r="D19" s="11" t="inlineStr">
         <is>
-          <t>BÈ 5 + BÈ 6</t>
+          <t>BÈ 6</t>
         </is>
       </c>
       <c r="E19" s="11" t="n">
-        <v>5.75</v>
+        <v>4</v>
       </c>
       <c r="F19" s="11" t="n">
         <v>0.4</v>
       </c>
       <c r="G19" s="11" t="n">
-        <v>13.21</v>
+        <v>6.38</v>
       </c>
       <c r="H19" s="11" t="n">
-        <v>602.4</v>
+        <v>291.1</v>
       </c>
       <c r="I19" s="11" t="n">
         <v>4</v>
@@ -13701,10 +13789,10 @@
         <v>153</v>
       </c>
       <c r="L19" s="11" t="n">
-        <v>33.7</v>
+        <v>16.31</v>
       </c>
       <c r="M19" s="11" t="n">
-        <v>0.95</v>
+        <v>0.99</v>
       </c>
     </row>
     <row r="20">
@@ -13718,7 +13806,7 @@
       </c>
       <c r="C20" s="11" t="inlineStr">
         <is>
-          <t>B6-D13</t>
+          <t>B6-D46</t>
         </is>
       </c>
       <c r="D20" s="11" t="inlineStr">
@@ -13751,174 +13839,142 @@
         <v>16.31</v>
       </c>
       <c r="M20" s="11" t="n">
-        <v>0.97</v>
+        <v>0.96</v>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="11" t="n">
-        <v>18</v>
+      <c r="A21" s="11" t="inlineStr">
+        <is>
+          <t>TỔNG</t>
+        </is>
       </c>
       <c r="B21" s="11" t="inlineStr">
         <is>
-          <t>BM-DV018</t>
-        </is>
-      </c>
-      <c r="C21" s="11" t="inlineStr">
-        <is>
-          <t>B6-D25</t>
-        </is>
-      </c>
-      <c r="D21" s="11" t="inlineStr">
-        <is>
-          <t>BÈ 6</t>
-        </is>
-      </c>
-      <c r="E21" s="11" t="n">
-        <v>4</v>
-      </c>
-      <c r="F21" s="11" t="n">
-        <v>0.4</v>
-      </c>
+          <t>17 đế</t>
+        </is>
+      </c>
+      <c r="C21" s="11" t="str"/>
+      <c r="D21" s="11" t="str"/>
+      <c r="E21" s="11" t="str"/>
+      <c r="F21" s="11" t="str"/>
       <c r="G21" s="11" t="n">
-        <v>6.38</v>
+        <v>128.28</v>
       </c>
       <c r="H21" s="11" t="n">
-        <v>291.1</v>
+        <v>5620</v>
       </c>
       <c r="I21" s="11" t="n">
-        <v>4</v>
+        <v>68</v>
       </c>
       <c r="J21" s="11" t="n">
-        <v>14.8</v>
+        <v>253.2</v>
       </c>
       <c r="K21" s="11" t="n">
-        <v>153</v>
-      </c>
-      <c r="L21" s="11" t="n">
-        <v>16.31</v>
-      </c>
-      <c r="M21" s="11" t="n">
-        <v>0.99</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="11" t="n">
-        <v>19</v>
-      </c>
-      <c r="B22" s="11" t="inlineStr">
-        <is>
-          <t>BM-DV019</t>
-        </is>
-      </c>
-      <c r="C22" s="11" t="inlineStr">
-        <is>
-          <t>B6-D46</t>
-        </is>
-      </c>
-      <c r="D22" s="11" t="inlineStr">
-        <is>
-          <t>BÈ 6</t>
-        </is>
-      </c>
-      <c r="E22" s="11" t="n">
-        <v>4</v>
-      </c>
-      <c r="F22" s="11" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="G22" s="11" t="n">
-        <v>6.38</v>
-      </c>
-      <c r="H22" s="11" t="n">
-        <v>291.1</v>
-      </c>
-      <c r="I22" s="11" t="n">
-        <v>4</v>
-      </c>
-      <c r="J22" s="11" t="n">
-        <v>14.8</v>
-      </c>
-      <c r="K22" s="11" t="n">
-        <v>153</v>
-      </c>
-      <c r="L22" s="11" t="n">
-        <v>16.31</v>
-      </c>
-      <c r="M22" s="11" t="n">
-        <v>0.96</v>
-      </c>
-    </row>
+        <v>2623</v>
+      </c>
+      <c r="L21" s="11" t="str"/>
+      <c r="M21" s="11" t="str"/>
+    </row>
+    <row r="22"/>
     <row r="23">
       <c r="A23" s="11" t="inlineStr">
         <is>
-          <t>TỔNG</t>
-        </is>
-      </c>
-      <c r="B23" s="11" t="inlineStr">
-        <is>
-          <t>19 đế</t>
-        </is>
-      </c>
+          <t>THEO CỠ ĐẾ</t>
+        </is>
+      </c>
+      <c r="B23" s="11" t="str"/>
       <c r="C23" s="11" t="str"/>
-      <c r="D23" s="11" t="str"/>
-      <c r="E23" s="11" t="str"/>
-      <c r="F23" s="11" t="str"/>
-      <c r="G23" s="11" t="n">
-        <v>133.24</v>
-      </c>
-      <c r="H23" s="11" t="n">
-        <v>5859</v>
-      </c>
-      <c r="I23" s="11" t="n">
-        <v>76</v>
-      </c>
-      <c r="J23" s="11" t="n">
-        <v>282.8</v>
-      </c>
-      <c r="K23" s="11" t="n">
-        <v>2929</v>
-      </c>
-      <c r="L23" s="11" t="str"/>
-      <c r="M23" s="11" t="str"/>
-    </row>
-    <row r="24"/>
+      <c r="D23" s="11" t="inlineStr">
+        <is>
+          <t>Số đế</t>
+        </is>
+      </c>
+      <c r="E23" s="11" t="inlineStr">
+        <is>
+          <t>Cạnh B (m)</t>
+        </is>
+      </c>
+      <c r="F23" s="11" t="inlineStr">
+        <is>
+          <t>Dày t (m)</t>
+        </is>
+      </c>
+      <c r="G23" s="11" t="inlineStr">
+        <is>
+          <t>Bê tông (m³)</t>
+        </is>
+      </c>
+      <c r="H23" s="11" t="inlineStr">
+        <is>
+          <t>Thép bản (kg)</t>
+        </is>
+      </c>
+      <c r="I23" s="11" t="inlineStr">
+        <is>
+          <t>Số vít</t>
+        </is>
+      </c>
+      <c r="J23" s="11" t="n"/>
+      <c r="K23" s="11" t="n"/>
+      <c r="L23" s="11" t="n"/>
+      <c r="M23" s="11" t="n"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="11" t="inlineStr">
+        <is>
+          <t>Đế 2,75 m</t>
+        </is>
+      </c>
+      <c r="B24" s="11" t="str"/>
+      <c r="C24" s="11" t="str"/>
+      <c r="D24" s="11" t="n">
+        <v>2</v>
+      </c>
+      <c r="E24" s="11" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="F24" s="11" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="G24" s="11" t="n">
+        <v>6.01</v>
+      </c>
+      <c r="H24" s="11" t="n">
+        <v>283</v>
+      </c>
+      <c r="I24" s="11" t="n">
+        <v>8</v>
+      </c>
+      <c r="J24" s="11" t="n"/>
+      <c r="K24" s="11" t="n"/>
+      <c r="L24" s="11" t="n"/>
+      <c r="M24" s="11" t="n"/>
+    </row>
     <row r="25">
       <c r="A25" s="11" t="inlineStr">
         <is>
-          <t>THEO CỠ ĐẾ</t>
+          <t>Đế 3,50 m</t>
         </is>
       </c>
       <c r="B25" s="11" t="str"/>
       <c r="C25" s="11" t="str"/>
-      <c r="D25" s="11" t="inlineStr">
-        <is>
-          <t>Số đế</t>
-        </is>
-      </c>
-      <c r="E25" s="11" t="inlineStr">
-        <is>
-          <t>Cạnh B (m)</t>
-        </is>
-      </c>
-      <c r="F25" s="11" t="inlineStr">
-        <is>
-          <t>Dày t (m)</t>
-        </is>
-      </c>
-      <c r="G25" s="11" t="inlineStr">
-        <is>
-          <t>Bê tông (m³)</t>
-        </is>
-      </c>
-      <c r="H25" s="11" t="inlineStr">
-        <is>
-          <t>Thép bản (kg)</t>
-        </is>
-      </c>
-      <c r="I25" s="11" t="inlineStr">
-        <is>
-          <t>Số vít</t>
-        </is>
+      <c r="D25" s="11" t="n">
+        <v>2</v>
+      </c>
+      <c r="E25" s="11" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="F25" s="11" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="G25" s="11" t="n">
+        <v>9.76</v>
+      </c>
+      <c r="H25" s="11" t="n">
+        <v>459</v>
+      </c>
+      <c r="I25" s="11" t="n">
+        <v>8</v>
       </c>
       <c r="J25" s="11" t="n"/>
       <c r="K25" s="11" t="n"/>
@@ -13928,28 +13984,28 @@
     <row r="26">
       <c r="A26" s="11" t="inlineStr">
         <is>
-          <t>Đế 2,50 m</t>
+          <t>Đế 3,75 m</t>
         </is>
       </c>
       <c r="B26" s="11" t="str"/>
       <c r="C26" s="11" t="str"/>
       <c r="D26" s="11" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E26" s="11" t="n">
-        <v>2.5</v>
+        <v>3.75</v>
       </c>
       <c r="F26" s="11" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="G26" s="11" t="n">
-        <v>4.96</v>
+        <v>7.01</v>
       </c>
       <c r="H26" s="11" t="n">
-        <v>239</v>
+        <v>259</v>
       </c>
       <c r="I26" s="11" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="J26" s="11" t="n"/>
       <c r="K26" s="11" t="n"/>
@@ -13959,28 +14015,28 @@
     <row r="27">
       <c r="A27" s="11" t="inlineStr">
         <is>
-          <t>Đế 2,75 m</t>
+          <t>Đế 4,00 m</t>
         </is>
       </c>
       <c r="B27" s="11" t="str"/>
       <c r="C27" s="11" t="str"/>
       <c r="D27" s="11" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E27" s="11" t="n">
-        <v>2.75</v>
+        <v>4</v>
       </c>
       <c r="F27" s="11" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="G27" s="11" t="n">
-        <v>6.01</v>
+        <v>43.08</v>
       </c>
       <c r="H27" s="11" t="n">
-        <v>283</v>
+        <v>1746</v>
       </c>
       <c r="I27" s="11" t="n">
-        <v>8</v>
+        <v>24</v>
       </c>
       <c r="J27" s="11" t="n"/>
       <c r="K27" s="11" t="n"/>
@@ -13990,28 +14046,28 @@
     <row r="28">
       <c r="A28" s="11" t="inlineStr">
         <is>
-          <t>Đế 3,50 m</t>
+          <t>Đế 4,25 m</t>
         </is>
       </c>
       <c r="B28" s="11" t="str"/>
       <c r="C28" s="11" t="str"/>
       <c r="D28" s="11" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E28" s="11" t="n">
-        <v>3.5</v>
+        <v>4.25</v>
       </c>
       <c r="F28" s="11" t="n">
         <v>0.4</v>
       </c>
       <c r="G28" s="11" t="n">
-        <v>9.76</v>
+        <v>21.62</v>
       </c>
       <c r="H28" s="11" t="n">
-        <v>459</v>
+        <v>1018</v>
       </c>
       <c r="I28" s="11" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="J28" s="11" t="n"/>
       <c r="K28" s="11" t="n"/>
@@ -14021,28 +14077,28 @@
     <row r="29">
       <c r="A29" s="11" t="inlineStr">
         <is>
-          <t>Đế 3,75 m</t>
+          <t>Đế 5,75 m</t>
         </is>
       </c>
       <c r="B29" s="11" t="str"/>
       <c r="C29" s="11" t="str"/>
       <c r="D29" s="11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E29" s="11" t="n">
-        <v>3.75</v>
+        <v>5.75</v>
       </c>
       <c r="F29" s="11" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="G29" s="11" t="n">
-        <v>7.01</v>
+        <v>26.41</v>
       </c>
       <c r="H29" s="11" t="n">
-        <v>259</v>
+        <v>1205</v>
       </c>
       <c r="I29" s="11" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="J29" s="11" t="n"/>
       <c r="K29" s="11" t="n"/>
@@ -14052,126 +14108,33 @@
     <row r="30">
       <c r="A30" s="11" t="inlineStr">
         <is>
-          <t>Đế 4,00 m</t>
+          <t>Đế 6,00 m</t>
         </is>
       </c>
       <c r="B30" s="11" t="str"/>
       <c r="C30" s="11" t="str"/>
       <c r="D30" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="E30" s="11" t="n">
         <v>6</v>
       </c>
-      <c r="E30" s="11" t="n">
+      <c r="F30" s="11" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="G30" s="11" t="n">
+        <v>14.38</v>
+      </c>
+      <c r="H30" s="11" t="n">
+        <v>650</v>
+      </c>
+      <c r="I30" s="11" t="n">
         <v>4</v>
-      </c>
-      <c r="F30" s="11" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="G30" s="11" t="n">
-        <v>43.08</v>
-      </c>
-      <c r="H30" s="11" t="n">
-        <v>1746</v>
-      </c>
-      <c r="I30" s="11" t="n">
-        <v>24</v>
       </c>
       <c r="J30" s="11" t="n"/>
       <c r="K30" s="11" t="n"/>
       <c r="L30" s="11" t="n"/>
       <c r="M30" s="11" t="n"/>
-    </row>
-    <row r="31">
-      <c r="A31" s="11" t="inlineStr">
-        <is>
-          <t>Đế 4,25 m</t>
-        </is>
-      </c>
-      <c r="B31" s="11" t="str"/>
-      <c r="C31" s="11" t="str"/>
-      <c r="D31" s="11" t="n">
-        <v>3</v>
-      </c>
-      <c r="E31" s="11" t="n">
-        <v>4.25</v>
-      </c>
-      <c r="F31" s="11" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="G31" s="11" t="n">
-        <v>21.62</v>
-      </c>
-      <c r="H31" s="11" t="n">
-        <v>1018</v>
-      </c>
-      <c r="I31" s="11" t="n">
-        <v>12</v>
-      </c>
-      <c r="J31" s="11" t="n"/>
-      <c r="K31" s="11" t="n"/>
-      <c r="L31" s="11" t="n"/>
-      <c r="M31" s="11" t="n"/>
-    </row>
-    <row r="32">
-      <c r="A32" s="11" t="inlineStr">
-        <is>
-          <t>Đế 5,75 m</t>
-        </is>
-      </c>
-      <c r="B32" s="11" t="str"/>
-      <c r="C32" s="11" t="str"/>
-      <c r="D32" s="11" t="n">
-        <v>2</v>
-      </c>
-      <c r="E32" s="11" t="n">
-        <v>5.75</v>
-      </c>
-      <c r="F32" s="11" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="G32" s="11" t="n">
-        <v>26.41</v>
-      </c>
-      <c r="H32" s="11" t="n">
-        <v>1205</v>
-      </c>
-      <c r="I32" s="11" t="n">
-        <v>8</v>
-      </c>
-      <c r="J32" s="11" t="n"/>
-      <c r="K32" s="11" t="n"/>
-      <c r="L32" s="11" t="n"/>
-      <c r="M32" s="11" t="n"/>
-    </row>
-    <row r="33">
-      <c r="A33" s="11" t="inlineStr">
-        <is>
-          <t>Đế 6,00 m</t>
-        </is>
-      </c>
-      <c r="B33" s="11" t="str"/>
-      <c r="C33" s="11" t="str"/>
-      <c r="D33" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="E33" s="11" t="n">
-        <v>6</v>
-      </c>
-      <c r="F33" s="11" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="G33" s="11" t="n">
-        <v>14.38</v>
-      </c>
-      <c r="H33" s="11" t="n">
-        <v>650</v>
-      </c>
-      <c r="I33" s="11" t="n">
-        <v>4</v>
-      </c>
-      <c r="J33" s="11" t="n"/>
-      <c r="K33" s="11" t="n"/>
-      <c r="L33" s="11" t="n"/>
-      <c r="M33" s="11" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -14388,7 +14351,7 @@
         </is>
       </c>
       <c r="B6" s="11" t="n">
-        <v>76.5</v>
+        <v>78.7</v>
       </c>
       <c r="C6" s="11" t="inlineStr">
         <is>
@@ -14399,10 +14362,10 @@
         <v>305</v>
       </c>
       <c r="E6" s="11" t="n">
-        <v>44.2</v>
+        <v>45.4</v>
       </c>
       <c r="F6" s="11" t="n">
-        <v>53.6</v>
+        <v>55.1</v>
       </c>
       <c r="G6" s="11" t="inlineStr">
         <is>
@@ -14413,10 +14376,10 @@
         <v>172</v>
       </c>
       <c r="I6" s="11" t="n">
-        <v>3.21</v>
+        <v>3.12</v>
       </c>
       <c r="J6" s="11" t="n">
-        <v>2.25</v>
+        <v>2.19</v>
       </c>
       <c r="K6" s="11" t="n">
         <v>9.5</v>
@@ -20845,27 +20808,27 @@
       </c>
       <c r="D114" s="11" t="inlineStr">
         <is>
-          <t>Đế đáy</t>
+          <t>Cọc bờ</t>
         </is>
       </c>
       <c r="E114" s="11" t="inlineStr">
         <is>
-          <t>DV-014</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F114" s="11" t="n">
-        <v>17.5</v>
+        <v>46.16</v>
       </c>
       <c r="G114" s="11" t="inlineStr">
         <is>
-          <t>MNLKT</t>
+          <t>MNC</t>
         </is>
       </c>
       <c r="H114" s="11" t="n">
-        <v>22.67</v>
+        <v>48.05</v>
       </c>
       <c r="I114" s="11" t="n">
-        <v>20.42</v>
+        <v>45.14</v>
       </c>
       <c r="J114" s="11" t="inlineStr">
         <is>
@@ -20882,11 +20845,7 @@
           <t>PES-24</t>
         </is>
       </c>
-      <c r="M114" s="11" t="inlineStr">
-        <is>
-          <t>Cáp dốc tới 39°: thành phần đứng lớn tại bích bè; Đo cao độ đáy thực tế trước khi cắt</t>
-        </is>
-      </c>
+      <c r="M114" s="11" t="str"/>
     </row>
     <row r="115">
       <c r="A115" s="11" t="n">
@@ -20959,27 +20918,27 @@
       </c>
       <c r="D116" s="11" t="inlineStr">
         <is>
-          <t>Đế đáy</t>
+          <t>Cọc bờ</t>
         </is>
       </c>
       <c r="E116" s="11" t="inlineStr">
         <is>
-          <t>DV-015</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F116" s="11" t="n">
-        <v>17.5</v>
+        <v>42</v>
       </c>
       <c r="G116" s="11" t="inlineStr">
         <is>
-          <t>MNLKT</t>
+          <t>MNC</t>
         </is>
       </c>
       <c r="H116" s="11" t="n">
-        <v>24.59</v>
+        <v>43.84</v>
       </c>
       <c r="I116" s="11" t="n">
-        <v>22.54</v>
+        <v>40.95</v>
       </c>
       <c r="J116" s="11" t="inlineStr">
         <is>
@@ -20996,11 +20955,7 @@
           <t>PES-24</t>
         </is>
       </c>
-      <c r="M116" s="11" t="inlineStr">
-        <is>
-          <t>Cáp dốc tới 45°: thành phần đứng lớn tại bích bè; Đo cao độ đáy thực tế trước khi cắt</t>
-        </is>
-      </c>
+      <c r="M116" s="11" t="str"/>
     </row>
     <row r="117">
       <c r="A117" s="11" t="n">
@@ -23011,7 +22966,7 @@
       </c>
       <c r="E153" s="11" t="inlineStr">
         <is>
-          <t>DV-016</t>
+          <t>DV-014</t>
         </is>
       </c>
       <c r="F153" s="11" t="n">
@@ -24170,7 +24125,7 @@
       </c>
       <c r="E174" s="11" t="inlineStr">
         <is>
-          <t>DV-016</t>
+          <t>DV-014</t>
         </is>
       </c>
       <c r="F174" s="11" t="n">
@@ -24559,7 +24514,7 @@
       </c>
       <c r="E181" s="11" t="inlineStr">
         <is>
-          <t>DV-017</t>
+          <t>DV-015</t>
         </is>
       </c>
       <c r="F181" s="11" t="n">
@@ -25223,7 +25178,7 @@
       </c>
       <c r="E193" s="11" t="inlineStr">
         <is>
-          <t>DV-018</t>
+          <t>DV-016</t>
         </is>
       </c>
       <c r="F193" s="11" t="n">
@@ -26382,7 +26337,7 @@
       </c>
       <c r="E214" s="11" t="inlineStr">
         <is>
-          <t>DV-019</t>
+          <t>DV-017</t>
         </is>
       </c>
       <c r="F214" s="11" t="n">
@@ -27000,10 +26955,10 @@
         </is>
       </c>
       <c r="C8" s="11" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="D8" s="11" t="n">
-        <v>76.5</v>
+        <v>78.7</v>
       </c>
       <c r="E8" s="11" t="n">
         <v>0</v>
@@ -27018,16 +26973,16 @@
         <v>600</v>
       </c>
       <c r="I8" s="11" t="n">
-        <v>0.92</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="J8" s="11" t="n">
-        <v>0.62</v>
+        <v>0.64</v>
       </c>
       <c r="K8" s="11" t="n">
         <v>0.18</v>
       </c>
       <c r="L8" s="11" t="n">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="M8" s="11" t="n">
         <v>0.07000000000000001</v>
@@ -27052,13 +27007,13 @@
         </is>
       </c>
       <c r="C9" s="11" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D9" s="11" t="n">
-        <v>67.5</v>
+        <v>78.7</v>
       </c>
       <c r="E9" s="11" t="n">
-        <v>68</v>
+        <v>63</v>
       </c>
       <c r="F9" s="11" t="n">
         <v>8.5</v>
@@ -27070,19 +27025,19 @@
         <v>350</v>
       </c>
       <c r="I9" s="11" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="J9" s="11" t="n">
-        <v>0.55</v>
+        <v>0.64</v>
       </c>
       <c r="K9" s="11" t="n">
-        <v>0.16</v>
+        <v>0.18</v>
       </c>
       <c r="L9" s="11" t="n">
-        <v>0.36</v>
+        <v>0.46</v>
       </c>
       <c r="M9" s="11" t="n">
-        <v>0.06</v>
+        <v>0.09</v>
       </c>
       <c r="N9" s="11" t="n">
         <v>0.9399999999999999</v>
@@ -27422,7 +27377,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Dây đáy: đế đặt trên mặt đất theo địa hình IFC (646,3–654,4 m), CHƯA khảo sát — đo thực tế trước khi cắt; đoạn xích 1,2 m giữa tấm chia Y và cáp chính để chỉnh trên mặt nước.</t>
+          <t>Dây đáy: đế đặt trên mặt đất theo địa hình IFC (646,3–650,5 m), CHƯA khảo sát — đo thực tế trước khi cắt; đoạn xích 1,2 m giữa tấm chia Y và cáp chính để chỉnh trên mặt nước.</t>
         </is>
       </c>
     </row>
@@ -27458,7 +27413,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>0 điểm neo bờ dùng cọc đôi (186 cọc / 186 điểm); đài nối đầu cọc đôi: thiết kế sơ bộ ở mục II. 9/19 đế là đế một dây ở vùng nước trống; đế nặng nhất 36,7 t — cần sà lan / cẩu phù hợp.</t>
+          <t>0 điểm neo bờ dùng cọc đôi (188 cọc / 188 điểm); đài nối đầu cọc đôi: thiết kế sơ bộ ở mục II. 7/17 đế là đế một dây ở vùng nước trống; đế nặng nhất 36,7 t — cần sà lan / cẩu phù hợp.</t>
         </is>
       </c>
     </row>
